--- a/src_files/data_files/ObservedTrends.xlsx
+++ b/src_files/data_files/ObservedTrends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526EDC1F-E058-4971-BDC9-7B576B48563F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8DEFB4-1E63-4F5A-964A-721DC2473E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="770" firstSheet="4" activeTab="12" xr2:uid="{FFD27B4C-068C-4319-9C46-FFCA72C83648}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="770" firstSheet="6" activeTab="15" xr2:uid="{FFD27B4C-068C-4319-9C46-FFCA72C83648}"/>
   </bookViews>
   <sheets>
     <sheet name="VRE cap - ENTSOE NT2030" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="transferdata" sheetId="15" r:id="rId13"/>
     <sheet name="emissiondata" sheetId="16" r:id="rId14"/>
     <sheet name="unitdata_other" sheetId="18" r:id="rId15"/>
-    <sheet name="fueldata" sheetId="17" r:id="rId16"/>
+    <sheet name="nodedata" sheetId="17" r:id="rId16"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId17"/>
@@ -1751,6 +1751,89 @@
   </cellStyles>
   <dxfs count="18">
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="0" tint="-0.14999847407452621"/>
@@ -1888,89 +1971,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3977,7 +3977,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{091DB227-DDC4-472D-997A-DFFFE388BE8E}" name="Table6" displayName="Table6" ref="A1:I185" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{091DB227-DDC4-472D-997A-DFFFE388BE8E}" name="Table6" displayName="Table6" ref="A1:I185" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
   <autoFilter ref="A1:I185" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{4D600E68-4859-4617-99C0-EA7B63208C31}" name="grid"/>
@@ -3995,29 +3995,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}" name="Table3" displayName="Table3" ref="A1:E154" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}" name="Table3" displayName="Table3" ref="A1:E154" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11">
   <autoFilter ref="A1:E154" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9E8A91B3-5637-47C2-B0AE-8BCDAB50C806}" name="Country" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{41E09046-0D25-4DEB-9887-2ECB6AE473F2}" name="Generator_ID" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{5500E0F2-38FA-425D-A49B-9DFF7856120F}" name="Scenario" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{2F7FD309-B9BB-4C5B-B61A-862D1DC7A785}" name="Year" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{278785FB-0A20-4E0A-8E84-551D5FDF9FC2}" name="capacity_output1" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{9E8A91B3-5637-47C2-B0AE-8BCDAB50C806}" name="Country" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{41E09046-0D25-4DEB-9887-2ECB6AE473F2}" name="Generator_ID" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{5500E0F2-38FA-425D-A49B-9DFF7856120F}" name="Scenario" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{2F7FD309-B9BB-4C5B-B61A-862D1DC7A785}" name="Year" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{278785FB-0A20-4E0A-8E84-551D5FDF9FC2}" name="capacity_output1" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6EBB9830-FC23-4A98-9C08-0AAF69FC2331}" name="Table8" displayName="Table8" ref="A1:F21" totalsRowShown="0" headerRowDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6EBB9830-FC23-4A98-9C08-0AAF69FC2331}" name="Table8" displayName="Table8" ref="A1:F21" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:F21" xr:uid="{D9844F2F-2EE0-434B-9492-0280A28AB057}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{46AB9A07-935D-4BDF-BDAD-833C2B08B5EA}" name="Scenario" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{46AB9A07-935D-4BDF-BDAD-833C2B08B5EA}" name="Scenario" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{9C0117C3-729A-4483-9D40-255263DE774C}" name="Year"/>
-    <tableColumn id="3" xr3:uid="{F8AC0906-AF4C-4DB5-A628-E0D92C5871CF}" name="grid" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{5DE58EB2-B819-4C37-B8D5-9DAA3695DA87}" name="Country" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{2FBFC74F-134A-4E2A-8A69-7E943A399965}" name="price" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{78F6DB46-B023-4964-AA01-C06A0F1B985D}" name="emission_CO2" dataDxfId="12">
+    <tableColumn id="3" xr3:uid="{F8AC0906-AF4C-4DB5-A628-E0D92C5871CF}" name="grid" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{5DE58EB2-B819-4C37-B8D5-9DAA3695DA87}" name="Country" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{2FBFC74F-134A-4E2A-8A69-7E943A399965}" name="price" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{78F6DB46-B023-4964-AA01-C06A0F1B985D}" name="emission_CO2" dataDxfId="0">
       <calculatedColumnFormula>IFERROR(VLOOKUP($C2, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>

--- a/src_files/data_files/ObservedTrends.xlsx
+++ b/src_files/data_files/ObservedTrends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8DEFB4-1E63-4F5A-964A-721DC2473E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F6FDD8-5400-4CFF-9E90-CD25D140FB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="770" firstSheet="6" activeTab="15" xr2:uid="{FFD27B4C-068C-4319-9C46-FFCA72C83648}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="770" firstSheet="6" activeTab="12" xr2:uid="{FFD27B4C-068C-4319-9C46-FFCA72C83648}"/>
   </bookViews>
   <sheets>
     <sheet name="VRE cap - ENTSOE NT2030" sheetId="7" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3855" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3854" uniqueCount="297">
   <si>
     <t>Installed wind power capacity</t>
   </si>
@@ -1008,9 +1008,6 @@
     <t>grid</t>
   </si>
   <si>
-    <t>rampLimit</t>
-  </si>
-  <si>
     <t>variableTransCost</t>
   </si>
   <si>
@@ -1751,89 +1748,6 @@
   </cellStyles>
   <dxfs count="18">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="0" tint="-0.14999847407452621"/>
@@ -1971,6 +1885,89 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3977,16 +3974,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{091DB227-DDC4-472D-997A-DFFFE388BE8E}" name="Table6" displayName="Table6" ref="A1:I185" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
-  <autoFilter ref="A1:I185" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{091DB227-DDC4-472D-997A-DFFFE388BE8E}" name="Table6" displayName="Table6" ref="A1:H185" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
+  <autoFilter ref="A1:H185" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{4D600E68-4859-4617-99C0-EA7B63208C31}" name="grid"/>
     <tableColumn id="2" xr3:uid="{55683E09-DD2F-48C0-AB3E-CC91087C7173}" name="from_country"/>
     <tableColumn id="3" xr3:uid="{C8327C88-FBE8-4FC2-A619-A4BA01413A1C}" name="to_country"/>
     <tableColumn id="4" xr3:uid="{742C6874-D199-4EE2-A562-EA0C285890D2}" name="scenario"/>
     <tableColumn id="5" xr3:uid="{1268EAAB-42FE-4A83-98BF-F41F14FEF437}" name="Year"/>
     <tableColumn id="6" xr3:uid="{DD03EC9C-1908-4818-A7AD-696B46FD7E55}" name="transferCap"/>
-    <tableColumn id="7" xr3:uid="{DC5490B1-E58F-4907-8D03-C2EB2A32E369}" name="rampLimit"/>
     <tableColumn id="8" xr3:uid="{858FE1C4-CAB1-497D-B42D-428703C91594}" name="variableTransCost"/>
     <tableColumn id="9" xr3:uid="{BEFF1833-3A5D-4270-8A18-81866BBAA2B1}" name="transferLoss"/>
   </tableColumns>
@@ -3995,29 +3991,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}" name="Table3" displayName="Table3" ref="A1:E154" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}" name="Table3" displayName="Table3" ref="A1:E154" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
   <autoFilter ref="A1:E154" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9E8A91B3-5637-47C2-B0AE-8BCDAB50C806}" name="Country" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{41E09046-0D25-4DEB-9887-2ECB6AE473F2}" name="Generator_ID" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{5500E0F2-38FA-425D-A49B-9DFF7856120F}" name="Scenario" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{2F7FD309-B9BB-4C5B-B61A-862D1DC7A785}" name="Year" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{278785FB-0A20-4E0A-8E84-551D5FDF9FC2}" name="capacity_output1" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{9E8A91B3-5637-47C2-B0AE-8BCDAB50C806}" name="Country" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{41E09046-0D25-4DEB-9887-2ECB6AE473F2}" name="Generator_ID" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{5500E0F2-38FA-425D-A49B-9DFF7856120F}" name="Scenario" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{2F7FD309-B9BB-4C5B-B61A-862D1DC7A785}" name="Year" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{278785FB-0A20-4E0A-8E84-551D5FDF9FC2}" name="capacity_output1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6EBB9830-FC23-4A98-9C08-0AAF69FC2331}" name="Table8" displayName="Table8" ref="A1:F21" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6EBB9830-FC23-4A98-9C08-0AAF69FC2331}" name="Table8" displayName="Table8" ref="A1:F21" totalsRowShown="0" headerRowDxfId="17">
   <autoFilter ref="A1:F21" xr:uid="{D9844F2F-2EE0-434B-9492-0280A28AB057}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{46AB9A07-935D-4BDF-BDAD-833C2B08B5EA}" name="Scenario" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{46AB9A07-935D-4BDF-BDAD-833C2B08B5EA}" name="Scenario" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{9C0117C3-729A-4483-9D40-255263DE774C}" name="Year"/>
-    <tableColumn id="3" xr3:uid="{F8AC0906-AF4C-4DB5-A628-E0D92C5871CF}" name="grid" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{5DE58EB2-B819-4C37-B8D5-9DAA3695DA87}" name="Country" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{2FBFC74F-134A-4E2A-8A69-7E943A399965}" name="price" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{78F6DB46-B023-4964-AA01-C06A0F1B985D}" name="emission_CO2" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{F8AC0906-AF4C-4DB5-A628-E0D92C5871CF}" name="grid" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{5DE58EB2-B819-4C37-B8D5-9DAA3695DA87}" name="Country" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{2FBFC74F-134A-4E2A-8A69-7E943A399965}" name="price" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{78F6DB46-B023-4964-AA01-C06A0F1B985D}" name="emission_CO2" dataDxfId="12">
       <calculatedColumnFormula>IFERROR(VLOOKUP($C2, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7504,7 +7500,7 @@
         <v>224</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D68" s="19">
         <v>2025</v>
@@ -7526,7 +7522,7 @@
         <v>224</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D69" s="19">
         <v>2025</v>
@@ -7548,7 +7544,7 @@
         <v>224</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D70" s="19">
         <v>2025</v>
@@ -7570,7 +7566,7 @@
         <v>224</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D71" s="19">
         <v>2025</v>
@@ -7592,7 +7588,7 @@
         <v>224</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D72" s="19">
         <v>2025</v>
@@ -7614,7 +7610,7 @@
         <v>224</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D73" s="19">
         <v>2025</v>
@@ -7636,7 +7632,7 @@
         <v>224</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D74" s="19">
         <v>2025</v>
@@ -7658,7 +7654,7 @@
         <v>224</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D75" s="19">
         <v>2025</v>
@@ -7680,7 +7676,7 @@
         <v>224</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D76" s="19">
         <v>2025</v>
@@ -7702,7 +7698,7 @@
         <v>224</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D77" s="19">
         <v>2025</v>
@@ -7724,7 +7720,7 @@
         <v>224</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D78" s="19">
         <v>2025</v>
@@ -7746,7 +7742,7 @@
         <v>224</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D79" s="19">
         <v>2025</v>
@@ -7768,7 +7764,7 @@
         <v>224</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D80" s="19">
         <v>2025</v>
@@ -7790,7 +7786,7 @@
         <v>224</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D81" s="19">
         <v>2025</v>
@@ -7812,7 +7808,7 @@
         <v>224</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D82" s="19">
         <v>2025</v>
@@ -7834,7 +7830,7 @@
         <v>224</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D83" s="19">
         <v>2025</v>
@@ -7856,7 +7852,7 @@
         <v>224</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D84" s="19">
         <v>2025</v>
@@ -7878,7 +7874,7 @@
         <v>224</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D85" s="19">
         <v>2025</v>
@@ -7900,7 +7896,7 @@
         <v>224</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D86" s="19">
         <v>2025</v>
@@ -7922,7 +7918,7 @@
         <v>224</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D87" s="19">
         <v>2025</v>
@@ -7944,7 +7940,7 @@
         <v>224</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D88" s="19">
         <v>2025</v>
@@ -7966,7 +7962,7 @@
         <v>224</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D89" s="19">
         <v>2025</v>
@@ -7988,7 +7984,7 @@
         <v>224</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D90" s="19">
         <v>2030</v>
@@ -8010,7 +8006,7 @@
         <v>224</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D91" s="19">
         <v>2030</v>
@@ -8032,7 +8028,7 @@
         <v>224</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D92" s="19">
         <v>2030</v>
@@ -8054,7 +8050,7 @@
         <v>224</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D93" s="19">
         <v>2030</v>
@@ -8076,7 +8072,7 @@
         <v>224</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D94" s="19">
         <v>2030</v>
@@ -8098,7 +8094,7 @@
         <v>224</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D95" s="19">
         <v>2030</v>
@@ -8120,7 +8116,7 @@
         <v>224</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D96" s="19">
         <v>2030</v>
@@ -8142,7 +8138,7 @@
         <v>224</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D97" s="19">
         <v>2030</v>
@@ -8164,7 +8160,7 @@
         <v>224</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D98" s="19">
         <v>2030</v>
@@ -8186,7 +8182,7 @@
         <v>224</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D99" s="19">
         <v>2030</v>
@@ -8208,7 +8204,7 @@
         <v>224</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D100" s="19">
         <v>2030</v>
@@ -8230,7 +8226,7 @@
         <v>224</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D101" s="19">
         <v>2030</v>
@@ -8252,7 +8248,7 @@
         <v>224</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D102" s="19">
         <v>2030</v>
@@ -8274,7 +8270,7 @@
         <v>224</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D103" s="19">
         <v>2030</v>
@@ -8296,7 +8292,7 @@
         <v>224</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D104" s="19">
         <v>2030</v>
@@ -8318,7 +8314,7 @@
         <v>224</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D105" s="19">
         <v>2030</v>
@@ -8340,7 +8336,7 @@
         <v>224</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D106" s="19">
         <v>2030</v>
@@ -8362,7 +8358,7 @@
         <v>224</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D107" s="19">
         <v>2030</v>
@@ -8384,7 +8380,7 @@
         <v>224</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D108" s="19">
         <v>2030</v>
@@ -8406,7 +8402,7 @@
         <v>224</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D109" s="19">
         <v>2030</v>
@@ -8428,7 +8424,7 @@
         <v>224</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D110" s="19">
         <v>2030</v>
@@ -8450,7 +8446,7 @@
         <v>224</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D111" s="19">
         <v>2030</v>
@@ -8874,7 +8870,7 @@
         <v>225</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D134" s="19">
         <v>2025</v>
@@ -8896,7 +8892,7 @@
         <v>225</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D135" s="19">
         <v>2025</v>
@@ -8918,7 +8914,7 @@
         <v>225</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D136" s="19">
         <v>2025</v>
@@ -8940,7 +8936,7 @@
         <v>225</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D137" s="19">
         <v>2025</v>
@@ -8962,7 +8958,7 @@
         <v>225</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D138" s="19">
         <v>2025</v>
@@ -8984,7 +8980,7 @@
         <v>225</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D139" s="19">
         <v>2025</v>
@@ -9006,7 +9002,7 @@
         <v>225</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D140" s="19">
         <v>2025</v>
@@ -9028,7 +9024,7 @@
         <v>225</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D141" s="19">
         <v>2025</v>
@@ -9050,7 +9046,7 @@
         <v>225</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D142" s="19">
         <v>2025</v>
@@ -9072,7 +9068,7 @@
         <v>225</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D143" s="19">
         <v>2025</v>
@@ -9094,7 +9090,7 @@
         <v>225</v>
       </c>
       <c r="C144" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D144" s="19">
         <v>2025</v>
@@ -9116,7 +9112,7 @@
         <v>225</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D145" s="19">
         <v>2025</v>
@@ -9138,7 +9134,7 @@
         <v>225</v>
       </c>
       <c r="C146" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D146" s="19">
         <v>2025</v>
@@ -9160,7 +9156,7 @@
         <v>225</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D147" s="19">
         <v>2025</v>
@@ -9182,7 +9178,7 @@
         <v>225</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D148" s="19">
         <v>2025</v>
@@ -9204,7 +9200,7 @@
         <v>225</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D149" s="19">
         <v>2025</v>
@@ -9226,7 +9222,7 @@
         <v>225</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D150" s="19">
         <v>2025</v>
@@ -9248,7 +9244,7 @@
         <v>225</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D151" s="19">
         <v>2025</v>
@@ -9270,7 +9266,7 @@
         <v>225</v>
       </c>
       <c r="C152" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D152" s="19">
         <v>2025</v>
@@ -9292,7 +9288,7 @@
         <v>225</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D153" s="19">
         <v>2025</v>
@@ -9314,7 +9310,7 @@
         <v>225</v>
       </c>
       <c r="C154" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D154" s="19">
         <v>2025</v>
@@ -9336,7 +9332,7 @@
         <v>225</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D155" s="19">
         <v>2025</v>
@@ -9358,7 +9354,7 @@
         <v>225</v>
       </c>
       <c r="C156" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D156" s="19">
         <v>2030</v>
@@ -9380,7 +9376,7 @@
         <v>225</v>
       </c>
       <c r="C157" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D157" s="19">
         <v>2030</v>
@@ -9402,7 +9398,7 @@
         <v>225</v>
       </c>
       <c r="C158" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D158" s="19">
         <v>2030</v>
@@ -9424,7 +9420,7 @@
         <v>225</v>
       </c>
       <c r="C159" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D159" s="19">
         <v>2030</v>
@@ -9446,7 +9442,7 @@
         <v>225</v>
       </c>
       <c r="C160" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D160" s="19">
         <v>2030</v>
@@ -9468,7 +9464,7 @@
         <v>225</v>
       </c>
       <c r="C161" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D161" s="19">
         <v>2030</v>
@@ -9490,7 +9486,7 @@
         <v>225</v>
       </c>
       <c r="C162" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D162" s="19">
         <v>2030</v>
@@ -9512,7 +9508,7 @@
         <v>225</v>
       </c>
       <c r="C163" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D163" s="19">
         <v>2030</v>
@@ -9534,7 +9530,7 @@
         <v>225</v>
       </c>
       <c r="C164" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D164" s="19">
         <v>2030</v>
@@ -9556,7 +9552,7 @@
         <v>225</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D165" s="19">
         <v>2030</v>
@@ -9578,7 +9574,7 @@
         <v>225</v>
       </c>
       <c r="C166" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D166" s="19">
         <v>2030</v>
@@ -9600,7 +9596,7 @@
         <v>225</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D167" s="19">
         <v>2030</v>
@@ -9622,7 +9618,7 @@
         <v>225</v>
       </c>
       <c r="C168" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D168" s="19">
         <v>2030</v>
@@ -9644,7 +9640,7 @@
         <v>225</v>
       </c>
       <c r="C169" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D169" s="19">
         <v>2030</v>
@@ -9666,7 +9662,7 @@
         <v>225</v>
       </c>
       <c r="C170" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D170" s="19">
         <v>2030</v>
@@ -9688,7 +9684,7 @@
         <v>225</v>
       </c>
       <c r="C171" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D171" s="19">
         <v>2030</v>
@@ -9710,7 +9706,7 @@
         <v>225</v>
       </c>
       <c r="C172" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D172" s="19">
         <v>2030</v>
@@ -9732,7 +9728,7 @@
         <v>225</v>
       </c>
       <c r="C173" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D173" s="19">
         <v>2030</v>
@@ -9754,7 +9750,7 @@
         <v>225</v>
       </c>
       <c r="C174" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D174" s="19">
         <v>2030</v>
@@ -9776,7 +9772,7 @@
         <v>225</v>
       </c>
       <c r="C175" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D175" s="19">
         <v>2030</v>
@@ -9798,7 +9794,7 @@
         <v>225</v>
       </c>
       <c r="C176" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D176" s="19">
         <v>2030</v>
@@ -9820,7 +9816,7 @@
         <v>225</v>
       </c>
       <c r="C177" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D177" s="19">
         <v>2030</v>
@@ -10427,26 +10423,25 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I185"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="14.5703125" customWidth="1"/>
     <col min="4" max="4" width="21.140625" customWidth="1"/>
     <col min="5" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="78" t="s">
         <v>284</v>
       </c>
       <c r="B1" s="78" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1" s="78" t="s">
         <v>294</v>
-      </c>
-      <c r="C1" s="78" t="s">
-        <v>295</v>
       </c>
       <c r="D1" s="78" t="s">
         <v>137</v>
@@ -10455,7 +10450,7 @@
         <v>211</v>
       </c>
       <c r="F1" s="78" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G1" s="78" t="s">
         <v>285</v>
@@ -10463,11 +10458,8 @@
       <c r="H1" s="78" t="s">
         <v>286</v>
       </c>
-      <c r="I1" s="78" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>242</v>
       </c>
@@ -10478,7 +10470,7 @@
         <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E2">
         <v>2030</v>
@@ -10487,16 +10479,13 @@
         <v>1200</v>
       </c>
       <c r="G2">
-        <v>8.7790000000000003E-3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>242</v>
       </c>
@@ -10507,7 +10496,7 @@
         <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E3">
         <v>2030</v>
@@ -10516,16 +10505,13 @@
         <v>1200</v>
       </c>
       <c r="G3">
-        <v>8.7790000000000003E-3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
         <v>0.01</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>242</v>
       </c>
@@ -10536,7 +10522,7 @@
         <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E4">
         <v>2030</v>
@@ -10545,16 +10531,13 @@
         <v>7500</v>
       </c>
       <c r="G4">
-        <v>2.134E-3</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
         <v>0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>242</v>
       </c>
@@ -10565,7 +10548,7 @@
         <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E5">
         <v>2030</v>
@@ -10574,16 +10557,13 @@
         <v>7500</v>
       </c>
       <c r="G5">
-        <v>2.134E-3</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>242</v>
       </c>
@@ -10594,7 +10574,7 @@
         <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E6">
         <v>2030</v>
@@ -10603,16 +10583,13 @@
         <v>1000</v>
       </c>
       <c r="G6">
-        <v>9.5930000000000008E-3</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>242</v>
       </c>
@@ -10623,7 +10600,7 @@
         <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E7">
         <v>2030</v>
@@ -10632,16 +10609,13 @@
         <v>1000</v>
       </c>
       <c r="G7">
-        <v>9.5930000000000008E-3</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>242</v>
       </c>
@@ -10652,7 +10626,7 @@
         <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E8">
         <v>2030</v>
@@ -10661,16 +10635,13 @@
         <v>2800</v>
       </c>
       <c r="G8">
-        <v>4.0200000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
         <v>0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>242</v>
       </c>
@@ -10681,7 +10652,7 @@
         <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E9">
         <v>2030</v>
@@ -10690,16 +10661,13 @@
         <v>4300</v>
       </c>
       <c r="G9">
-        <v>2.6180000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>242</v>
       </c>
@@ -10710,7 +10678,7 @@
         <v>126</v>
       </c>
       <c r="D10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E10">
         <v>2030</v>
@@ -10719,16 +10687,13 @@
         <v>3400</v>
       </c>
       <c r="G10">
-        <v>4.6319999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>242</v>
       </c>
@@ -10739,7 +10704,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E11">
         <v>2030</v>
@@ -10748,16 +10713,13 @@
         <v>3400</v>
       </c>
       <c r="G11">
-        <v>4.6319999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>242</v>
       </c>
@@ -10768,7 +10730,7 @@
         <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E12">
         <v>2030</v>
@@ -10777,16 +10739,13 @@
         <v>2400</v>
       </c>
       <c r="G12">
-        <v>8.4419999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>242</v>
       </c>
@@ -10797,7 +10756,7 @@
         <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E13">
         <v>2030</v>
@@ -10806,16 +10765,13 @@
         <v>2400</v>
       </c>
       <c r="G13">
-        <v>8.4419999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>242</v>
       </c>
@@ -10826,7 +10782,7 @@
         <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E14">
         <v>2030</v>
@@ -10835,16 +10791,13 @@
         <v>4200</v>
       </c>
       <c r="G14">
-        <v>5.7710000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>242</v>
       </c>
@@ -10855,7 +10808,7 @@
         <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E15">
         <v>2030</v>
@@ -10864,16 +10817,13 @@
         <v>4400</v>
       </c>
       <c r="G15">
-        <v>5.509E-3</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>242</v>
       </c>
@@ -10884,7 +10834,7 @@
         <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E16">
         <v>2030</v>
@@ -10893,16 +10843,13 @@
         <v>2200</v>
       </c>
       <c r="G16">
-        <v>7.3699999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
         <v>0.01</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>242</v>
       </c>
@@ -10913,7 +10860,7 @@
         <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E17">
         <v>2030</v>
@@ -10922,16 +10869,13 @@
         <v>4500</v>
       </c>
       <c r="G17">
-        <v>3.6029999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
         <v>0.01</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>242</v>
       </c>
@@ -10942,7 +10886,7 @@
         <v>118</v>
       </c>
       <c r="D18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E18">
         <v>2030</v>
@@ -10951,16 +10895,13 @@
         <v>2200</v>
       </c>
       <c r="G18">
-        <v>5.143E-3</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
         <v>0.01</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>242</v>
       </c>
@@ -10971,7 +10912,7 @@
         <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E19">
         <v>2030</v>
@@ -10980,16 +10921,13 @@
         <v>3000</v>
       </c>
       <c r="G19">
-        <v>3.7720000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
         <v>0.01</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>242</v>
       </c>
@@ -11000,7 +10938,7 @@
         <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E20">
         <v>2030</v>
@@ -11009,16 +10947,13 @@
         <v>3500</v>
       </c>
       <c r="G20">
-        <v>4.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
         <v>0.01</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>242</v>
       </c>
@@ -11029,7 +10964,7 @@
         <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E21">
         <v>2030</v>
@@ -11038,16 +10973,13 @@
         <v>3500</v>
       </c>
       <c r="G21">
-        <v>4.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21">
         <v>0.01</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>242</v>
       </c>
@@ -11058,7 +10990,7 @@
         <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E22">
         <v>2030</v>
@@ -11067,16 +10999,13 @@
         <v>4800</v>
       </c>
       <c r="G22">
-        <v>4.2189999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
         <v>0.01</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>242</v>
       </c>
@@ -11087,7 +11016,7 @@
         <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E23">
         <v>2030</v>
@@ -11096,16 +11025,13 @@
         <v>4800</v>
       </c>
       <c r="G23">
-        <v>4.2189999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
         <v>0.01</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>242</v>
       </c>
@@ -11116,7 +11042,7 @@
         <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E24">
         <v>2030</v>
@@ -11125,16 +11051,13 @@
         <v>5000</v>
       </c>
       <c r="G24">
-        <v>2.7590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
         <v>0.01</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>242</v>
       </c>
@@ -11145,7 +11068,7 @@
         <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E25">
         <v>2030</v>
@@ -11154,16 +11077,13 @@
         <v>5000</v>
       </c>
       <c r="G25">
-        <v>2.7590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
         <v>0.01</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>242</v>
       </c>
@@ -11174,7 +11094,7 @@
         <v>129</v>
       </c>
       <c r="D26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E26">
         <v>2030</v>
@@ -11183,16 +11103,13 @@
         <v>1400</v>
       </c>
       <c r="G26">
-        <v>3.571E-3</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
         <v>0.01</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>242</v>
       </c>
@@ -11203,7 +11120,7 @@
         <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E27">
         <v>2030</v>
@@ -11212,16 +11129,13 @@
         <v>1400</v>
       </c>
       <c r="G27">
-        <v>3.571E-3</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
         <v>0.01</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>242</v>
       </c>
@@ -11232,7 +11146,7 @@
         <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E28">
         <v>2030</v>
@@ -11241,16 +11155,13 @@
         <v>2000</v>
       </c>
       <c r="G28">
-        <v>3.388E-3</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28">
         <v>0.01</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>242</v>
       </c>
@@ -11261,7 +11172,7 @@
         <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E29">
         <v>2030</v>
@@ -11270,16 +11181,13 @@
         <v>3000</v>
       </c>
       <c r="G29">
-        <v>2.2590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
         <v>0.01</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>242</v>
       </c>
@@ -11290,7 +11198,7 @@
         <v>134</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E30">
         <v>2030</v>
@@ -11299,16 +11207,13 @@
         <v>1315</v>
       </c>
       <c r="G30">
-        <v>8.1300000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
         <v>0.01</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>242</v>
       </c>
@@ -11319,7 +11224,7 @@
         <v>117</v>
       </c>
       <c r="D31" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E31">
         <v>2030</v>
@@ -11328,16 +11233,13 @@
         <v>1315</v>
       </c>
       <c r="G31">
-        <v>8.1300000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="I31">
         <v>0.01</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>242</v>
       </c>
@@ -11348,7 +11250,7 @@
         <v>135</v>
       </c>
       <c r="D32" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E32">
         <v>2030</v>
@@ -11357,16 +11259,13 @@
         <v>1400</v>
       </c>
       <c r="G32">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32">
         <v>0.01</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>242</v>
       </c>
@@ -11377,7 +11276,7 @@
         <v>117</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E33">
         <v>2030</v>
@@ -11386,16 +11285,13 @@
         <v>1400</v>
       </c>
       <c r="G33">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33">
         <v>0.01</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>242</v>
       </c>
@@ -11406,7 +11302,7 @@
         <v>119</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E34">
         <v>2030</v>
@@ -11415,16 +11311,13 @@
         <v>600</v>
       </c>
       <c r="G34">
-        <v>8.4030000000000007E-3</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="I34">
         <v>0.01</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>242</v>
       </c>
@@ -11435,7 +11328,7 @@
         <v>118</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E35">
         <v>2030</v>
@@ -11444,16 +11337,13 @@
         <v>590</v>
       </c>
       <c r="G35">
-        <v>8.5450000000000005E-3</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35">
         <v>0.01</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>242</v>
       </c>
@@ -11464,7 +11354,7 @@
         <v>130</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E36">
         <v>2030</v>
@@ -11473,16 +11363,13 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
         <v>0.01</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
         <v>242</v>
       </c>
@@ -11493,7 +11380,7 @@
         <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E37">
         <v>2030</v>
@@ -11502,16 +11389,13 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37">
         <v>0.01</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
         <v>242</v>
       </c>
@@ -11522,7 +11406,7 @@
         <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E38">
         <v>2030</v>
@@ -11531,16 +11415,13 @@
         <v>1700</v>
       </c>
       <c r="G38">
-        <v>5.5469999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38">
         <v>0.01</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>242</v>
       </c>
@@ -11551,7 +11432,7 @@
         <v>118</v>
       </c>
       <c r="D39" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E39">
         <v>2030</v>
@@ -11560,16 +11441,13 @@
         <v>1300</v>
       </c>
       <c r="G39">
-        <v>7.254E-3</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39">
         <v>0.01</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>242</v>
       </c>
@@ -11580,7 +11458,7 @@
         <v>126</v>
       </c>
       <c r="D40" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E40">
         <v>2030</v>
@@ -11589,16 +11467,13 @@
         <v>700</v>
       </c>
       <c r="G40">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40">
         <v>0.01</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
         <v>242</v>
       </c>
@@ -11609,7 +11484,7 @@
         <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E41">
         <v>2030</v>
@@ -11618,16 +11493,13 @@
         <v>700</v>
       </c>
       <c r="G41">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41">
         <v>0.01</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
         <v>242</v>
       </c>
@@ -11638,7 +11510,7 @@
         <v>129</v>
       </c>
       <c r="D42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E42">
         <v>2030</v>
@@ -11647,16 +11519,13 @@
         <v>1632</v>
       </c>
       <c r="G42">
-        <v>2.3080000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>1</v>
-      </c>
-      <c r="I42">
         <v>0.01</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
         <v>242</v>
       </c>
@@ -11667,7 +11536,7 @@
         <v>119</v>
       </c>
       <c r="D43" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E43">
         <v>2030</v>
@@ -11676,16 +11545,13 @@
         <v>1632</v>
       </c>
       <c r="G43">
-        <v>2.3080000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43">
         <v>0.01</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
         <v>242</v>
       </c>
@@ -11696,7 +11562,7 @@
         <v>133</v>
       </c>
       <c r="D44" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E44">
         <v>2030</v>
@@ -11705,16 +11571,13 @@
         <v>715</v>
       </c>
       <c r="G44">
-        <v>6.8729999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44">
         <v>0.01</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
         <v>242</v>
       </c>
@@ -11725,7 +11588,7 @@
         <v>119</v>
       </c>
       <c r="D45" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E45">
         <v>2030</v>
@@ -11734,16 +11597,13 @@
         <v>715</v>
       </c>
       <c r="G45">
-        <v>6.8729999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45">
         <v>0.01</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
         <v>242</v>
       </c>
@@ -11754,7 +11614,7 @@
         <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E46">
         <v>2030</v>
@@ -11763,16 +11623,13 @@
         <v>1400</v>
       </c>
       <c r="G46">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46">
         <v>0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
         <v>242</v>
       </c>
@@ -11783,7 +11640,7 @@
         <v>119</v>
       </c>
       <c r="D47" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E47">
         <v>2030</v>
@@ -11792,16 +11649,13 @@
         <v>1400</v>
       </c>
       <c r="G47">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47">
         <v>0.01</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
         <v>242</v>
       </c>
@@ -11812,7 +11666,7 @@
         <v>122</v>
       </c>
       <c r="D48" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E48">
         <v>2030</v>
@@ -11821,16 +11675,13 @@
         <v>1016</v>
       </c>
       <c r="G48">
-        <v>3.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48">
         <v>0.01</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
         <v>242</v>
       </c>
@@ -11841,7 +11692,7 @@
         <v>120</v>
       </c>
       <c r="D49" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E49">
         <v>2030</v>
@@ -11850,16 +11701,13 @@
         <v>1016</v>
       </c>
       <c r="G49">
-        <v>3.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49">
         <v>0.01</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
         <v>242</v>
       </c>
@@ -11870,7 +11718,7 @@
         <v>125</v>
       </c>
       <c r="D50" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E50">
         <v>2030</v>
@@ -11879,16 +11727,13 @@
         <v>950</v>
       </c>
       <c r="G50">
-        <v>3.3059999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50">
         <v>0.01</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
         <v>242</v>
       </c>
@@ -11899,7 +11744,7 @@
         <v>120</v>
       </c>
       <c r="D51" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E51">
         <v>2030</v>
@@ -11908,16 +11753,13 @@
         <v>879</v>
       </c>
       <c r="G51">
-        <v>3.5729999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>1</v>
-      </c>
-      <c r="I51">
         <v>0.01</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
         <v>242</v>
       </c>
@@ -11928,7 +11770,7 @@
         <v>123</v>
       </c>
       <c r="D52" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E52">
         <v>2030</v>
@@ -11937,16 +11779,13 @@
         <v>5000</v>
       </c>
       <c r="G52">
-        <v>4.627E-3</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>1</v>
-      </c>
-      <c r="I52">
         <v>0.01</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
         <v>242</v>
       </c>
@@ -11957,7 +11796,7 @@
         <v>121</v>
       </c>
       <c r="D53" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E53">
         <v>2030</v>
@@ -11966,16 +11805,13 @@
         <v>5000</v>
       </c>
       <c r="G53">
-        <v>4.627E-3</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>1</v>
-      </c>
-      <c r="I53">
         <v>0.01</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
         <v>242</v>
       </c>
@@ -11986,7 +11822,7 @@
         <v>128</v>
       </c>
       <c r="D54" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E54">
         <v>2030</v>
@@ -11995,16 +11831,13 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>1</v>
-      </c>
-      <c r="I54">
         <v>0.01</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
         <v>242</v>
       </c>
@@ -12015,7 +11848,7 @@
         <v>122</v>
       </c>
       <c r="D55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E55">
         <v>2030</v>
@@ -12024,16 +11857,13 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>1</v>
-      </c>
-      <c r="I55">
         <v>0.01</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
         <v>242</v>
       </c>
@@ -12044,7 +11874,7 @@
         <v>131</v>
       </c>
       <c r="D56" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E56">
         <v>2030</v>
@@ -12053,16 +11883,13 @@
         <v>2000</v>
       </c>
       <c r="G56">
-        <v>2.9039999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>1</v>
-      </c>
-      <c r="I56">
         <v>0.01</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
         <v>242</v>
       </c>
@@ -12073,7 +11900,7 @@
         <v>122</v>
       </c>
       <c r="D57" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E57">
         <v>2030</v>
@@ -12082,16 +11909,13 @@
         <v>2000</v>
       </c>
       <c r="G57">
-        <v>2.9039999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>1</v>
-      </c>
-      <c r="I57">
         <v>0.01</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
         <v>242</v>
       </c>
@@ -12102,7 +11926,7 @@
         <v>133</v>
       </c>
       <c r="D58" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E58">
         <v>2030</v>
@@ -12111,16 +11935,13 @@
         <v>1200</v>
       </c>
       <c r="G58">
-        <v>4.1539999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>1</v>
-      </c>
-      <c r="I58">
         <v>0.01</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
         <v>242</v>
       </c>
@@ -12131,7 +11952,7 @@
         <v>122</v>
       </c>
       <c r="D59" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E59">
         <v>2030</v>
@@ -12140,16 +11961,13 @@
         <v>1200</v>
       </c>
       <c r="G59">
-        <v>4.1539999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>1</v>
-      </c>
-      <c r="I59">
         <v>0.01</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
         <v>242</v>
       </c>
@@ -12160,7 +11978,7 @@
         <v>135</v>
       </c>
       <c r="D60" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E60">
         <v>2030</v>
@@ -12169,16 +11987,13 @@
         <v>5600</v>
       </c>
       <c r="G60">
-        <v>4.3889999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>1</v>
-      </c>
-      <c r="I60">
         <v>0.01</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
         <v>242</v>
       </c>
@@ -12189,7 +12004,7 @@
         <v>123</v>
       </c>
       <c r="D61" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E61">
         <v>2030</v>
@@ -12198,16 +12013,13 @@
         <v>5600</v>
       </c>
       <c r="G61">
-        <v>4.3889999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>1</v>
-      </c>
-      <c r="I61">
         <v>0.01</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
         <v>242</v>
       </c>
@@ -12218,7 +12030,7 @@
         <v>125</v>
       </c>
       <c r="D62" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E62">
         <v>2030</v>
@@ -12227,16 +12039,13 @@
         <v>950</v>
       </c>
       <c r="G62">
-        <v>3.3210000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>1</v>
-      </c>
-      <c r="I62">
         <v>0.01</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
         <v>242</v>
       </c>
@@ -12247,7 +12056,7 @@
         <v>124</v>
       </c>
       <c r="D63" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E63">
         <v>2030</v>
@@ -12256,16 +12065,13 @@
         <v>950</v>
       </c>
       <c r="G63">
-        <v>3.3210000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>1</v>
-      </c>
-      <c r="I63">
         <v>0.01</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
         <v>242</v>
       </c>
@@ -12276,7 +12082,7 @@
         <v>130</v>
       </c>
       <c r="D64" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E64">
         <v>2030</v>
@@ -12285,16 +12091,13 @@
         <v>700</v>
       </c>
       <c r="G64">
-        <v>8.796E-3</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>1</v>
-      </c>
-      <c r="I64">
         <v>0.01</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
         <v>242</v>
       </c>
@@ -12305,7 +12108,7 @@
         <v>124</v>
       </c>
       <c r="D65" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E65">
         <v>2030</v>
@@ -12314,16 +12117,13 @@
         <v>700</v>
       </c>
       <c r="G65">
-        <v>8.796E-3</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>1</v>
-      </c>
-      <c r="I65">
         <v>0.01</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
         <v>242</v>
       </c>
@@ -12334,7 +12134,7 @@
         <v>134</v>
       </c>
       <c r="D66" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E66">
         <v>2030</v>
@@ -12343,16 +12143,13 @@
         <v>700</v>
       </c>
       <c r="G66">
-        <v>4.8089999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>1</v>
-      </c>
-      <c r="I66">
         <v>0.01</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
         <v>242</v>
       </c>
@@ -12363,7 +12160,7 @@
         <v>124</v>
       </c>
       <c r="D67" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E67">
         <v>2030</v>
@@ -12372,16 +12169,13 @@
         <v>700</v>
       </c>
       <c r="G67">
-        <v>4.8089999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>1</v>
-      </c>
-      <c r="I67">
         <v>0.01</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
         <v>242</v>
       </c>
@@ -12392,7 +12186,7 @@
         <v>129</v>
       </c>
       <c r="D68" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E68">
         <v>2030</v>
@@ -12401,16 +12195,13 @@
         <v>700</v>
       </c>
       <c r="G68">
-        <v>3.813E-3</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>1</v>
-      </c>
-      <c r="I68">
         <v>0.01</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
         <v>242</v>
       </c>
@@ -12421,7 +12212,7 @@
         <v>126</v>
       </c>
       <c r="D69" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E69">
         <v>2030</v>
@@ -12430,16 +12221,13 @@
         <v>700</v>
       </c>
       <c r="G69">
-        <v>3.813E-3</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>1</v>
-      </c>
-      <c r="I69">
         <v>0.01</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
         <v>242</v>
       </c>
@@ -12450,7 +12238,7 @@
         <v>135</v>
       </c>
       <c r="D70" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E70">
         <v>2030</v>
@@ -12459,16 +12247,13 @@
         <v>2800</v>
       </c>
       <c r="G70">
-        <v>9.7680000000000006E-3</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>1</v>
-      </c>
-      <c r="I70">
         <v>0.01</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
         <v>242</v>
       </c>
@@ -12479,7 +12264,7 @@
         <v>126</v>
       </c>
       <c r="D71" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E71">
         <v>2030</v>
@@ -12488,16 +12273,13 @@
         <v>2800</v>
       </c>
       <c r="G71">
-        <v>9.7680000000000006E-3</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>1</v>
-      </c>
-      <c r="I71">
         <v>0.01</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
         <v>242</v>
       </c>
@@ -12508,7 +12290,7 @@
         <v>128</v>
       </c>
       <c r="D72" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E72">
         <v>2030</v>
@@ -12517,16 +12299,13 @@
         <v>350</v>
       </c>
       <c r="G72">
-        <v>2.5279999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>1</v>
-      </c>
-      <c r="I72">
         <v>0.01</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
         <v>242</v>
       </c>
@@ -12537,7 +12316,7 @@
         <v>127</v>
       </c>
       <c r="D73" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E73">
         <v>2030</v>
@@ -12546,16 +12325,13 @@
         <v>1300</v>
       </c>
       <c r="G73">
-        <v>6.8099999999999996E-4</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>1</v>
-      </c>
-      <c r="I73">
         <v>0.01</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
         <v>242</v>
       </c>
@@ -12566,7 +12342,7 @@
         <v>129</v>
       </c>
       <c r="D74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E74">
         <v>2030</v>
@@ -12575,16 +12351,13 @@
         <v>800</v>
       </c>
       <c r="G74">
-        <v>1.603E-3</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>1</v>
-      </c>
-      <c r="I74">
         <v>0.01</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
         <v>242</v>
       </c>
@@ -12595,7 +12368,7 @@
         <v>127</v>
       </c>
       <c r="D75" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E75">
         <v>2030</v>
@@ -12604,16 +12377,13 @@
         <v>600</v>
       </c>
       <c r="G75">
-        <v>2.137E-3</v>
+        <v>1</v>
       </c>
       <c r="H75">
-        <v>1</v>
-      </c>
-      <c r="I75">
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
         <v>242</v>
       </c>
@@ -12624,7 +12394,7 @@
         <v>132</v>
       </c>
       <c r="D76" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E76">
         <v>2030</v>
@@ -12633,16 +12403,13 @@
         <v>600</v>
       </c>
       <c r="G76">
-        <v>3.9880000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>1</v>
-      </c>
-      <c r="I76">
         <v>0.01</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
         <v>242</v>
       </c>
@@ -12653,7 +12420,7 @@
         <v>127</v>
       </c>
       <c r="D77" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E77">
         <v>2030</v>
@@ -12662,16 +12429,13 @@
         <v>1000</v>
       </c>
       <c r="G77">
-        <v>2.3930000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>1</v>
-      </c>
-      <c r="I77">
         <v>0.01</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
         <v>242</v>
       </c>
@@ -12682,7 +12446,7 @@
         <v>131</v>
       </c>
       <c r="D78" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E78">
         <v>2030</v>
@@ -12691,16 +12455,13 @@
         <v>700</v>
       </c>
       <c r="G78">
-        <v>4.3309999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H78">
-        <v>1</v>
-      </c>
-      <c r="I78">
         <v>0.01</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:8">
       <c r="A79" t="s">
         <v>242</v>
       </c>
@@ -12711,7 +12472,7 @@
         <v>128</v>
       </c>
       <c r="D79" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E79">
         <v>2030</v>
@@ -12720,16 +12481,13 @@
         <v>600</v>
       </c>
       <c r="G79">
-        <v>5.0530000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>1</v>
-      </c>
-      <c r="I79">
         <v>0.01</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:8">
       <c r="A80" t="s">
         <v>242</v>
       </c>
@@ -12740,7 +12498,7 @@
         <v>132</v>
       </c>
       <c r="D80" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E80">
         <v>2030</v>
@@ -12749,16 +12507,13 @@
         <v>250</v>
       </c>
       <c r="G80">
-        <v>3.2550000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>1</v>
-      </c>
-      <c r="I80">
         <v>0.01</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:8">
       <c r="A81" t="s">
         <v>242</v>
       </c>
@@ -12769,7 +12524,7 @@
         <v>128</v>
       </c>
       <c r="D81" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E81">
         <v>2030</v>
@@ -12778,16 +12533,13 @@
         <v>300</v>
       </c>
       <c r="G81">
-        <v>2.7130000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H81">
-        <v>1</v>
-      </c>
-      <c r="I81">
         <v>0.01</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:8">
       <c r="A82" t="s">
         <v>242</v>
       </c>
@@ -12798,7 +12550,7 @@
         <v>133</v>
       </c>
       <c r="D82" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E82">
         <v>2030</v>
@@ -12807,16 +12559,13 @@
         <v>2145</v>
       </c>
       <c r="G82">
-        <v>4.248E-3</v>
+        <v>1</v>
       </c>
       <c r="H82">
-        <v>1</v>
-      </c>
-      <c r="I82">
         <v>0.01</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:8">
       <c r="A83" t="s">
         <v>242</v>
       </c>
@@ -12827,7 +12576,7 @@
         <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E83">
         <v>2030</v>
@@ -12836,16 +12585,13 @@
         <v>2095</v>
       </c>
       <c r="G83">
-        <v>4.3489999999999996E-3</v>
+        <v>1</v>
       </c>
       <c r="H83">
-        <v>1</v>
-      </c>
-      <c r="I83">
         <v>0.01</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:8">
       <c r="A84" t="s">
         <v>242</v>
       </c>
@@ -12856,7 +12602,7 @@
         <v>135</v>
       </c>
       <c r="D84" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E84">
         <v>2030</v>
@@ -12865,16 +12611,13 @@
         <v>1400</v>
       </c>
       <c r="G84">
-        <v>2.7680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H84">
-        <v>1</v>
-      </c>
-      <c r="I84">
         <v>0.01</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:8">
       <c r="A85" t="s">
         <v>242</v>
       </c>
@@ -12885,7 +12628,7 @@
         <v>129</v>
       </c>
       <c r="D85" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E85">
         <v>2030</v>
@@ -12894,16 +12637,13 @@
         <v>1400</v>
       </c>
       <c r="G85">
-        <v>2.7680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H85">
-        <v>1</v>
-      </c>
-      <c r="I85">
         <v>0.01</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
         <v>242</v>
       </c>
@@ -12914,7 +12654,7 @@
         <v>134</v>
       </c>
       <c r="D86" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E86">
         <v>2030</v>
@@ -12923,16 +12663,13 @@
         <v>600</v>
       </c>
       <c r="G86">
-        <v>8.3330000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H86">
-        <v>1</v>
-      </c>
-      <c r="I86">
         <v>0.01</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:8">
       <c r="A87" t="s">
         <v>242</v>
       </c>
@@ -12943,7 +12680,7 @@
         <v>130</v>
       </c>
       <c r="D87" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E87">
         <v>2030</v>
@@ -12952,16 +12689,13 @@
         <v>600</v>
       </c>
       <c r="G87">
-        <v>8.3330000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H87">
-        <v>1</v>
-      </c>
-      <c r="I87">
         <v>0.01</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:8">
       <c r="A88" t="s">
         <v>242</v>
       </c>
@@ -12972,7 +12706,7 @@
         <v>132</v>
       </c>
       <c r="D88" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E88">
         <v>2030</v>
@@ -12981,16 +12715,13 @@
         <v>3300</v>
       </c>
       <c r="G88">
-        <v>2.1359999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H88">
-        <v>1</v>
-      </c>
-      <c r="I88">
         <v>0.01</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:8">
       <c r="A89" t="s">
         <v>242</v>
       </c>
@@ -13001,7 +12732,7 @@
         <v>131</v>
       </c>
       <c r="D89" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E89">
         <v>2030</v>
@@ -13010,16 +12741,13 @@
         <v>3300</v>
       </c>
       <c r="G89">
-        <v>2.1359999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H89">
-        <v>1</v>
-      </c>
-      <c r="I89">
         <v>0.01</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:8">
       <c r="A90" t="s">
         <v>242</v>
       </c>
@@ -13030,7 +12758,7 @@
         <v>133</v>
       </c>
       <c r="D90" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E90">
         <v>2030</v>
@@ -13039,16 +12767,13 @@
         <v>7300</v>
       </c>
       <c r="G90">
-        <v>1.8680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H90">
-        <v>1</v>
-      </c>
-      <c r="I90">
         <v>0.01</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:8">
       <c r="A91" t="s">
         <v>242</v>
       </c>
@@ -13059,7 +12784,7 @@
         <v>132</v>
       </c>
       <c r="D91" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E91">
         <v>2030</v>
@@ -13068,16 +12793,13 @@
         <v>7300</v>
       </c>
       <c r="G91">
-        <v>1.8680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>1</v>
-      </c>
-      <c r="I91">
         <v>0.01</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:8">
       <c r="A92" t="s">
         <v>242</v>
       </c>
@@ -13088,7 +12810,7 @@
         <v>134</v>
       </c>
       <c r="D92" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E92">
         <v>2030</v>
@@ -13097,16 +12819,13 @@
         <v>6200</v>
       </c>
       <c r="G92">
-        <v>2.679E-3</v>
+        <v>1</v>
       </c>
       <c r="H92">
-        <v>1</v>
-      </c>
-      <c r="I92">
         <v>0.01</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:8">
       <c r="A93" t="s">
         <v>242</v>
       </c>
@@ -13117,7 +12836,7 @@
         <v>133</v>
       </c>
       <c r="D93" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E93">
         <v>2030</v>
@@ -13126,16 +12845,13 @@
         <v>2800</v>
       </c>
       <c r="G93">
-        <v>5.9319999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H93">
-        <v>1</v>
-      </c>
-      <c r="I93">
         <v>0.01</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:8">
       <c r="A94" t="s">
         <v>242</v>
       </c>
@@ -13146,7 +12862,7 @@
         <v>116</v>
       </c>
       <c r="D94" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E94">
         <v>2040</v>
@@ -13155,16 +12871,13 @@
         <v>1200</v>
       </c>
       <c r="G94">
-        <v>8.7790000000000003E-3</v>
+        <v>1</v>
       </c>
       <c r="H94">
-        <v>1</v>
-      </c>
-      <c r="I94">
         <v>0.01</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:8">
       <c r="A95" t="s">
         <v>242</v>
       </c>
@@ -13175,7 +12888,7 @@
         <v>111</v>
       </c>
       <c r="D95" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E95">
         <v>2040</v>
@@ -13184,16 +12897,13 @@
         <v>1200</v>
       </c>
       <c r="G95">
-        <v>8.7790000000000003E-3</v>
+        <v>1</v>
       </c>
       <c r="H95">
-        <v>1</v>
-      </c>
-      <c r="I95">
         <v>0.01</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:8">
       <c r="A96" t="s">
         <v>242</v>
       </c>
@@ -13204,7 +12914,7 @@
         <v>117</v>
       </c>
       <c r="D96" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E96">
         <v>2040</v>
@@ -13213,16 +12923,13 @@
         <v>7500</v>
       </c>
       <c r="G96">
-        <v>2.134E-3</v>
+        <v>1</v>
       </c>
       <c r="H96">
-        <v>1</v>
-      </c>
-      <c r="I96">
         <v>0.01</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>242</v>
       </c>
@@ -13233,7 +12940,7 @@
         <v>111</v>
       </c>
       <c r="D97" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E97">
         <v>2040</v>
@@ -13242,16 +12949,13 @@
         <v>7500</v>
       </c>
       <c r="G97">
-        <v>2.134E-3</v>
+        <v>1</v>
       </c>
       <c r="H97">
-        <v>1</v>
-      </c>
-      <c r="I97">
         <v>0.01</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:8">
       <c r="A98" t="s">
         <v>242</v>
       </c>
@@ -13262,7 +12966,7 @@
         <v>117</v>
       </c>
       <c r="D98" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E98">
         <v>2040</v>
@@ -13271,16 +12975,13 @@
         <v>1000</v>
       </c>
       <c r="G98">
-        <v>9.5930000000000008E-3</v>
+        <v>1</v>
       </c>
       <c r="H98">
-        <v>1</v>
-      </c>
-      <c r="I98">
         <v>0.01</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:8">
       <c r="A99" t="s">
         <v>242</v>
       </c>
@@ -13291,7 +12992,7 @@
         <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E99">
         <v>2040</v>
@@ -13300,16 +13001,13 @@
         <v>1000</v>
       </c>
       <c r="G99">
-        <v>9.5930000000000008E-3</v>
+        <v>1</v>
       </c>
       <c r="H99">
-        <v>1</v>
-      </c>
-      <c r="I99">
         <v>0.01</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:8">
       <c r="A100" t="s">
         <v>242</v>
       </c>
@@ -13320,7 +13018,7 @@
         <v>123</v>
       </c>
       <c r="D100" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E100">
         <v>2040</v>
@@ -13329,16 +13027,13 @@
         <v>3800</v>
       </c>
       <c r="G100">
-        <v>4.0200000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H100">
-        <v>1</v>
-      </c>
-      <c r="I100">
         <v>0.01</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:8">
       <c r="A101" t="s">
         <v>242</v>
       </c>
@@ -13349,7 +13044,7 @@
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E101">
         <v>2040</v>
@@ -13358,16 +13053,13 @@
         <v>5300</v>
       </c>
       <c r="G101">
-        <v>2.882E-3</v>
+        <v>1</v>
       </c>
       <c r="H101">
-        <v>1</v>
-      </c>
-      <c r="I101">
         <v>0.01</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:8">
       <c r="A102" t="s">
         <v>242</v>
       </c>
@@ -13378,7 +13070,7 @@
         <v>126</v>
       </c>
       <c r="D102" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E102">
         <v>2040</v>
@@ -13387,16 +13079,13 @@
         <v>5400</v>
       </c>
       <c r="G102">
-        <v>4.6319999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H102">
-        <v>1</v>
-      </c>
-      <c r="I102">
         <v>0.01</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:8">
       <c r="A103" t="s">
         <v>242</v>
       </c>
@@ -13407,7 +13096,7 @@
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E103">
         <v>2040</v>
@@ -13416,16 +13105,13 @@
         <v>4400</v>
       </c>
       <c r="G103">
-        <v>5.6849999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H103">
-        <v>1</v>
-      </c>
-      <c r="I103">
         <v>0.01</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:8">
       <c r="A104" t="s">
         <v>242</v>
       </c>
@@ -13436,7 +13122,7 @@
         <v>135</v>
       </c>
       <c r="D104" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E104">
         <v>2040</v>
@@ -13445,16 +13131,13 @@
         <v>4800</v>
       </c>
       <c r="G104">
-        <v>8.4419999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H104">
-        <v>1</v>
-      </c>
-      <c r="I104">
         <v>0.01</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
         <v>242</v>
       </c>
@@ -13465,7 +13148,7 @@
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E105">
         <v>2040</v>
@@ -13474,16 +13157,13 @@
         <v>4800</v>
       </c>
       <c r="G105">
-        <v>8.4419999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H105">
-        <v>1</v>
-      </c>
-      <c r="I105">
         <v>0.01</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
         <v>242</v>
       </c>
@@ -13494,7 +13174,7 @@
         <v>117</v>
       </c>
       <c r="D106" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E106">
         <v>2040</v>
@@ -13503,16 +13183,13 @@
         <v>4500</v>
       </c>
       <c r="G106">
-        <v>5.7710000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H106">
-        <v>1</v>
-      </c>
-      <c r="I106">
         <v>0.01</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:8">
       <c r="A107" t="s">
         <v>242</v>
       </c>
@@ -13523,7 +13200,7 @@
         <v>116</v>
       </c>
       <c r="D107" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E107">
         <v>2040</v>
@@ -13532,16 +13209,13 @@
         <v>5000</v>
       </c>
       <c r="G107">
-        <v>5.1939999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H107">
-        <v>1</v>
-      </c>
-      <c r="I107">
         <v>0.01</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:8">
       <c r="A108" t="s">
         <v>242</v>
       </c>
@@ -13552,7 +13226,7 @@
         <v>123</v>
       </c>
       <c r="D108" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E108">
         <v>2040</v>
@@ -13561,16 +13235,13 @@
         <v>2200</v>
       </c>
       <c r="G108">
-        <v>7.3699999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H108">
-        <v>1</v>
-      </c>
-      <c r="I108">
         <v>0.01</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:8">
       <c r="A109" t="s">
         <v>242</v>
       </c>
@@ -13581,7 +13252,7 @@
         <v>116</v>
       </c>
       <c r="D109" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E109">
         <v>2040</v>
@@ -13590,16 +13261,13 @@
         <v>4500</v>
       </c>
       <c r="G109">
-        <v>3.6029999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H109">
-        <v>1</v>
-      </c>
-      <c r="I109">
         <v>0.01</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:8">
       <c r="A110" t="s">
         <v>242</v>
       </c>
@@ -13610,7 +13278,7 @@
         <v>118</v>
       </c>
       <c r="D110" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E110">
         <v>2040</v>
@@ -13619,16 +13287,13 @@
         <v>2200</v>
       </c>
       <c r="G110">
-        <v>5.143E-3</v>
+        <v>1</v>
       </c>
       <c r="H110">
-        <v>1</v>
-      </c>
-      <c r="I110">
         <v>0.01</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:8">
       <c r="A111" t="s">
         <v>242</v>
       </c>
@@ -13639,7 +13304,7 @@
         <v>117</v>
       </c>
       <c r="D111" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E111">
         <v>2040</v>
@@ -13648,16 +13313,13 @@
         <v>3000</v>
       </c>
       <c r="G111">
-        <v>3.7720000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H111">
-        <v>1</v>
-      </c>
-      <c r="I111">
         <v>0.01</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:8">
       <c r="A112" t="s">
         <v>242</v>
       </c>
@@ -13668,7 +13330,7 @@
         <v>119</v>
       </c>
       <c r="D112" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E112">
         <v>2040</v>
@@ -13677,16 +13339,13 @@
         <v>3500</v>
       </c>
       <c r="G112">
-        <v>4.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H112">
-        <v>1</v>
-      </c>
-      <c r="I112">
         <v>0.01</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:8">
       <c r="A113" t="s">
         <v>242</v>
       </c>
@@ -13697,7 +13356,7 @@
         <v>117</v>
       </c>
       <c r="D113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E113">
         <v>2040</v>
@@ -13706,16 +13365,13 @@
         <v>3500</v>
       </c>
       <c r="G113">
-        <v>4.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H113">
-        <v>1</v>
-      </c>
-      <c r="I113">
         <v>0.01</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:8">
       <c r="A114" t="s">
         <v>242</v>
       </c>
@@ -13726,7 +13382,7 @@
         <v>123</v>
       </c>
       <c r="D114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E114">
         <v>2040</v>
@@ -13735,16 +13391,13 @@
         <v>4800</v>
       </c>
       <c r="G114">
-        <v>4.2189999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H114">
-        <v>1</v>
-      </c>
-      <c r="I114">
         <v>0.01</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:8">
       <c r="A115" t="s">
         <v>242</v>
       </c>
@@ -13755,7 +13408,7 @@
         <v>117</v>
       </c>
       <c r="D115" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E115">
         <v>2040</v>
@@ -13764,16 +13417,13 @@
         <v>4800</v>
       </c>
       <c r="G115">
-        <v>4.2189999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H115">
-        <v>1</v>
-      </c>
-      <c r="I115">
         <v>0.01</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:8">
       <c r="A116" t="s">
         <v>242</v>
       </c>
@@ -13784,7 +13434,7 @@
         <v>126</v>
       </c>
       <c r="D116" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E116">
         <v>2040</v>
@@ -13793,16 +13443,13 @@
         <v>5000</v>
       </c>
       <c r="G116">
-        <v>2.7590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H116">
-        <v>1</v>
-      </c>
-      <c r="I116">
         <v>0.01</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:8">
       <c r="A117" t="s">
         <v>242</v>
       </c>
@@ -13813,7 +13460,7 @@
         <v>117</v>
       </c>
       <c r="D117" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E117">
         <v>2040</v>
@@ -13822,16 +13469,13 @@
         <v>5000</v>
       </c>
       <c r="G117">
-        <v>2.7590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H117">
-        <v>1</v>
-      </c>
-      <c r="I117">
         <v>0.01</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:8">
       <c r="A118" t="s">
         <v>242</v>
       </c>
@@ -13842,7 +13486,7 @@
         <v>129</v>
       </c>
       <c r="D118" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E118">
         <v>2040</v>
@@ -13851,16 +13495,13 @@
         <v>1400</v>
       </c>
       <c r="G118">
-        <v>3.571E-3</v>
+        <v>1</v>
       </c>
       <c r="H118">
-        <v>1</v>
-      </c>
-      <c r="I118">
         <v>0.01</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:8">
       <c r="A119" t="s">
         <v>242</v>
       </c>
@@ -13871,7 +13512,7 @@
         <v>117</v>
       </c>
       <c r="D119" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E119">
         <v>2040</v>
@@ -13880,16 +13521,13 @@
         <v>1400</v>
       </c>
       <c r="G119">
-        <v>3.571E-3</v>
+        <v>1</v>
       </c>
       <c r="H119">
-        <v>1</v>
-      </c>
-      <c r="I119">
         <v>0.01</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:8">
       <c r="A120" t="s">
         <v>242</v>
       </c>
@@ -13900,7 +13538,7 @@
         <v>130</v>
       </c>
       <c r="D120" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E120">
         <v>2040</v>
@@ -13909,16 +13547,13 @@
         <v>2000</v>
       </c>
       <c r="G120">
-        <v>3.388E-3</v>
+        <v>1</v>
       </c>
       <c r="H120">
-        <v>1</v>
-      </c>
-      <c r="I120">
         <v>0.01</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:8">
       <c r="A121" t="s">
         <v>242</v>
       </c>
@@ -13929,7 +13564,7 @@
         <v>117</v>
       </c>
       <c r="D121" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E121">
         <v>2040</v>
@@ -13938,16 +13573,13 @@
         <v>3000</v>
       </c>
       <c r="G121">
-        <v>2.2590000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H121">
-        <v>1</v>
-      </c>
-      <c r="I121">
         <v>0.01</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:8">
       <c r="A122" t="s">
         <v>242</v>
       </c>
@@ -13958,7 +13590,7 @@
         <v>134</v>
       </c>
       <c r="D122" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E122">
         <v>2040</v>
@@ -13967,16 +13599,13 @@
         <v>2015</v>
       </c>
       <c r="G122">
-        <v>8.1300000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H122">
-        <v>1</v>
-      </c>
-      <c r="I122">
         <v>0.01</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:8">
       <c r="A123" t="s">
         <v>242</v>
       </c>
@@ -13987,7 +13616,7 @@
         <v>117</v>
       </c>
       <c r="D123" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E123">
         <v>2040</v>
@@ -13996,16 +13625,13 @@
         <v>2015</v>
       </c>
       <c r="G123">
-        <v>8.1300000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H123">
-        <v>1</v>
-      </c>
-      <c r="I123">
         <v>0.01</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:8">
       <c r="A124" t="s">
         <v>242</v>
       </c>
@@ -14016,7 +13642,7 @@
         <v>135</v>
       </c>
       <c r="D124" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E124">
         <v>2040</v>
@@ -14025,16 +13651,13 @@
         <v>2800</v>
       </c>
       <c r="G124">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H124">
-        <v>1</v>
-      </c>
-      <c r="I124">
         <v>0.01</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:8">
       <c r="A125" t="s">
         <v>242</v>
       </c>
@@ -14045,7 +13668,7 @@
         <v>117</v>
       </c>
       <c r="D125" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E125">
         <v>2040</v>
@@ -14054,16 +13677,13 @@
         <v>2800</v>
       </c>
       <c r="G125">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H125">
-        <v>1</v>
-      </c>
-      <c r="I125">
         <v>0.01</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:8">
       <c r="A126" t="s">
         <v>242</v>
       </c>
@@ -14074,7 +13694,7 @@
         <v>119</v>
       </c>
       <c r="D126" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E126">
         <v>2040</v>
@@ -14083,16 +13703,13 @@
         <v>600</v>
       </c>
       <c r="G126">
-        <v>8.4030000000000007E-3</v>
+        <v>1</v>
       </c>
       <c r="H126">
-        <v>1</v>
-      </c>
-      <c r="I126">
         <v>0.01</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:8">
       <c r="A127" t="s">
         <v>242</v>
       </c>
@@ -14103,7 +13720,7 @@
         <v>118</v>
       </c>
       <c r="D127" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E127">
         <v>2040</v>
@@ -14112,16 +13729,13 @@
         <v>590</v>
       </c>
       <c r="G127">
-        <v>8.5450000000000005E-3</v>
+        <v>1</v>
       </c>
       <c r="H127">
-        <v>1</v>
-      </c>
-      <c r="I127">
         <v>0.01</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:8">
       <c r="A128" t="s">
         <v>242</v>
       </c>
@@ -14132,7 +13746,7 @@
         <v>130</v>
       </c>
       <c r="D128" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E128">
         <v>2040</v>
@@ -14141,16 +13755,13 @@
         <v>0</v>
       </c>
       <c r="G128">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H128">
-        <v>1</v>
-      </c>
-      <c r="I128">
         <v>0.01</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:8">
       <c r="A129" t="s">
         <v>242</v>
       </c>
@@ -14161,7 +13772,7 @@
         <v>118</v>
       </c>
       <c r="D129" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E129">
         <v>2040</v>
@@ -14170,16 +13781,13 @@
         <v>0</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129">
-        <v>1</v>
-      </c>
-      <c r="I129">
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:8">
       <c r="A130" t="s">
         <v>242</v>
       </c>
@@ -14190,7 +13798,7 @@
         <v>134</v>
       </c>
       <c r="D130" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E130">
         <v>2040</v>
@@ -14199,16 +13807,13 @@
         <v>1700</v>
       </c>
       <c r="G130">
-        <v>5.5469999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H130">
-        <v>1</v>
-      </c>
-      <c r="I130">
         <v>0.01</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:8">
       <c r="A131" t="s">
         <v>242</v>
       </c>
@@ -14219,7 +13824,7 @@
         <v>118</v>
       </c>
       <c r="D131" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E131">
         <v>2040</v>
@@ -14228,16 +13833,13 @@
         <v>1300</v>
       </c>
       <c r="G131">
-        <v>7.254E-3</v>
+        <v>1</v>
       </c>
       <c r="H131">
-        <v>1</v>
-      </c>
-      <c r="I131">
         <v>0.01</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:8">
       <c r="A132" t="s">
         <v>242</v>
       </c>
@@ -14248,7 +13850,7 @@
         <v>126</v>
       </c>
       <c r="D132" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E132">
         <v>2040</v>
@@ -14257,16 +13859,13 @@
         <v>700</v>
       </c>
       <c r="G132">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H132">
-        <v>1</v>
-      </c>
-      <c r="I132">
         <v>0.01</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:8">
       <c r="A133" t="s">
         <v>242</v>
       </c>
@@ -14277,7 +13876,7 @@
         <v>119</v>
       </c>
       <c r="D133" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E133">
         <v>2040</v>
@@ -14286,16 +13885,13 @@
         <v>700</v>
       </c>
       <c r="G133">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H133">
-        <v>1</v>
-      </c>
-      <c r="I133">
         <v>0.01</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:8">
       <c r="A134" t="s">
         <v>242</v>
       </c>
@@ -14306,7 +13902,7 @@
         <v>129</v>
       </c>
       <c r="D134" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E134">
         <v>2040</v>
@@ -14315,16 +13911,13 @@
         <v>1632</v>
       </c>
       <c r="G134">
-        <v>2.3080000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H134">
-        <v>1</v>
-      </c>
-      <c r="I134">
         <v>0.01</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:8">
       <c r="A135" t="s">
         <v>242</v>
       </c>
@@ -14335,7 +13928,7 @@
         <v>119</v>
       </c>
       <c r="D135" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E135">
         <v>2040</v>
@@ -14344,16 +13937,13 @@
         <v>1632</v>
       </c>
       <c r="G135">
-        <v>2.3080000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H135">
-        <v>1</v>
-      </c>
-      <c r="I135">
         <v>0.01</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:8">
       <c r="A136" t="s">
         <v>242</v>
       </c>
@@ -14364,7 +13954,7 @@
         <v>133</v>
       </c>
       <c r="D136" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E136">
         <v>2040</v>
@@ -14373,16 +13963,13 @@
         <v>715</v>
       </c>
       <c r="G136">
-        <v>6.8729999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H136">
-        <v>1</v>
-      </c>
-      <c r="I136">
         <v>0.01</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:8">
       <c r="A137" t="s">
         <v>242</v>
       </c>
@@ -14393,7 +13980,7 @@
         <v>119</v>
       </c>
       <c r="D137" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E137">
         <v>2040</v>
@@ -14402,16 +13989,13 @@
         <v>715</v>
       </c>
       <c r="G137">
-        <v>6.8729999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H137">
-        <v>1</v>
-      </c>
-      <c r="I137">
         <v>0.01</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:8">
       <c r="A138" t="s">
         <v>242</v>
       </c>
@@ -14422,7 +14006,7 @@
         <v>135</v>
       </c>
       <c r="D138" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E138">
         <v>2040</v>
@@ -14431,16 +14015,13 @@
         <v>2800</v>
       </c>
       <c r="G138">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H138">
-        <v>1</v>
-      </c>
-      <c r="I138">
         <v>0.01</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:8">
       <c r="A139" t="s">
         <v>242</v>
       </c>
@@ -14451,7 +14032,7 @@
         <v>119</v>
       </c>
       <c r="D139" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E139">
         <v>2040</v>
@@ -14460,16 +14041,13 @@
         <v>2800</v>
       </c>
       <c r="G139">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H139">
-        <v>1</v>
-      </c>
-      <c r="I139">
         <v>0.01</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:8">
       <c r="A140" t="s">
         <v>242</v>
       </c>
@@ -14480,7 +14058,7 @@
         <v>122</v>
       </c>
       <c r="D140" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E140">
         <v>2040</v>
@@ -14489,16 +14067,13 @@
         <v>1716</v>
       </c>
       <c r="G140">
-        <v>3.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H140">
-        <v>1</v>
-      </c>
-      <c r="I140">
         <v>0.01</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:8">
       <c r="A141" t="s">
         <v>242</v>
       </c>
@@ -14509,7 +14084,7 @@
         <v>120</v>
       </c>
       <c r="D141" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E141">
         <v>2040</v>
@@ -14518,16 +14093,13 @@
         <v>1716</v>
       </c>
       <c r="G141">
-        <v>3.2859999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H141">
-        <v>1</v>
-      </c>
-      <c r="I141">
         <v>0.01</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:8">
       <c r="A142" t="s">
         <v>242</v>
       </c>
@@ -14538,7 +14110,7 @@
         <v>125</v>
       </c>
       <c r="D142" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E142">
         <v>2040</v>
@@ -14547,16 +14119,13 @@
         <v>1950</v>
       </c>
       <c r="G142">
-        <v>3.3059999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H142">
-        <v>1</v>
-      </c>
-      <c r="I142">
         <v>0.01</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:8">
       <c r="A143" t="s">
         <v>242</v>
       </c>
@@ -14567,7 +14136,7 @@
         <v>120</v>
       </c>
       <c r="D143" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E143">
         <v>2040</v>
@@ -14576,16 +14145,13 @@
         <v>1879</v>
       </c>
       <c r="G143">
-        <v>3.431E-3</v>
+        <v>1</v>
       </c>
       <c r="H143">
-        <v>1</v>
-      </c>
-      <c r="I143">
         <v>0.01</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:8">
       <c r="A144" t="s">
         <v>242</v>
       </c>
@@ -14596,7 +14162,7 @@
         <v>123</v>
       </c>
       <c r="D144" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E144">
         <v>2040</v>
@@ -14605,16 +14171,13 @@
         <v>6500</v>
       </c>
       <c r="G144">
-        <v>4.627E-3</v>
+        <v>1</v>
       </c>
       <c r="H144">
-        <v>1</v>
-      </c>
-      <c r="I144">
         <v>0.01</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:8">
       <c r="A145" t="s">
         <v>242</v>
       </c>
@@ -14625,7 +14188,7 @@
         <v>121</v>
       </c>
       <c r="D145" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E145">
         <v>2040</v>
@@ -14634,16 +14197,13 @@
         <v>6500</v>
       </c>
       <c r="G145">
-        <v>4.627E-3</v>
+        <v>1</v>
       </c>
       <c r="H145">
-        <v>1</v>
-      </c>
-      <c r="I145">
         <v>0.01</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:8">
       <c r="A146" t="s">
         <v>242</v>
       </c>
@@ -14654,7 +14214,7 @@
         <v>128</v>
       </c>
       <c r="D146" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E146">
         <v>2040</v>
@@ -14663,16 +14223,13 @@
         <v>0</v>
       </c>
       <c r="G146">
-        <v>4.7959999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H146">
-        <v>1</v>
-      </c>
-      <c r="I146">
         <v>0.01</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:8">
       <c r="A147" t="s">
         <v>242</v>
       </c>
@@ -14683,7 +14240,7 @@
         <v>122</v>
       </c>
       <c r="D147" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E147">
         <v>2040</v>
@@ -14692,16 +14249,13 @@
         <v>0</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147">
-        <v>1</v>
-      </c>
-      <c r="I147">
         <v>0.01</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:8">
       <c r="A148" t="s">
         <v>242</v>
       </c>
@@ -14712,7 +14266,7 @@
         <v>131</v>
       </c>
       <c r="D148" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E148">
         <v>2040</v>
@@ -14721,16 +14275,13 @@
         <v>2800</v>
       </c>
       <c r="G148">
-        <v>2.9039999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H148">
-        <v>1</v>
-      </c>
-      <c r="I148">
         <v>0.01</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:8">
       <c r="A149" t="s">
         <v>242</v>
       </c>
@@ -14741,7 +14292,7 @@
         <v>122</v>
       </c>
       <c r="D149" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E149">
         <v>2040</v>
@@ -14750,16 +14301,13 @@
         <v>2800</v>
       </c>
       <c r="G149">
-        <v>2.9039999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H149">
-        <v>1</v>
-      </c>
-      <c r="I149">
         <v>0.01</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:8">
       <c r="A150" t="s">
         <v>242</v>
       </c>
@@ -14770,7 +14318,7 @@
         <v>133</v>
       </c>
       <c r="D150" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E150">
         <v>2040</v>
@@ -14779,16 +14327,13 @@
         <v>1200</v>
       </c>
       <c r="G150">
-        <v>4.1539999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H150">
-        <v>1</v>
-      </c>
-      <c r="I150">
         <v>0.01</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:8">
       <c r="A151" t="s">
         <v>242</v>
       </c>
@@ -14799,7 +14344,7 @@
         <v>122</v>
       </c>
       <c r="D151" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E151">
         <v>2040</v>
@@ -14808,16 +14353,13 @@
         <v>1200</v>
       </c>
       <c r="G151">
-        <v>4.1539999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H151">
-        <v>1</v>
-      </c>
-      <c r="I151">
         <v>0.01</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:8">
       <c r="A152" t="s">
         <v>242</v>
       </c>
@@ -14828,7 +14370,7 @@
         <v>135</v>
       </c>
       <c r="D152" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E152">
         <v>2040</v>
@@ -14837,16 +14379,13 @@
         <v>8725</v>
       </c>
       <c r="G152">
-        <v>4.3889999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H152">
-        <v>1</v>
-      </c>
-      <c r="I152">
         <v>0.01</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:8">
       <c r="A153" t="s">
         <v>242</v>
       </c>
@@ -14857,7 +14396,7 @@
         <v>123</v>
       </c>
       <c r="D153" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E153">
         <v>2040</v>
@@ -14866,16 +14405,13 @@
         <v>8725</v>
       </c>
       <c r="G153">
-        <v>4.3889999999999997E-3</v>
+        <v>1</v>
       </c>
       <c r="H153">
-        <v>1</v>
-      </c>
-      <c r="I153">
         <v>0.01</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:8">
       <c r="A154" t="s">
         <v>242</v>
       </c>
@@ -14886,7 +14422,7 @@
         <v>125</v>
       </c>
       <c r="D154" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E154">
         <v>2040</v>
@@ -14895,16 +14431,13 @@
         <v>950</v>
       </c>
       <c r="G154">
-        <v>3.3210000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H154">
-        <v>1</v>
-      </c>
-      <c r="I154">
         <v>0.01</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:8">
       <c r="A155" t="s">
         <v>242</v>
       </c>
@@ -14915,7 +14448,7 @@
         <v>124</v>
       </c>
       <c r="D155" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E155">
         <v>2040</v>
@@ -14924,16 +14457,13 @@
         <v>950</v>
       </c>
       <c r="G155">
-        <v>3.3210000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H155">
-        <v>1</v>
-      </c>
-      <c r="I155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:8">
       <c r="A156" t="s">
         <v>242</v>
       </c>
@@ -14944,7 +14474,7 @@
         <v>130</v>
       </c>
       <c r="D156" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E156">
         <v>2040</v>
@@ -14953,16 +14483,13 @@
         <v>700</v>
       </c>
       <c r="G156">
-        <v>8.796E-3</v>
+        <v>1</v>
       </c>
       <c r="H156">
-        <v>1</v>
-      </c>
-      <c r="I156">
         <v>0.01</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:8">
       <c r="A157" t="s">
         <v>242</v>
       </c>
@@ -14973,7 +14500,7 @@
         <v>124</v>
       </c>
       <c r="D157" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E157">
         <v>2040</v>
@@ -14982,16 +14509,13 @@
         <v>700</v>
       </c>
       <c r="G157">
-        <v>8.796E-3</v>
+        <v>1</v>
       </c>
       <c r="H157">
-        <v>1</v>
-      </c>
-      <c r="I157">
         <v>0.01</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:8">
       <c r="A158" t="s">
         <v>242</v>
       </c>
@@ -15002,7 +14526,7 @@
         <v>134</v>
       </c>
       <c r="D158" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E158">
         <v>2040</v>
@@ -15011,16 +14535,13 @@
         <v>700</v>
       </c>
       <c r="G158">
-        <v>4.8089999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H158">
-        <v>1</v>
-      </c>
-      <c r="I158">
         <v>0.01</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:8">
       <c r="A159" t="s">
         <v>242</v>
       </c>
@@ -15031,7 +14552,7 @@
         <v>124</v>
       </c>
       <c r="D159" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E159">
         <v>2040</v>
@@ -15040,16 +14561,13 @@
         <v>700</v>
       </c>
       <c r="G159">
-        <v>4.8089999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H159">
-        <v>1</v>
-      </c>
-      <c r="I159">
         <v>0.01</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:8">
       <c r="A160" t="s">
         <v>242</v>
       </c>
@@ -15060,7 +14578,7 @@
         <v>129</v>
       </c>
       <c r="D160" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E160">
         <v>2040</v>
@@ -15069,16 +14587,13 @@
         <v>700</v>
       </c>
       <c r="G160">
-        <v>3.813E-3</v>
+        <v>1</v>
       </c>
       <c r="H160">
-        <v>1</v>
-      </c>
-      <c r="I160">
         <v>0.01</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:8">
       <c r="A161" t="s">
         <v>242</v>
       </c>
@@ -15089,7 +14604,7 @@
         <v>126</v>
       </c>
       <c r="D161" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E161">
         <v>2040</v>
@@ -15098,16 +14613,13 @@
         <v>700</v>
       </c>
       <c r="G161">
-        <v>3.813E-3</v>
+        <v>1</v>
       </c>
       <c r="H161">
-        <v>1</v>
-      </c>
-      <c r="I161">
         <v>0.01</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:8">
       <c r="A162" t="s">
         <v>242</v>
       </c>
@@ -15118,7 +14630,7 @@
         <v>135</v>
       </c>
       <c r="D162" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E162">
         <v>2040</v>
@@ -15127,16 +14639,13 @@
         <v>2800</v>
       </c>
       <c r="G162">
-        <v>9.7680000000000006E-3</v>
+        <v>1</v>
       </c>
       <c r="H162">
-        <v>1</v>
-      </c>
-      <c r="I162">
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:8">
       <c r="A163" t="s">
         <v>242</v>
       </c>
@@ -15147,7 +14656,7 @@
         <v>126</v>
       </c>
       <c r="D163" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E163">
         <v>2040</v>
@@ -15156,16 +14665,13 @@
         <v>2800</v>
       </c>
       <c r="G163">
-        <v>9.7680000000000006E-3</v>
+        <v>1</v>
       </c>
       <c r="H163">
-        <v>1</v>
-      </c>
-      <c r="I163">
         <v>0.01</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:8">
       <c r="A164" t="s">
         <v>242</v>
       </c>
@@ -15176,7 +14682,7 @@
         <v>128</v>
       </c>
       <c r="D164" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E164">
         <v>2040</v>
@@ -15185,16 +14691,13 @@
         <v>350</v>
       </c>
       <c r="G164">
-        <v>2.5279999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H164">
-        <v>1</v>
-      </c>
-      <c r="I164">
         <v>0.01</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:8">
       <c r="A165" t="s">
         <v>242</v>
       </c>
@@ -15205,7 +14708,7 @@
         <v>127</v>
       </c>
       <c r="D165" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E165">
         <v>2040</v>
@@ -15214,16 +14717,13 @@
         <v>1300</v>
       </c>
       <c r="G165">
-        <v>6.8099999999999996E-4</v>
+        <v>1</v>
       </c>
       <c r="H165">
-        <v>1</v>
-      </c>
-      <c r="I165">
         <v>0.01</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:8">
       <c r="A166" t="s">
         <v>242</v>
       </c>
@@ -15234,7 +14734,7 @@
         <v>129</v>
       </c>
       <c r="D166" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E166">
         <v>2040</v>
@@ -15243,16 +14743,13 @@
         <v>800</v>
       </c>
       <c r="G166">
-        <v>1.603E-3</v>
+        <v>1</v>
       </c>
       <c r="H166">
-        <v>1</v>
-      </c>
-      <c r="I166">
         <v>0.01</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:8">
       <c r="A167" t="s">
         <v>242</v>
       </c>
@@ -15263,7 +14760,7 @@
         <v>127</v>
       </c>
       <c r="D167" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E167">
         <v>2040</v>
@@ -15272,16 +14769,13 @@
         <v>600</v>
       </c>
       <c r="G167">
-        <v>2.137E-3</v>
+        <v>1</v>
       </c>
       <c r="H167">
-        <v>1</v>
-      </c>
-      <c r="I167">
         <v>0.01</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:8">
       <c r="A168" t="s">
         <v>242</v>
       </c>
@@ -15292,7 +14786,7 @@
         <v>132</v>
       </c>
       <c r="D168" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E168">
         <v>2040</v>
@@ -15301,16 +14795,13 @@
         <v>600</v>
       </c>
       <c r="G168">
-        <v>3.9880000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H168">
-        <v>1</v>
-      </c>
-      <c r="I168">
         <v>0.01</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:8">
       <c r="A169" t="s">
         <v>242</v>
       </c>
@@ -15321,7 +14812,7 @@
         <v>127</v>
       </c>
       <c r="D169" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E169">
         <v>2040</v>
@@ -15330,16 +14821,13 @@
         <v>1000</v>
       </c>
       <c r="G169">
-        <v>2.3930000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H169">
-        <v>1</v>
-      </c>
-      <c r="I169">
         <v>0.01</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:8">
       <c r="A170" t="s">
         <v>242</v>
       </c>
@@ -15350,7 +14838,7 @@
         <v>131</v>
       </c>
       <c r="D170" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E170">
         <v>2040</v>
@@ -15359,16 +14847,13 @@
         <v>700</v>
       </c>
       <c r="G170">
-        <v>4.3309999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H170">
-        <v>1</v>
-      </c>
-      <c r="I170">
         <v>0.01</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:8">
       <c r="A171" t="s">
         <v>242</v>
       </c>
@@ -15379,7 +14864,7 @@
         <v>128</v>
       </c>
       <c r="D171" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E171">
         <v>2040</v>
@@ -15388,16 +14873,13 @@
         <v>600</v>
       </c>
       <c r="G171">
-        <v>5.0530000000000002E-3</v>
+        <v>1</v>
       </c>
       <c r="H171">
-        <v>1</v>
-      </c>
-      <c r="I171">
         <v>0.01</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:8">
       <c r="A172" t="s">
         <v>242</v>
       </c>
@@ -15408,7 +14890,7 @@
         <v>132</v>
       </c>
       <c r="D172" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E172">
         <v>2040</v>
@@ -15417,16 +14899,13 @@
         <v>250</v>
       </c>
       <c r="G172">
-        <v>3.2550000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H172">
-        <v>1</v>
-      </c>
-      <c r="I172">
         <v>0.01</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:8">
       <c r="A173" t="s">
         <v>242</v>
       </c>
@@ -15437,7 +14916,7 @@
         <v>128</v>
       </c>
       <c r="D173" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E173">
         <v>2040</v>
@@ -15446,16 +14925,13 @@
         <v>300</v>
       </c>
       <c r="G173">
-        <v>2.7130000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H173">
-        <v>1</v>
-      </c>
-      <c r="I173">
         <v>0.01</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:8">
       <c r="A174" t="s">
         <v>242</v>
       </c>
@@ -15466,7 +14942,7 @@
         <v>133</v>
       </c>
       <c r="D174" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E174">
         <v>2040</v>
@@ -15475,16 +14951,13 @@
         <v>2145</v>
       </c>
       <c r="G174">
-        <v>4.248E-3</v>
+        <v>1</v>
       </c>
       <c r="H174">
-        <v>1</v>
-      </c>
-      <c r="I174">
         <v>0.01</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:8">
       <c r="A175" t="s">
         <v>242</v>
       </c>
@@ -15495,7 +14968,7 @@
         <v>129</v>
       </c>
       <c r="D175" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E175">
         <v>2040</v>
@@ -15504,16 +14977,13 @@
         <v>2095</v>
       </c>
       <c r="G175">
-        <v>4.3489999999999996E-3</v>
+        <v>1</v>
       </c>
       <c r="H175">
-        <v>1</v>
-      </c>
-      <c r="I175">
         <v>0.01</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:8">
       <c r="A176" t="s">
         <v>242</v>
       </c>
@@ -15524,7 +14994,7 @@
         <v>135</v>
       </c>
       <c r="D176" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E176">
         <v>2040</v>
@@ -15533,16 +15003,13 @@
         <v>1400</v>
       </c>
       <c r="G176">
-        <v>2.7680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H176">
-        <v>1</v>
-      </c>
-      <c r="I176">
         <v>0.01</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:8">
       <c r="A177" t="s">
         <v>242</v>
       </c>
@@ -15553,7 +15020,7 @@
         <v>129</v>
       </c>
       <c r="D177" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E177">
         <v>2040</v>
@@ -15562,16 +15029,13 @@
         <v>1400</v>
       </c>
       <c r="G177">
-        <v>2.7680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H177">
-        <v>1</v>
-      </c>
-      <c r="I177">
         <v>0.01</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:8">
       <c r="A178" t="s">
         <v>242</v>
       </c>
@@ -15582,7 +15046,7 @@
         <v>134</v>
       </c>
       <c r="D178" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E178">
         <v>2040</v>
@@ -15591,16 +15055,13 @@
         <v>600</v>
       </c>
       <c r="G178">
-        <v>8.3330000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H178">
-        <v>1</v>
-      </c>
-      <c r="I178">
         <v>0.01</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:8">
       <c r="A179" t="s">
         <v>242</v>
       </c>
@@ -15611,7 +15072,7 @@
         <v>130</v>
       </c>
       <c r="D179" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E179">
         <v>2040</v>
@@ -15620,16 +15081,13 @@
         <v>600</v>
       </c>
       <c r="G179">
-        <v>8.3330000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H179">
-        <v>1</v>
-      </c>
-      <c r="I179">
         <v>0.01</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:8">
       <c r="A180" t="s">
         <v>242</v>
       </c>
@@ -15640,7 +15098,7 @@
         <v>132</v>
       </c>
       <c r="D180" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E180">
         <v>2040</v>
@@ -15649,16 +15107,13 @@
         <v>3300</v>
       </c>
       <c r="G180">
-        <v>2.1359999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H180">
-        <v>1</v>
-      </c>
-      <c r="I180">
         <v>0.01</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:8">
       <c r="A181" t="s">
         <v>242</v>
       </c>
@@ -15669,7 +15124,7 @@
         <v>131</v>
       </c>
       <c r="D181" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E181">
         <v>2040</v>
@@ -15678,16 +15133,13 @@
         <v>3300</v>
       </c>
       <c r="G181">
-        <v>2.1359999999999999E-3</v>
+        <v>1</v>
       </c>
       <c r="H181">
-        <v>1</v>
-      </c>
-      <c r="I181">
         <v>0.01</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:8">
       <c r="A182" t="s">
         <v>242</v>
       </c>
@@ -15698,7 +15150,7 @@
         <v>133</v>
       </c>
       <c r="D182" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E182">
         <v>2040</v>
@@ -15707,16 +15159,13 @@
         <v>7300</v>
       </c>
       <c r="G182">
-        <v>1.8680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H182">
-        <v>1</v>
-      </c>
-      <c r="I182">
         <v>0.01</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:8">
       <c r="A183" t="s">
         <v>242</v>
       </c>
@@ -15727,7 +15176,7 @@
         <v>132</v>
       </c>
       <c r="D183" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E183">
         <v>2040</v>
@@ -15736,16 +15185,13 @@
         <v>7300</v>
       </c>
       <c r="G183">
-        <v>1.8680000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="H183">
-        <v>1</v>
-      </c>
-      <c r="I183">
         <v>0.01</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:8">
       <c r="A184" t="s">
         <v>242</v>
       </c>
@@ -15756,7 +15202,7 @@
         <v>134</v>
       </c>
       <c r="D184" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E184">
         <v>2040</v>
@@ -15765,16 +15211,13 @@
         <v>6200</v>
       </c>
       <c r="G184">
-        <v>2.679E-3</v>
+        <v>1</v>
       </c>
       <c r="H184">
-        <v>1</v>
-      </c>
-      <c r="I184">
         <v>0.01</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:8">
       <c r="A185" t="s">
         <v>242</v>
       </c>
@@ -15785,7 +15228,7 @@
         <v>133</v>
       </c>
       <c r="D185" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E185">
         <v>2040</v>
@@ -15794,12 +15237,9 @@
         <v>2800</v>
       </c>
       <c r="G185">
-        <v>5.9319999999999998E-3</v>
+        <v>1</v>
       </c>
       <c r="H185">
-        <v>1</v>
-      </c>
-      <c r="I185">
         <v>0.01</v>
       </c>
     </row>
@@ -15830,13 +15270,13 @@
         <v>211</v>
       </c>
       <c r="C1" s="79" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1" s="79" t="s">
         <v>288</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="E1" s="79" t="s">
         <v>289</v>
-      </c>
-      <c r="E1" s="79" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -18525,10 +17965,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="82" t="s">
+        <v>289</v>
+      </c>
+      <c r="F1" s="82" t="s">
         <v>290</v>
-      </c>
-      <c r="F1" s="82" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -18686,7 +18126,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D9" s="81" t="s">
         <v>214</v>
@@ -18896,7 +18336,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D19" s="81" t="s">
         <v>214</v>
@@ -43424,7 +42864,7 @@
         <v>217</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D2" s="19">
         <v>2015</v>
@@ -43446,7 +42886,7 @@
         <v>217</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D3" s="19">
         <v>2015</v>
@@ -43468,7 +42908,7 @@
         <v>217</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D4" s="19">
         <v>2015</v>
@@ -43490,7 +42930,7 @@
         <v>217</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D5" s="19">
         <v>2015</v>
@@ -43512,7 +42952,7 @@
         <v>217</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D6" s="19">
         <v>2015</v>
@@ -43534,7 +42974,7 @@
         <v>217</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D7" s="19">
         <v>2015</v>
@@ -43556,7 +42996,7 @@
         <v>217</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D8" s="19">
         <v>2015</v>
@@ -43578,7 +43018,7 @@
         <v>217</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D9" s="19">
         <v>2015</v>
@@ -43600,7 +43040,7 @@
         <v>217</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D10" s="19">
         <v>2015</v>
@@ -43622,7 +43062,7 @@
         <v>217</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D11" s="19">
         <v>2015</v>
@@ -43644,7 +43084,7 @@
         <v>217</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D12" s="19">
         <v>2015</v>
@@ -43666,7 +43106,7 @@
         <v>217</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D13" s="19">
         <v>2015</v>
@@ -43688,7 +43128,7 @@
         <v>217</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D14" s="19">
         <v>2015</v>
@@ -43710,7 +43150,7 @@
         <v>217</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D15" s="19">
         <v>2015</v>
@@ -43732,7 +43172,7 @@
         <v>217</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D16" s="19">
         <v>2015</v>
@@ -43754,7 +43194,7 @@
         <v>217</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D17" s="19">
         <v>2015</v>
@@ -43776,7 +43216,7 @@
         <v>217</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D18" s="19">
         <v>2015</v>
@@ -43798,7 +43238,7 @@
         <v>217</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D19" s="19">
         <v>2015</v>
@@ -43820,7 +43260,7 @@
         <v>217</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D20" s="19">
         <v>2015</v>
@@ -43842,7 +43282,7 @@
         <v>217</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D21" s="19">
         <v>2015</v>
@@ -43864,7 +43304,7 @@
         <v>217</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D22" s="19">
         <v>2015</v>
@@ -43886,7 +43326,7 @@
         <v>217</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D23" s="19">
         <v>2015</v>
@@ -43908,7 +43348,7 @@
         <v>217</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D24" s="19">
         <v>2020</v>
@@ -43930,7 +43370,7 @@
         <v>217</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D25" s="19">
         <v>2020</v>
@@ -43952,7 +43392,7 @@
         <v>217</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D26" s="19">
         <v>2020</v>
@@ -43974,7 +43414,7 @@
         <v>217</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D27" s="19">
         <v>2020</v>
@@ -43996,7 +43436,7 @@
         <v>217</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D28" s="19">
         <v>2020</v>
@@ -44018,7 +43458,7 @@
         <v>217</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D29" s="19">
         <v>2020</v>
@@ -44040,7 +43480,7 @@
         <v>217</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D30" s="19">
         <v>2020</v>
@@ -44062,7 +43502,7 @@
         <v>217</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D31" s="19">
         <v>2020</v>
@@ -44084,7 +43524,7 @@
         <v>217</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D32" s="19">
         <v>2020</v>
@@ -44106,7 +43546,7 @@
         <v>217</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D33" s="19">
         <v>2020</v>
@@ -44128,7 +43568,7 @@
         <v>217</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D34" s="19">
         <v>2020</v>
@@ -44150,7 +43590,7 @@
         <v>217</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D35" s="19">
         <v>2020</v>
@@ -44172,7 +43612,7 @@
         <v>217</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D36" s="19">
         <v>2020</v>
@@ -44194,7 +43634,7 @@
         <v>217</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D37" s="19">
         <v>2020</v>
@@ -44216,7 +43656,7 @@
         <v>217</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D38" s="19">
         <v>2020</v>
@@ -44238,7 +43678,7 @@
         <v>217</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D39" s="19">
         <v>2020</v>
@@ -44260,7 +43700,7 @@
         <v>217</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D40" s="19">
         <v>2020</v>
@@ -44282,7 +43722,7 @@
         <v>217</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D41" s="19">
         <v>2020</v>
@@ -44304,7 +43744,7 @@
         <v>217</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D42" s="19">
         <v>2020</v>
@@ -44326,7 +43766,7 @@
         <v>217</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D43" s="19">
         <v>2020</v>
@@ -44348,7 +43788,7 @@
         <v>217</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D44" s="19">
         <v>2020</v>
@@ -44370,7 +43810,7 @@
         <v>217</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D45" s="19">
         <v>2020</v>
@@ -44392,7 +43832,7 @@
         <v>217</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D46" s="19">
         <v>2025</v>
@@ -44414,7 +43854,7 @@
         <v>217</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D47" s="19">
         <v>2025</v>
@@ -44436,7 +43876,7 @@
         <v>217</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D48" s="19">
         <v>2025</v>
@@ -44458,7 +43898,7 @@
         <v>217</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D49" s="19">
         <v>2025</v>
@@ -44480,7 +43920,7 @@
         <v>217</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D50" s="19">
         <v>2025</v>
@@ -44502,7 +43942,7 @@
         <v>217</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D51" s="19">
         <v>2025</v>
@@ -44524,7 +43964,7 @@
         <v>217</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D52" s="19">
         <v>2025</v>
@@ -44546,7 +43986,7 @@
         <v>217</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D53" s="19">
         <v>2025</v>
@@ -44568,7 +44008,7 @@
         <v>217</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D54" s="19">
         <v>2025</v>
@@ -44590,7 +44030,7 @@
         <v>217</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D55" s="19">
         <v>2025</v>
@@ -44612,7 +44052,7 @@
         <v>217</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D56" s="19">
         <v>2025</v>
@@ -44634,7 +44074,7 @@
         <v>217</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D57" s="19">
         <v>2025</v>
@@ -44656,7 +44096,7 @@
         <v>217</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D58" s="19">
         <v>2025</v>
@@ -44678,7 +44118,7 @@
         <v>217</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D59" s="19">
         <v>2025</v>
@@ -44700,7 +44140,7 @@
         <v>217</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D60" s="19">
         <v>2025</v>
@@ -44722,7 +44162,7 @@
         <v>217</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D61" s="19">
         <v>2025</v>
@@ -44744,7 +44184,7 @@
         <v>217</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D62" s="19">
         <v>2025</v>
@@ -44766,7 +44206,7 @@
         <v>217</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D63" s="19">
         <v>2025</v>
@@ -44788,7 +44228,7 @@
         <v>217</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D64" s="19">
         <v>2025</v>
@@ -44810,7 +44250,7 @@
         <v>217</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D65" s="19">
         <v>2025</v>
@@ -44832,7 +44272,7 @@
         <v>217</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D66" s="19">
         <v>2025</v>
@@ -44854,7 +44294,7 @@
         <v>217</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D67" s="19">
         <v>2025</v>
@@ -44876,7 +44316,7 @@
         <v>217</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D68" s="19">
         <v>2030</v>
@@ -44898,7 +44338,7 @@
         <v>217</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D69" s="19">
         <v>2030</v>
@@ -44920,7 +44360,7 @@
         <v>217</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D70" s="19">
         <v>2030</v>
@@ -44942,7 +44382,7 @@
         <v>217</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D71" s="19">
         <v>2030</v>
@@ -44964,7 +44404,7 @@
         <v>217</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D72" s="19">
         <v>2030</v>
@@ -44986,7 +44426,7 @@
         <v>217</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D73" s="19">
         <v>2030</v>
@@ -45008,7 +44448,7 @@
         <v>217</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D74" s="19">
         <v>2030</v>
@@ -45030,7 +44470,7 @@
         <v>217</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D75" s="19">
         <v>2030</v>
@@ -45052,7 +44492,7 @@
         <v>217</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D76" s="19">
         <v>2030</v>
@@ -45074,7 +44514,7 @@
         <v>217</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D77" s="19">
         <v>2030</v>
@@ -45096,7 +44536,7 @@
         <v>217</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D78" s="19">
         <v>2030</v>
@@ -45118,7 +44558,7 @@
         <v>217</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D79" s="19">
         <v>2030</v>
@@ -45140,7 +44580,7 @@
         <v>217</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D80" s="19">
         <v>2030</v>
@@ -45162,7 +44602,7 @@
         <v>217</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D81" s="19">
         <v>2030</v>
@@ -45184,7 +44624,7 @@
         <v>217</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D82" s="19">
         <v>2030</v>
@@ -45206,7 +44646,7 @@
         <v>217</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D83" s="19">
         <v>2030</v>
@@ -45228,7 +44668,7 @@
         <v>217</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D84" s="19">
         <v>2030</v>
@@ -45250,7 +44690,7 @@
         <v>217</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D85" s="19">
         <v>2030</v>
@@ -45272,7 +44712,7 @@
         <v>217</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D86" s="19">
         <v>2030</v>
@@ -45294,7 +44734,7 @@
         <v>217</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D87" s="19">
         <v>2030</v>
@@ -45316,7 +44756,7 @@
         <v>217</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D88" s="19">
         <v>2030</v>
@@ -45338,7 +44778,7 @@
         <v>217</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D89" s="19">
         <v>2030</v>
@@ -45360,7 +44800,7 @@
         <v>216</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D90" s="19">
         <v>2015</v>
@@ -45385,7 +44825,7 @@
         <v>216</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D91" s="19">
         <v>2015</v>
@@ -45407,7 +44847,7 @@
         <v>216</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D92" s="19">
         <v>2015</v>
@@ -45429,7 +44869,7 @@
         <v>216</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D93" s="19">
         <v>2015</v>
@@ -45451,7 +44891,7 @@
         <v>216</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D94" s="19">
         <v>2015</v>
@@ -45473,7 +44913,7 @@
         <v>216</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D95" s="19">
         <v>2015</v>
@@ -45495,7 +44935,7 @@
         <v>216</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D96" s="19">
         <v>2015</v>
@@ -45517,7 +44957,7 @@
         <v>216</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D97" s="19">
         <v>2015</v>
@@ -45539,7 +44979,7 @@
         <v>216</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D98" s="19">
         <v>2015</v>
@@ -45561,7 +45001,7 @@
         <v>216</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D99" s="19">
         <v>2015</v>
@@ -45583,7 +45023,7 @@
         <v>216</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D100" s="19">
         <v>2015</v>
@@ -45605,7 +45045,7 @@
         <v>216</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D101" s="19">
         <v>2015</v>
@@ -45627,7 +45067,7 @@
         <v>216</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D102" s="19">
         <v>2015</v>
@@ -45649,7 +45089,7 @@
         <v>216</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D103" s="19">
         <v>2015</v>
@@ -45671,7 +45111,7 @@
         <v>216</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D104" s="19">
         <v>2015</v>
@@ -45693,7 +45133,7 @@
         <v>216</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D105" s="19">
         <v>2015</v>
@@ -45715,7 +45155,7 @@
         <v>216</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D106" s="19">
         <v>2015</v>
@@ -45737,7 +45177,7 @@
         <v>216</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D107" s="19">
         <v>2015</v>
@@ -45759,7 +45199,7 @@
         <v>216</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D108" s="19">
         <v>2015</v>
@@ -45781,7 +45221,7 @@
         <v>216</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D109" s="19">
         <v>2015</v>
@@ -45803,7 +45243,7 @@
         <v>216</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D110" s="19">
         <v>2015</v>
@@ -45825,7 +45265,7 @@
         <v>216</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D111" s="19">
         <v>2015</v>
@@ -45847,7 +45287,7 @@
         <v>216</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D112" s="19">
         <v>2020</v>
@@ -45869,7 +45309,7 @@
         <v>216</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D113" s="19">
         <v>2020</v>
@@ -45891,7 +45331,7 @@
         <v>216</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D114" s="19">
         <v>2020</v>
@@ -45913,7 +45353,7 @@
         <v>216</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D115" s="19">
         <v>2020</v>
@@ -45935,7 +45375,7 @@
         <v>216</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D116" s="19">
         <v>2020</v>
@@ -45957,7 +45397,7 @@
         <v>216</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D117" s="19">
         <v>2020</v>
@@ -45979,7 +45419,7 @@
         <v>216</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D118" s="19">
         <v>2020</v>
@@ -46001,7 +45441,7 @@
         <v>216</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D119" s="19">
         <v>2020</v>
@@ -46023,7 +45463,7 @@
         <v>216</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D120" s="19">
         <v>2020</v>
@@ -46045,7 +45485,7 @@
         <v>216</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D121" s="19">
         <v>2020</v>
@@ -46067,7 +45507,7 @@
         <v>216</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D122" s="19">
         <v>2020</v>
@@ -46089,7 +45529,7 @@
         <v>216</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D123" s="19">
         <v>2020</v>
@@ -46111,7 +45551,7 @@
         <v>216</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D124" s="19">
         <v>2020</v>
@@ -46133,7 +45573,7 @@
         <v>216</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D125" s="19">
         <v>2020</v>
@@ -46155,7 +45595,7 @@
         <v>216</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D126" s="19">
         <v>2020</v>
@@ -46177,7 +45617,7 @@
         <v>216</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D127" s="19">
         <v>2020</v>
@@ -46199,7 +45639,7 @@
         <v>216</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D128" s="19">
         <v>2020</v>
@@ -46221,7 +45661,7 @@
         <v>216</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D129" s="19">
         <v>2020</v>
@@ -46243,7 +45683,7 @@
         <v>216</v>
       </c>
       <c r="C130" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D130" s="19">
         <v>2020</v>
@@ -46265,7 +45705,7 @@
         <v>216</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D131" s="19">
         <v>2020</v>
@@ -46287,7 +45727,7 @@
         <v>216</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D132" s="19">
         <v>2020</v>
@@ -46309,7 +45749,7 @@
         <v>216</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D133" s="19">
         <v>2020</v>
@@ -46331,7 +45771,7 @@
         <v>216</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D134" s="19">
         <v>2025</v>
@@ -46353,7 +45793,7 @@
         <v>216</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D135" s="19">
         <v>2025</v>
@@ -46375,7 +45815,7 @@
         <v>216</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D136" s="19">
         <v>2025</v>
@@ -46397,7 +45837,7 @@
         <v>216</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D137" s="19">
         <v>2025</v>
@@ -46419,7 +45859,7 @@
         <v>216</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D138" s="19">
         <v>2025</v>
@@ -46441,7 +45881,7 @@
         <v>216</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D139" s="19">
         <v>2025</v>
@@ -46463,7 +45903,7 @@
         <v>216</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D140" s="19">
         <v>2025</v>
@@ -46485,7 +45925,7 @@
         <v>216</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D141" s="19">
         <v>2025</v>
@@ -46507,7 +45947,7 @@
         <v>216</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D142" s="19">
         <v>2025</v>
@@ -46529,7 +45969,7 @@
         <v>216</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D143" s="19">
         <v>2025</v>
@@ -46551,7 +45991,7 @@
         <v>216</v>
       </c>
       <c r="C144" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D144" s="19">
         <v>2025</v>
@@ -46573,7 +46013,7 @@
         <v>216</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D145" s="19">
         <v>2025</v>
@@ -46595,7 +46035,7 @@
         <v>216</v>
       </c>
       <c r="C146" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D146" s="19">
         <v>2025</v>
@@ -46617,7 +46057,7 @@
         <v>216</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D147" s="19">
         <v>2025</v>
@@ -46639,7 +46079,7 @@
         <v>216</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D148" s="19">
         <v>2025</v>
@@ -46661,7 +46101,7 @@
         <v>216</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D149" s="19">
         <v>2025</v>
@@ -46683,7 +46123,7 @@
         <v>216</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D150" s="19">
         <v>2025</v>
@@ -46705,7 +46145,7 @@
         <v>216</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D151" s="19">
         <v>2025</v>
@@ -46727,7 +46167,7 @@
         <v>216</v>
       </c>
       <c r="C152" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D152" s="19">
         <v>2025</v>
@@ -46749,7 +46189,7 @@
         <v>216</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D153" s="19">
         <v>2025</v>
@@ -46771,7 +46211,7 @@
         <v>216</v>
       </c>
       <c r="C154" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D154" s="19">
         <v>2025</v>
@@ -46793,7 +46233,7 @@
         <v>216</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D155" s="19">
         <v>2025</v>
@@ -46815,7 +46255,7 @@
         <v>216</v>
       </c>
       <c r="C156" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D156" s="19">
         <v>2030</v>
@@ -46837,7 +46277,7 @@
         <v>216</v>
       </c>
       <c r="C157" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D157" s="19">
         <v>2030</v>
@@ -46859,7 +46299,7 @@
         <v>216</v>
       </c>
       <c r="C158" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D158" s="19">
         <v>2030</v>
@@ -46881,7 +46321,7 @@
         <v>216</v>
       </c>
       <c r="C159" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D159" s="19">
         <v>2030</v>
@@ -46903,7 +46343,7 @@
         <v>216</v>
       </c>
       <c r="C160" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D160" s="19">
         <v>2030</v>
@@ -46925,7 +46365,7 @@
         <v>216</v>
       </c>
       <c r="C161" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D161" s="19">
         <v>2030</v>
@@ -46947,7 +46387,7 @@
         <v>216</v>
       </c>
       <c r="C162" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D162" s="19">
         <v>2030</v>
@@ -46969,7 +46409,7 @@
         <v>216</v>
       </c>
       <c r="C163" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D163" s="19">
         <v>2030</v>
@@ -46991,7 +46431,7 @@
         <v>216</v>
       </c>
       <c r="C164" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D164" s="19">
         <v>2030</v>
@@ -47013,7 +46453,7 @@
         <v>216</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D165" s="19">
         <v>2030</v>
@@ -47035,7 +46475,7 @@
         <v>216</v>
       </c>
       <c r="C166" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D166" s="19">
         <v>2030</v>
@@ -47057,7 +46497,7 @@
         <v>216</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D167" s="19">
         <v>2030</v>
@@ -47079,7 +46519,7 @@
         <v>216</v>
       </c>
       <c r="C168" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D168" s="19">
         <v>2030</v>
@@ -47101,7 +46541,7 @@
         <v>216</v>
       </c>
       <c r="C169" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D169" s="19">
         <v>2030</v>
@@ -47123,7 +46563,7 @@
         <v>216</v>
       </c>
       <c r="C170" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D170" s="19">
         <v>2030</v>
@@ -47145,7 +46585,7 @@
         <v>216</v>
       </c>
       <c r="C171" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D171" s="19">
         <v>2030</v>
@@ -47167,7 +46607,7 @@
         <v>216</v>
       </c>
       <c r="C172" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D172" s="19">
         <v>2030</v>
@@ -47189,7 +46629,7 @@
         <v>216</v>
       </c>
       <c r="C173" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D173" s="19">
         <v>2030</v>
@@ -47211,7 +46651,7 @@
         <v>216</v>
       </c>
       <c r="C174" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D174" s="19">
         <v>2030</v>
@@ -47233,7 +46673,7 @@
         <v>216</v>
       </c>
       <c r="C175" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D175" s="19">
         <v>2030</v>
@@ -47255,7 +46695,7 @@
         <v>216</v>
       </c>
       <c r="C176" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D176" s="19">
         <v>2030</v>
@@ -47277,7 +46717,7 @@
         <v>216</v>
       </c>
       <c r="C177" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D177" s="19">
         <v>2030</v>
@@ -47299,7 +46739,7 @@
         <v>215</v>
       </c>
       <c r="C178" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D178" s="19">
         <v>2015</v>
@@ -47324,7 +46764,7 @@
         <v>215</v>
       </c>
       <c r="C179" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D179" s="19">
         <v>2015</v>
@@ -47346,7 +46786,7 @@
         <v>215</v>
       </c>
       <c r="C180" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D180" s="19">
         <v>2015</v>
@@ -47368,7 +46808,7 @@
         <v>215</v>
       </c>
       <c r="C181" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D181" s="19">
         <v>2015</v>
@@ -47390,7 +46830,7 @@
         <v>215</v>
       </c>
       <c r="C182" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D182" s="19">
         <v>2015</v>
@@ -47412,7 +46852,7 @@
         <v>215</v>
       </c>
       <c r="C183" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D183" s="19">
         <v>2015</v>
@@ -47434,7 +46874,7 @@
         <v>215</v>
       </c>
       <c r="C184" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D184" s="19">
         <v>2015</v>
@@ -47456,7 +46896,7 @@
         <v>215</v>
       </c>
       <c r="C185" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D185" s="19">
         <v>2015</v>
@@ -47478,7 +46918,7 @@
         <v>215</v>
       </c>
       <c r="C186" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D186" s="19">
         <v>2015</v>
@@ -47500,7 +46940,7 @@
         <v>215</v>
       </c>
       <c r="C187" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D187" s="19">
         <v>2015</v>
@@ -47522,7 +46962,7 @@
         <v>215</v>
       </c>
       <c r="C188" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D188" s="19">
         <v>2015</v>
@@ -47544,7 +46984,7 @@
         <v>215</v>
       </c>
       <c r="C189" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D189" s="19">
         <v>2015</v>
@@ -47566,7 +47006,7 @@
         <v>215</v>
       </c>
       <c r="C190" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D190" s="19">
         <v>2015</v>
@@ -47588,7 +47028,7 @@
         <v>215</v>
       </c>
       <c r="C191" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D191" s="19">
         <v>2015</v>
@@ -47610,7 +47050,7 @@
         <v>215</v>
       </c>
       <c r="C192" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D192" s="19">
         <v>2015</v>
@@ -47632,7 +47072,7 @@
         <v>215</v>
       </c>
       <c r="C193" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D193" s="19">
         <v>2015</v>
@@ -47654,7 +47094,7 @@
         <v>215</v>
       </c>
       <c r="C194" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D194" s="19">
         <v>2015</v>
@@ -47676,7 +47116,7 @@
         <v>215</v>
       </c>
       <c r="C195" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D195" s="19">
         <v>2015</v>
@@ -47698,7 +47138,7 @@
         <v>215</v>
       </c>
       <c r="C196" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D196" s="19">
         <v>2015</v>
@@ -47720,7 +47160,7 @@
         <v>215</v>
       </c>
       <c r="C197" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D197" s="19">
         <v>2015</v>
@@ -47742,7 +47182,7 @@
         <v>215</v>
       </c>
       <c r="C198" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D198" s="19">
         <v>2015</v>
@@ -47764,7 +47204,7 @@
         <v>215</v>
       </c>
       <c r="C199" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D199" s="19">
         <v>2015</v>
@@ -47786,7 +47226,7 @@
         <v>215</v>
       </c>
       <c r="C200" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D200" s="19">
         <v>2020</v>
@@ -47808,7 +47248,7 @@
         <v>215</v>
       </c>
       <c r="C201" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D201" s="19">
         <v>2020</v>
@@ -47830,7 +47270,7 @@
         <v>215</v>
       </c>
       <c r="C202" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D202" s="19">
         <v>2020</v>
@@ -47852,7 +47292,7 @@
         <v>215</v>
       </c>
       <c r="C203" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D203" s="19">
         <v>2020</v>
@@ -47874,7 +47314,7 @@
         <v>215</v>
       </c>
       <c r="C204" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D204" s="19">
         <v>2020</v>
@@ -47896,7 +47336,7 @@
         <v>215</v>
       </c>
       <c r="C205" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D205" s="19">
         <v>2020</v>
@@ -47918,7 +47358,7 @@
         <v>215</v>
       </c>
       <c r="C206" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D206" s="19">
         <v>2020</v>
@@ -47940,7 +47380,7 @@
         <v>215</v>
       </c>
       <c r="C207" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D207" s="19">
         <v>2020</v>
@@ -47962,7 +47402,7 @@
         <v>215</v>
       </c>
       <c r="C208" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D208" s="19">
         <v>2020</v>
@@ -47984,7 +47424,7 @@
         <v>215</v>
       </c>
       <c r="C209" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D209" s="19">
         <v>2020</v>
@@ -48006,7 +47446,7 @@
         <v>215</v>
       </c>
       <c r="C210" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D210" s="19">
         <v>2020</v>
@@ -48028,7 +47468,7 @@
         <v>215</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D211" s="19">
         <v>2020</v>
@@ -48050,7 +47490,7 @@
         <v>215</v>
       </c>
       <c r="C212" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D212" s="19">
         <v>2020</v>
@@ -48072,7 +47512,7 @@
         <v>215</v>
       </c>
       <c r="C213" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D213" s="19">
         <v>2020</v>
@@ -48094,7 +47534,7 @@
         <v>215</v>
       </c>
       <c r="C214" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D214" s="19">
         <v>2020</v>
@@ -48116,7 +47556,7 @@
         <v>215</v>
       </c>
       <c r="C215" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D215" s="19">
         <v>2020</v>
@@ -48138,7 +47578,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D216" s="19">
         <v>2020</v>
@@ -48160,7 +47600,7 @@
         <v>215</v>
       </c>
       <c r="C217" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D217" s="19">
         <v>2020</v>
@@ -48182,7 +47622,7 @@
         <v>215</v>
       </c>
       <c r="C218" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D218" s="19">
         <v>2020</v>
@@ -48204,7 +47644,7 @@
         <v>215</v>
       </c>
       <c r="C219" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D219" s="19">
         <v>2020</v>
@@ -48226,7 +47666,7 @@
         <v>215</v>
       </c>
       <c r="C220" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D220" s="19">
         <v>2020</v>
@@ -48248,7 +47688,7 @@
         <v>215</v>
       </c>
       <c r="C221" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D221" s="19">
         <v>2020</v>
@@ -48270,7 +47710,7 @@
         <v>215</v>
       </c>
       <c r="C222" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D222" s="19">
         <v>2025</v>
@@ -48292,7 +47732,7 @@
         <v>215</v>
       </c>
       <c r="C223" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D223" s="19">
         <v>2025</v>
@@ -48314,7 +47754,7 @@
         <v>215</v>
       </c>
       <c r="C224" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D224" s="19">
         <v>2025</v>
@@ -48336,7 +47776,7 @@
         <v>215</v>
       </c>
       <c r="C225" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D225" s="19">
         <v>2025</v>
@@ -48358,7 +47798,7 @@
         <v>215</v>
       </c>
       <c r="C226" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D226" s="19">
         <v>2025</v>
@@ -48380,7 +47820,7 @@
         <v>215</v>
       </c>
       <c r="C227" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D227" s="19">
         <v>2025</v>
@@ -48402,7 +47842,7 @@
         <v>215</v>
       </c>
       <c r="C228" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D228" s="19">
         <v>2025</v>
@@ -48424,7 +47864,7 @@
         <v>215</v>
       </c>
       <c r="C229" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D229" s="19">
         <v>2025</v>
@@ -48446,7 +47886,7 @@
         <v>215</v>
       </c>
       <c r="C230" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D230" s="19">
         <v>2025</v>
@@ -48468,7 +47908,7 @@
         <v>215</v>
       </c>
       <c r="C231" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D231" s="19">
         <v>2025</v>
@@ -48490,7 +47930,7 @@
         <v>215</v>
       </c>
       <c r="C232" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D232" s="19">
         <v>2025</v>
@@ -48512,7 +47952,7 @@
         <v>215</v>
       </c>
       <c r="C233" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D233" s="19">
         <v>2025</v>
@@ -48534,7 +47974,7 @@
         <v>215</v>
       </c>
       <c r="C234" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D234" s="19">
         <v>2025</v>
@@ -48556,7 +47996,7 @@
         <v>215</v>
       </c>
       <c r="C235" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D235" s="19">
         <v>2025</v>
@@ -48578,7 +48018,7 @@
         <v>215</v>
       </c>
       <c r="C236" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D236" s="19">
         <v>2025</v>
@@ -48600,7 +48040,7 @@
         <v>215</v>
       </c>
       <c r="C237" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D237" s="19">
         <v>2025</v>
@@ -48622,7 +48062,7 @@
         <v>215</v>
       </c>
       <c r="C238" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D238" s="19">
         <v>2025</v>
@@ -48644,7 +48084,7 @@
         <v>215</v>
       </c>
       <c r="C239" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D239" s="19">
         <v>2025</v>
@@ -48666,7 +48106,7 @@
         <v>215</v>
       </c>
       <c r="C240" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D240" s="19">
         <v>2025</v>
@@ -48688,7 +48128,7 @@
         <v>215</v>
       </c>
       <c r="C241" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D241" s="19">
         <v>2025</v>
@@ -48710,7 +48150,7 @@
         <v>215</v>
       </c>
       <c r="C242" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D242" s="19">
         <v>2025</v>
@@ -48732,7 +48172,7 @@
         <v>215</v>
       </c>
       <c r="C243" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D243" s="19">
         <v>2025</v>
@@ -48754,7 +48194,7 @@
         <v>215</v>
       </c>
       <c r="C244" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D244" s="19">
         <v>2030</v>
@@ -48776,7 +48216,7 @@
         <v>215</v>
       </c>
       <c r="C245" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D245" s="19">
         <v>2030</v>
@@ -48798,7 +48238,7 @@
         <v>215</v>
       </c>
       <c r="C246" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D246" s="19">
         <v>2030</v>
@@ -48820,7 +48260,7 @@
         <v>215</v>
       </c>
       <c r="C247" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D247" s="19">
         <v>2030</v>
@@ -48842,7 +48282,7 @@
         <v>215</v>
       </c>
       <c r="C248" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D248" s="19">
         <v>2030</v>
@@ -48864,7 +48304,7 @@
         <v>215</v>
       </c>
       <c r="C249" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D249" s="19">
         <v>2030</v>
@@ -48886,7 +48326,7 @@
         <v>215</v>
       </c>
       <c r="C250" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D250" s="19">
         <v>2030</v>
@@ -48908,7 +48348,7 @@
         <v>215</v>
       </c>
       <c r="C251" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D251" s="19">
         <v>2030</v>
@@ -48930,7 +48370,7 @@
         <v>215</v>
       </c>
       <c r="C252" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D252" s="19">
         <v>2030</v>
@@ -48952,7 +48392,7 @@
         <v>215</v>
       </c>
       <c r="C253" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D253" s="19">
         <v>2030</v>
@@ -48974,7 +48414,7 @@
         <v>215</v>
       </c>
       <c r="C254" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D254" s="19">
         <v>2030</v>
@@ -48996,7 +48436,7 @@
         <v>215</v>
       </c>
       <c r="C255" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D255" s="19">
         <v>2030</v>
@@ -49018,7 +48458,7 @@
         <v>215</v>
       </c>
       <c r="C256" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D256" s="19">
         <v>2030</v>
@@ -49040,7 +48480,7 @@
         <v>215</v>
       </c>
       <c r="C257" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D257" s="19">
         <v>2030</v>
@@ -49062,7 +48502,7 @@
         <v>215</v>
       </c>
       <c r="C258" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D258" s="19">
         <v>2030</v>
@@ -49084,7 +48524,7 @@
         <v>215</v>
       </c>
       <c r="C259" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D259" s="19">
         <v>2030</v>
@@ -49106,7 +48546,7 @@
         <v>215</v>
       </c>
       <c r="C260" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D260" s="19">
         <v>2030</v>
@@ -49128,7 +48568,7 @@
         <v>215</v>
       </c>
       <c r="C261" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D261" s="19">
         <v>2030</v>
@@ -49150,7 +48590,7 @@
         <v>215</v>
       </c>
       <c r="C262" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D262" s="19">
         <v>2030</v>
@@ -49172,7 +48612,7 @@
         <v>215</v>
       </c>
       <c r="C263" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D263" s="19">
         <v>2030</v>
@@ -49194,7 +48634,7 @@
         <v>215</v>
       </c>
       <c r="C264" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D264" s="19">
         <v>2030</v>
@@ -49216,7 +48656,7 @@
         <v>215</v>
       </c>
       <c r="C265" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D265" s="19">
         <v>2030</v>

--- a/src_files/data_files/ObservedTrends.xlsx
+++ b/src_files/data_files/ObservedTrends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F6FDD8-5400-4CFF-9E90-CD25D140FB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30821A77-E233-4909-8A3D-C16EC2EE6A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="770" firstSheet="6" activeTab="12" xr2:uid="{FFD27B4C-068C-4319-9C46-FFCA72C83648}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="770" firstSheet="6" activeTab="15" xr2:uid="{FFD27B4C-068C-4319-9C46-FFCA72C83648}"/>
   </bookViews>
   <sheets>
     <sheet name="VRE cap - ENTSOE NT2030" sheetId="7" r:id="rId1"/>
@@ -1748,6 +1748,89 @@
   </cellStyles>
   <dxfs count="18">
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="0" tint="-0.14999847407452621"/>
@@ -1885,89 +1968,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3974,7 +3974,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{091DB227-DDC4-472D-997A-DFFFE388BE8E}" name="Table6" displayName="Table6" ref="A1:H185" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{091DB227-DDC4-472D-997A-DFFFE388BE8E}" name="Table6" displayName="Table6" ref="A1:H185" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
   <autoFilter ref="A1:H185" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{4D600E68-4859-4617-99C0-EA7B63208C31}" name="grid"/>
@@ -3991,29 +3991,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}" name="Table3" displayName="Table3" ref="A1:E154" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}" name="Table3" displayName="Table3" ref="A1:E154" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11">
   <autoFilter ref="A1:E154" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9E8A91B3-5637-47C2-B0AE-8BCDAB50C806}" name="Country" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{41E09046-0D25-4DEB-9887-2ECB6AE473F2}" name="Generator_ID" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{5500E0F2-38FA-425D-A49B-9DFF7856120F}" name="Scenario" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{2F7FD309-B9BB-4C5B-B61A-862D1DC7A785}" name="Year" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{278785FB-0A20-4E0A-8E84-551D5FDF9FC2}" name="capacity_output1" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{9E8A91B3-5637-47C2-B0AE-8BCDAB50C806}" name="Country" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{41E09046-0D25-4DEB-9887-2ECB6AE473F2}" name="Generator_ID" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{5500E0F2-38FA-425D-A49B-9DFF7856120F}" name="Scenario" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{2F7FD309-B9BB-4C5B-B61A-862D1DC7A785}" name="Year" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{278785FB-0A20-4E0A-8E84-551D5FDF9FC2}" name="capacity_output1" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6EBB9830-FC23-4A98-9C08-0AAF69FC2331}" name="Table8" displayName="Table8" ref="A1:F21" totalsRowShown="0" headerRowDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6EBB9830-FC23-4A98-9C08-0AAF69FC2331}" name="Table8" displayName="Table8" ref="A1:F21" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:F21" xr:uid="{D9844F2F-2EE0-434B-9492-0280A28AB057}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{46AB9A07-935D-4BDF-BDAD-833C2B08B5EA}" name="Scenario" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{46AB9A07-935D-4BDF-BDAD-833C2B08B5EA}" name="Scenario" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{9C0117C3-729A-4483-9D40-255263DE774C}" name="Year"/>
-    <tableColumn id="3" xr3:uid="{F8AC0906-AF4C-4DB5-A628-E0D92C5871CF}" name="grid" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{5DE58EB2-B819-4C37-B8D5-9DAA3695DA87}" name="Country" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{2FBFC74F-134A-4E2A-8A69-7E943A399965}" name="price" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{78F6DB46-B023-4964-AA01-C06A0F1B985D}" name="emission_CO2" dataDxfId="12">
+    <tableColumn id="3" xr3:uid="{F8AC0906-AF4C-4DB5-A628-E0D92C5871CF}" name="grid" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{5DE58EB2-B819-4C37-B8D5-9DAA3695DA87}" name="Country" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{2FBFC74F-134A-4E2A-8A69-7E943A399965}" name="price" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{78F6DB46-B023-4964-AA01-C06A0F1B985D}" name="emission_CO2" dataDxfId="0">
       <calculatedColumnFormula>IFERROR(VLOOKUP($C2, [1]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>

--- a/src_files/data_files/ObservedTrends.xlsx
+++ b/src_files/data_files/ObservedTrends.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978AE20D-20F3-42C2-A4B7-A21314830BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9DA93E-C666-4AA5-9F89-E5B85EE617C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="801" xr2:uid="{FFD27B4C-068C-4319-9C46-FFCA72C83648}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="801" firstSheet="3" activeTab="10" xr2:uid="{FFD27B4C-068C-4319-9C46-FFCA72C83648}"/>
   </bookViews>
   <sheets>
     <sheet name="vomcost mult" sheetId="20" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2965" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3010" uniqueCount="328">
   <si>
     <t>Installed wind power capacity</t>
   </si>
@@ -950,15 +950,6 @@
     <t>EUR/MWh</t>
   </si>
   <si>
-    <t># Tier 1</t>
-  </si>
-  <si>
-    <t># Tier 2</t>
-  </si>
-  <si>
-    <t># Tier 3</t>
-  </si>
-  <si>
     <t>emission_bioCO2</t>
   </si>
   <si>
@@ -1061,21 +1052,6 @@
     <t>region multiplier</t>
   </si>
   <si>
-    <t># PV</t>
-  </si>
-  <si>
-    <t># Onshore</t>
-  </si>
-  <si>
-    <t># Offshore</t>
-  </si>
-  <si>
-    <t># Copying discharger capacity from charger capacity</t>
-  </si>
-  <si>
-    <t># Query charger capacity from previous sheets</t>
-  </si>
-  <si>
     <t>cost index 1</t>
   </si>
   <si>
@@ -1108,6 +1084,33 @@
   <si>
     <t>https://greenpowerdenmark.dk/nyheder/danmarks-stoerste-batteri-leverer-systemydelser-til-elnettet</t>
   </si>
+  <si>
+    <t>## Onshore</t>
+  </si>
+  <si>
+    <t>## Offshore</t>
+  </si>
+  <si>
+    <t>## PV</t>
+  </si>
+  <si>
+    <t>## Query charger capacity from previous sheets</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>## Copying discharger capacity from charger capacity</t>
+  </si>
+  <si>
+    <t>## Tier 1</t>
+  </si>
+  <si>
+    <t>## Tier 2</t>
+  </si>
+  <si>
+    <t>## Tier 3</t>
+  </si>
 </sst>
 </file>
 
@@ -1115,7 +1118,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.##########"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1555,7 +1558,7 @@
     <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1730,7 +1733,7 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
@@ -1758,6 +1761,11 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1787,8 +1795,6 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1799,16 +1805,6 @@
     <cellStyle name="Standard_Data provided by OT3" xfId="2" xr:uid="{CF5A235E-FF11-451C-B874-DD8F77BDC2C9}"/>
   </cellStyles>
   <dxfs count="40">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1894,61 +1890,31 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1956,14 +1922,6 @@
           <color auto="1"/>
         </top>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1986,15 +1944,8 @@
         <sz val="11"/>
         <color auto="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -2006,6 +1957,16 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2119,31 +2080,61 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border outline="0">
@@ -2151,6 +2142,14 @@
           <color auto="1"/>
         </top>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border outline="0">
@@ -2173,8 +2172,15 @@
         <sz val="11"/>
         <color auto="1"/>
         <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -4797,6 +4803,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="fueldata"/>
@@ -4927,21 +4934,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}" name="Table3" displayName="Table3" ref="A1:G104" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}" name="Table3" displayName="Table3" ref="A1:G104" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
   <autoFilter ref="A1:G104" xr:uid="{E20E85B3-70B8-42FA-A4DB-D01011C9C779}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F104">
     <sortCondition ref="A1:A104"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9E8A91B3-5637-47C2-B0AE-8BCDAB50C806}" name="Country" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{41E09046-0D25-4DEB-9887-2ECB6AE473F2}" name="Generator_ID" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{5500E0F2-38FA-425D-A49B-9DFF7856120F}" name="Scenario" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{2F7FD309-B9BB-4C5B-B61A-862D1DC7A785}" name="Year" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{278785FB-0A20-4E0A-8E84-551D5FDF9FC2}" name="capacity_output1" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{E48C78BB-51CD-490E-8B43-C4B84C6DDF67}" name="vomCosts" dataDxfId="18">
-      <calculatedColumnFormula>ROUND( VLOOKUP($B2,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A2,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{9E8A91B3-5637-47C2-B0AE-8BCDAB50C806}" name="Country" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{41E09046-0D25-4DEB-9887-2ECB6AE473F2}" name="Generator_ID" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{5500E0F2-38FA-425D-A49B-9DFF7856120F}" name="Scenario" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{2F7FD309-B9BB-4C5B-B61A-862D1DC7A785}" name="Year" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{278785FB-0A20-4E0A-8E84-551D5FDF9FC2}" name="capacity_output1" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{E48C78BB-51CD-490E-8B43-C4B84C6DDF67}" name="vomCosts" dataDxfId="19">
+      <calculatedColumnFormula>ROUND( VLOOKUP($B2,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A2,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D44E8CC1-3697-402B-8C4C-49C226851A8A}" name="method" dataDxfId="0">
+    <tableColumn id="7" xr3:uid="{D44E8CC1-3697-402B-8C4C-49C226851A8A}" name="method" dataDxfId="18">
       <calculatedColumnFormula>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4950,18 +4957,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3889FA67-DEB7-4516-91A9-7CF17095E2EC}" name="Table4" displayName="Table4" ref="A1:G70" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3889FA67-DEB7-4516-91A9-7CF17095E2EC}" name="Table4" displayName="Table4" ref="A1:G70" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36">
   <autoFilter ref="A1:G70" xr:uid="{3889FA67-DEB7-4516-91A9-7CF17095E2EC}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E45B6B69-99E0-46CC-B622-954E9F00977C}" name="Country" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{0C46E4F6-5176-430E-8288-0E4AD27B50FB}" name="Generator_ID" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{23013750-786E-46E4-BB5A-5093E68C9E50}" name="Scenario" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{34290B83-B2CB-4767-BBB2-F1BACB31B343}" name="Year" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{C5354F01-9DC1-45FC-9DAC-9FEB4789196D}" name="capacity_output1" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{4BC02F33-D1CC-4D1B-829D-EC13C6E66759}" name="vomCosts" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{E45B6B69-99E0-46CC-B622-954E9F00977C}" name="Country" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{0C46E4F6-5176-430E-8288-0E4AD27B50FB}" name="Generator_ID" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{23013750-786E-46E4-BB5A-5093E68C9E50}" name="Scenario" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{34290B83-B2CB-4767-BBB2-F1BACB31B343}" name="Year" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{C5354F01-9DC1-45FC-9DAC-9FEB4789196D}" name="capacity_output1" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{4BC02F33-D1CC-4D1B-829D-EC13C6E66759}" name="vomCosts" dataDxfId="30">
       <calculatedColumnFormula>400+V5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{44CC38D0-922B-47B3-AD5D-D98AD32D8306}" name="method" dataDxfId="7">
+    <tableColumn id="7" xr3:uid="{44CC38D0-922B-47B3-AD5D-D98AD32D8306}" name="method" dataDxfId="29">
       <calculatedColumnFormula>IF(Table4[[#This Row],[capacity_output1]]&lt;10, "remove", "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4970,20 +4977,20 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{091DB227-DDC4-472D-997A-DFFFE388BE8E}" name="Table6" displayName="Table6" ref="A1:I93" totalsRowShown="0" headerRowDxfId="39" headerRowBorderDxfId="38" tableBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{091DB227-DDC4-472D-997A-DFFFE388BE8E}" name="Table6" displayName="Table6" ref="A1:I93" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
   <autoFilter ref="A1:I93" xr:uid="{B440C99F-3BB1-4A8C-9867-FC60A58307DE}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{4D600E68-4859-4617-99C0-EA7B63208C31}" name="grid" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{55683E09-DD2F-48C0-AB3E-CC91087C7173}" name="from_country" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{C8327C88-FBE8-4FC2-A619-A4BA01413A1C}" name="to_country" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{742C6874-D199-4EE2-A562-EA0C285890D2}" name="scenario" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{1268EAAB-42FE-4A83-98BF-F41F14FEF437}" name="Year" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{DD03EC9C-1908-4818-A7AD-696B46FD7E55}" name="transferCap" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{858FE1C4-CAB1-497D-B42D-428703C91594}" name="variableTransCost" dataDxfId="30">
-      <calculatedColumnFormula>M2</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{4D600E68-4859-4617-99C0-EA7B63208C31}" name="grid" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{55683E09-DD2F-48C0-AB3E-CC91087C7173}" name="from_country" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{C8327C88-FBE8-4FC2-A619-A4BA01413A1C}" name="to_country" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{742C6874-D199-4EE2-A562-EA0C285890D2}" name="scenario" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{1268EAAB-42FE-4A83-98BF-F41F14FEF437}" name="Year" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{DD03EC9C-1908-4818-A7AD-696B46FD7E55}" name="transferCap" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{858FE1C4-CAB1-497D-B42D-428703C91594}" name="variableTransCost" dataDxfId="8">
+      <calculatedColumnFormula>M3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{BEFF1833-3A5D-4270-8A18-81866BBAA2B1}" name="transferLoss" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{B1909AD5-E5F0-4095-9C30-EDBB8410D520}" name="method" dataDxfId="28">
+    <tableColumn id="9" xr3:uid="{BEFF1833-3A5D-4270-8A18-81866BBAA2B1}" name="transferLoss" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{B1909AD5-E5F0-4095-9C30-EDBB8410D520}" name="method" dataDxfId="6">
       <calculatedColumnFormula>IF(Table6[[#This Row],[transferCap]]&lt;10, "remove", "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4992,15 +4999,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6EBB9830-FC23-4A98-9C08-0AAF69FC2331}" name="Table8" displayName="Table8" ref="A1:F11" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6EBB9830-FC23-4A98-9C08-0AAF69FC2331}" name="Table8" displayName="Table8" ref="A1:F11" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:F11" xr:uid="{D9844F2F-2EE0-434B-9492-0280A28AB057}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{46AB9A07-935D-4BDF-BDAD-833C2B08B5EA}" name="Scenario" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{46AB9A07-935D-4BDF-BDAD-833C2B08B5EA}" name="Scenario" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{9C0117C3-729A-4483-9D40-255263DE774C}" name="Year"/>
-    <tableColumn id="3" xr3:uid="{F8AC0906-AF4C-4DB5-A628-E0D92C5871CF}" name="grid" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{5DE58EB2-B819-4C37-B8D5-9DAA3695DA87}" name="Country" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{2FBFC74F-134A-4E2A-8A69-7E943A399965}" name="price" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{78F6DB46-B023-4964-AA01-C06A0F1B985D}" name="emission_CO2" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{F8AC0906-AF4C-4DB5-A628-E0D92C5871CF}" name="grid" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{5DE58EB2-B819-4C37-B8D5-9DAA3695DA87}" name="Country" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{2FBFC74F-134A-4E2A-8A69-7E943A399965}" name="price" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{78F6DB46-B023-4964-AA01-C06A0F1B985D}" name="emission_CO2" dataDxfId="0">
       <calculatedColumnFormula>IFERROR(VLOOKUP($C2, [2]data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5339,7 +5346,7 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="27" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -5347,7 +5354,7 @@
         <v>146</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -5355,7 +5362,7 @@
         <v>147</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -5371,15 +5378,15 @@
         <v>150</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -5399,7 +5406,7 @@
         <v>156</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -5422,16 +5429,16 @@
         <v>152</v>
       </c>
       <c r="J10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="O10" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="P10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Q10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="R10" s="23" t="s">
         <v>271</v>
@@ -5477,7 +5484,7 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="32" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B12" s="33">
         <v>33160</v>
@@ -5515,7 +5522,7 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="32" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B13" s="35">
         <v>33610</v>
@@ -5632,7 +5639,7 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="32" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B16" s="33">
         <v>20980</v>
@@ -6349,7 +6356,7 @@
         <v>72</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O34" s="37">
         <f>F11</f>
@@ -6587,7 +6594,7 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B46" s="33">
         <v>33840</v>
@@ -6717,35 +6724,35 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="28" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="28" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="28" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B62" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B63" s="74">
         <v>46077</v>
@@ -6753,23 +6760,23 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B65" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B66" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B69" t="s">
         <v>153</v>
@@ -6784,7 +6791,7 @@
         <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -6829,7 +6836,7 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B73">
         <v>1.1422000000000001</v>
@@ -6847,12 +6854,12 @@
         <v>1.0824</v>
       </c>
       <c r="H73" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B75">
         <f>ROUND(B70/B$73,0)</f>
@@ -6880,7 +6887,7 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B76">
         <f t="shared" ref="B76:F76" si="4">ROUND(B71/B$73,0)</f>
@@ -6948,10 +6955,37 @@
       <c r="G1" s="39" t="s">
         <v>167</v>
       </c>
+      <c r="K1" t="s">
+        <v>323</v>
+      </c>
+      <c r="L1" t="s">
+        <v>323</v>
+      </c>
+      <c r="M1" t="s">
+        <v>323</v>
+      </c>
+      <c r="N1" t="s">
+        <v>323</v>
+      </c>
+      <c r="O1" t="s">
+        <v>323</v>
+      </c>
+      <c r="P1" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>323</v>
+      </c>
+      <c r="R1" t="s">
+        <v>323</v>
+      </c>
+      <c r="S1" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="17" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B2" s="76"/>
       <c r="C2" s="76"/>
@@ -7333,7 +7367,7 @@
         <v>2000</v>
       </c>
       <c r="S13" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -7479,7 +7513,7 @@
         <v>350</v>
       </c>
       <c r="S16" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -8592,7 +8626,7 @@
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="17" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C47" s="19"/>
       <c r="D47" s="19"/>
@@ -10104,7 +10138,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -10117,7 +10151,7 @@
     <col min="12" max="12" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="52" t="s">
         <v>3</v>
       </c>
@@ -10139,11 +10173,20 @@
       <c r="G1" s="52" t="s">
         <v>167</v>
       </c>
+      <c r="K1" t="s">
+        <v>323</v>
+      </c>
+      <c r="L1" t="s">
+        <v>323</v>
+      </c>
       <c r="M1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>323</v>
+      </c>
+      <c r="N1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>111</v>
       </c>
@@ -10160,22 +10203,15 @@
         <v>113</v>
       </c>
       <c r="F2" s="19">
-        <f>ROUND( VLOOKUP($B2,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A2,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B2,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A2,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.93</v>
       </c>
       <c r="G2" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L2" s="60" t="s">
-        <v>190</v>
-      </c>
-      <c r="M2">
-        <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, $L2)</f>
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -10192,22 +10228,15 @@
         <v>356.5</v>
       </c>
       <c r="F3" s="19">
-        <f>ROUND( VLOOKUP($B3,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A3,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B3,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A3,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.93</v>
       </c>
       <c r="G3" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L3" t="s">
-        <v>191</v>
-      </c>
-      <c r="M3">
-        <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L3)</f>
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -10224,22 +10253,18 @@
         <v>220</v>
       </c>
       <c r="F4" s="19">
-        <f>ROUND( VLOOKUP($B4,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A4,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B4,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A4,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.93</v>
       </c>
       <c r="G4" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L4" s="60" t="s">
-        <v>192</v>
-      </c>
-      <c r="M4">
-        <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L4)</f>
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="M4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -10256,22 +10281,22 @@
         <v>370</v>
       </c>
       <c r="F5" s="19">
-        <f>ROUND( VLOOKUP($B5,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A5,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B5,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A5,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.93</v>
       </c>
       <c r="G5" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L5" t="s">
-        <v>194</v>
+      <c r="L5" s="60" t="s">
+        <v>190</v>
       </c>
       <c r="M5">
-        <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L5)</f>
+        <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, $L5)</f>
         <v>2.6</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>111</v>
       </c>
@@ -10288,22 +10313,22 @@
         <v>1751.6</v>
       </c>
       <c r="F6" s="19">
-        <f>ROUND( VLOOKUP($B6,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A6,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B6,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A6,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.93</v>
       </c>
       <c r="G6" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L6" s="60" t="s">
-        <v>195</v>
+      <c r="L6" t="s">
+        <v>191</v>
       </c>
       <c r="M6">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L6)</f>
         <v>2.6</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -10320,22 +10345,22 @@
         <v>51.2</v>
       </c>
       <c r="F7" s="19">
-        <f>ROUND( VLOOKUP($B7,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A7,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B7,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A7,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.93</v>
       </c>
       <c r="G7" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L7" t="s">
-        <v>198</v>
+      <c r="L7" s="60" t="s">
+        <v>192</v>
       </c>
       <c r="M7">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L7)</f>
         <v>2.6</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>111</v>
       </c>
@@ -10352,22 +10377,22 @@
         <v>17.2</v>
       </c>
       <c r="F8" s="19">
-        <f>ROUND( VLOOKUP($B8,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A8,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B8,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A8,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.93</v>
       </c>
       <c r="G8" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L8" s="60" t="s">
-        <v>199</v>
+      <c r="L8" t="s">
+        <v>194</v>
       </c>
       <c r="M8">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L8)</f>
         <v>2.6</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>111</v>
       </c>
@@ -10384,22 +10409,22 @@
         <v>414.3</v>
       </c>
       <c r="F9" s="19">
-        <f>ROUND( VLOOKUP($B9,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A9,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B9,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A9,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.37</v>
       </c>
       <c r="G9" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L9" t="s">
-        <v>196</v>
+      <c r="L9" s="60" t="s">
+        <v>195</v>
       </c>
       <c r="M9">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L9)</f>
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>111</v>
       </c>
@@ -10416,22 +10441,22 @@
         <v>79.5</v>
       </c>
       <c r="F10" s="19">
-        <f>ROUND( VLOOKUP($B10,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A10,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B10,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A10,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.37</v>
       </c>
       <c r="G10" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L10" s="60" t="s">
-        <v>197</v>
+      <c r="L10" t="s">
+        <v>198</v>
       </c>
       <c r="M10">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L10)</f>
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>111</v>
       </c>
@@ -10448,22 +10473,22 @@
         <v>120</v>
       </c>
       <c r="F11" s="19">
-        <f>ROUND( VLOOKUP($B11,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A11,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B11,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A11,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.37</v>
       </c>
       <c r="G11" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L11" t="s">
-        <v>207</v>
+      <c r="L11" s="60" t="s">
+        <v>199</v>
       </c>
       <c r="M11">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L11)</f>
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>114</v>
       </c>
@@ -10480,22 +10505,22 @@
         <v>1775</v>
       </c>
       <c r="F12" s="19">
-        <f>ROUND( VLOOKUP($B12,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A12,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B12,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A12,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.91</v>
       </c>
       <c r="G12" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L12" s="60" t="s">
-        <v>201</v>
+      <c r="L12" t="s">
+        <v>196</v>
       </c>
       <c r="M12">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L12)</f>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>114</v>
       </c>
@@ -10512,22 +10537,22 @@
         <v>1732.1</v>
       </c>
       <c r="F13" s="19">
-        <f>ROUND( VLOOKUP($B13,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A13,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B13,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A13,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.91</v>
       </c>
       <c r="G13" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L13" t="s">
-        <v>204</v>
+      <c r="L13" s="60" t="s">
+        <v>197</v>
       </c>
       <c r="M13">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L13)</f>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>114</v>
       </c>
@@ -10544,21 +10569,22 @@
         <v>244</v>
       </c>
       <c r="F14" s="19">
-        <f>ROUND( VLOOKUP($B14,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A14,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B14,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A14,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.91</v>
       </c>
       <c r="G14" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L14" s="60" t="s">
-        <v>212</v>
+      <c r="L14" t="s">
+        <v>207</v>
       </c>
       <c r="M14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L14)</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -10575,22 +10601,22 @@
         <v>871</v>
       </c>
       <c r="F15" s="19">
-        <f>ROUND( VLOOKUP($B15,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A15,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B15,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A15,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.35</v>
       </c>
       <c r="G15" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L15" t="s">
-        <v>193</v>
+      <c r="L15" s="60" t="s">
+        <v>201</v>
       </c>
       <c r="M15">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L15)</f>
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -10607,7 +10633,7 @@
         <v>354.4</v>
       </c>
       <c r="F16" s="19">
-        <f>ROUND( VLOOKUP($B16,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A16,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B16,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A16,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.7</v>
       </c>
       <c r="G16" s="19" t="str">
@@ -10615,7 +10641,7 @@
         <v/>
       </c>
       <c r="L16" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="M16">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L16)</f>
@@ -10639,7 +10665,7 @@
         <v>140</v>
       </c>
       <c r="F17" s="19">
-        <f>ROUND( VLOOKUP($B17,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A17,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B17,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A17,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.7</v>
       </c>
       <c r="G17" s="19" t="str">
@@ -10647,11 +10673,10 @@
         <v/>
       </c>
       <c r="L17" s="60" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M17">
-        <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L17)</f>
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -10671,19 +10696,19 @@
         <v>1765.5</v>
       </c>
       <c r="F18" s="19">
-        <f>ROUND( VLOOKUP($B18,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A18,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B18,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A18,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.36</v>
       </c>
       <c r="G18" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L18" s="60" t="s">
-        <v>200</v>
+      <c r="L18" t="s">
+        <v>193</v>
       </c>
       <c r="M18">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L18)</f>
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -10703,15 +10728,15 @@
         <v>311.60000000000002</v>
       </c>
       <c r="F19" s="19">
-        <f>ROUND( VLOOKUP($B19,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A19,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B19,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A19,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.36</v>
       </c>
       <c r="G19" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L19" s="60" t="s">
-        <v>202</v>
+      <c r="L19" t="s">
+        <v>214</v>
       </c>
       <c r="M19">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L19)</f>
@@ -10735,15 +10760,15 @@
         <v>1011.5</v>
       </c>
       <c r="F20" s="19">
-        <f>ROUND( VLOOKUP($B20,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A20,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B20,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A20,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>4.37</v>
       </c>
       <c r="G20" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L20" t="s">
-        <v>203</v>
+      <c r="L20" s="60" t="s">
+        <v>215</v>
       </c>
       <c r="M20">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L20)</f>
@@ -10767,7 +10792,7 @@
         <v>178.5</v>
       </c>
       <c r="F21" s="19">
-        <f>ROUND( VLOOKUP($B21,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A21,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B21,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A21,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>4.37</v>
       </c>
       <c r="G21" s="19" t="str">
@@ -10775,7 +10800,7 @@
         <v/>
       </c>
       <c r="L21" s="60" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="M21">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L21)</f>
@@ -10799,15 +10824,15 @@
         <v>1620.4</v>
       </c>
       <c r="F22" s="19">
-        <f>ROUND( VLOOKUP($B22,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A22,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B22,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A22,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G22" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L22" t="s">
-        <v>211</v>
+      <c r="L22" s="60" t="s">
+        <v>202</v>
       </c>
       <c r="M22">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L22)</f>
@@ -10831,7 +10856,7 @@
         <v>53.6</v>
       </c>
       <c r="F23" s="19">
-        <f>ROUND( VLOOKUP($B23,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A23,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B23,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A23,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G23" s="19" t="str">
@@ -10839,11 +10864,11 @@
         <v/>
       </c>
       <c r="L23" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="M23">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L23)</f>
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -10863,7 +10888,7 @@
         <v>460.4</v>
       </c>
       <c r="F24" s="19">
-        <f>ROUND( VLOOKUP($B24,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A24,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B24,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A24,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G24" s="19" t="str">
@@ -10871,7 +10896,7 @@
         <v/>
       </c>
       <c r="L24" s="60" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M24">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L24)</f>
@@ -10895,15 +10920,15 @@
         <v>1658.6</v>
       </c>
       <c r="F25" s="19">
-        <f>ROUND( VLOOKUP($B25,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A25,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B25,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A25,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G25" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L25" s="60" t="s">
-        <v>210</v>
+      <c r="L25" t="s">
+        <v>211</v>
       </c>
       <c r="M25">
         <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L25)</f>
@@ -10927,18 +10952,19 @@
         <v>18452.900000000001</v>
       </c>
       <c r="F26" s="19">
-        <f>ROUND( VLOOKUP($B26,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A26,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B26,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A26,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G26" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="L26" s="60" t="s">
-        <v>229</v>
+      <c r="L26" t="s">
+        <v>187</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L26)</f>
+        <v>3.2</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -10958,13 +10984,20 @@
         <v>2355.8000000000002</v>
       </c>
       <c r="F27" s="19">
-        <f>ROUND( VLOOKUP($B27,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A27,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B27,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A27,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G27" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
+      <c r="L27" s="60" t="s">
+        <v>206</v>
+      </c>
+      <c r="M27">
+        <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L27)</f>
+        <v>3.3</v>
+      </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
@@ -10983,13 +11016,20 @@
         <v>43.3</v>
       </c>
       <c r="F28" s="19">
-        <f>ROUND( VLOOKUP($B28,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A28,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B28,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A28,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G28" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
+      <c r="L28" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="M28">
+        <f>SUMIFS([1]unittypedata!$S:$S,[1]unittypedata!$C:$C, L28)</f>
+        <v>3.3</v>
+      </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
@@ -11008,13 +11048,19 @@
         <v>109.7</v>
       </c>
       <c r="F29" s="19">
-        <f>ROUND( VLOOKUP($B29,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A29,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B29,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A29,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.33</v>
       </c>
       <c r="G29" s="19" t="str">
         <f>IF(Table3[[#This Row],[capacity_output1]]&lt;10, "remove", "")</f>
         <v/>
       </c>
+      <c r="L29" s="60" t="s">
+        <v>229</v>
+      </c>
+      <c r="M29">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
@@ -11033,7 +11079,7 @@
         <v>945.1</v>
       </c>
       <c r="F30" s="19">
-        <f>ROUND( VLOOKUP($B30,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A30,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B30,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A30,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.33</v>
       </c>
       <c r="G30" s="19" t="str">
@@ -11058,7 +11104,7 @@
         <v>1585.3</v>
       </c>
       <c r="F31" s="19">
-        <f>ROUND( VLOOKUP($B31,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A31,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B31,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A31,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.33</v>
       </c>
       <c r="G31" s="19" t="str">
@@ -11083,7 +11129,7 @@
         <v>57.8</v>
       </c>
       <c r="F32" s="19">
-        <f>ROUND( VLOOKUP($B32,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A32,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B32,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A32,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.25</v>
       </c>
       <c r="G32" s="19" t="str">
@@ -11108,7 +11154,7 @@
         <v>54.6</v>
       </c>
       <c r="F33" s="19">
-        <f>ROUND( VLOOKUP($B33,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A33,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B33,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A33,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.25</v>
       </c>
       <c r="G33" s="19" t="str">
@@ -11133,7 +11179,7 @@
         <v>72</v>
       </c>
       <c r="F34" s="19">
-        <f>ROUND( VLOOKUP($B34,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A34,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B34,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A34,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.25</v>
       </c>
       <c r="G34" s="19" t="str">
@@ -11158,7 +11204,7 @@
         <v>103.1</v>
       </c>
       <c r="F35" s="19">
-        <f>ROUND( VLOOKUP($B35,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A35,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B35,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A35,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.25</v>
       </c>
       <c r="G35" s="19" t="str">
@@ -11183,7 +11229,7 @@
         <v>1165.5</v>
       </c>
       <c r="F36" s="19">
-        <f>ROUND( VLOOKUP($B36,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A36,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B36,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A36,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>4.13</v>
       </c>
       <c r="G36" s="19" t="str">
@@ -11208,7 +11254,7 @@
         <v>65.099999999999994</v>
       </c>
       <c r="F37" s="19">
-        <f>ROUND( VLOOKUP($B37,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A37,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B37,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A37,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>4.13</v>
       </c>
       <c r="G37" s="19" t="str">
@@ -11233,7 +11279,7 @@
         <v>531</v>
       </c>
       <c r="F38" s="19">
-        <f>ROUND( VLOOKUP($B38,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A38,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B38,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A38,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.63</v>
       </c>
       <c r="G38" s="19" t="str">
@@ -11258,7 +11304,7 @@
         <v>47.2</v>
       </c>
       <c r="F39" s="19">
-        <f>ROUND( VLOOKUP($B39,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A39,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B39,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A39,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.22</v>
       </c>
       <c r="G39" s="19" t="str">
@@ -11283,7 +11329,7 @@
         <v>54.3</v>
       </c>
       <c r="F40" s="19">
-        <f>ROUND( VLOOKUP($B40,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A40,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B40,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A40,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.22</v>
       </c>
       <c r="G40" s="19" t="str">
@@ -11308,7 +11354,7 @@
         <v>129.6</v>
       </c>
       <c r="F41" s="19">
-        <f>ROUND( VLOOKUP($B41,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A41,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B41,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A41,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.22</v>
       </c>
       <c r="G41" s="19" t="str">
@@ -11333,7 +11379,7 @@
         <v>69.7</v>
       </c>
       <c r="F42" s="19">
-        <f>ROUND( VLOOKUP($B42,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A42,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B42,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A42,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.22</v>
       </c>
       <c r="G42" s="19" t="str">
@@ -11358,7 +11404,7 @@
         <v>448.2</v>
       </c>
       <c r="F43" s="19">
-        <f>ROUND( VLOOKUP($B43,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A43,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B43,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A43,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.22</v>
       </c>
       <c r="G43" s="19" t="str">
@@ -11383,7 +11429,7 @@
         <v>111.7</v>
       </c>
       <c r="F44" s="19">
-        <f>ROUND( VLOOKUP($B44,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A44,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B44,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A44,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.6</v>
       </c>
       <c r="G44" s="19" t="str">
@@ -11408,7 +11454,7 @@
         <v>375.4</v>
       </c>
       <c r="F45" s="19">
-        <f>ROUND( VLOOKUP($B45,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A45,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B45,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A45,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.6</v>
       </c>
       <c r="G45" s="19" t="str">
@@ -11433,7 +11479,7 @@
         <v>778.1</v>
       </c>
       <c r="F46" s="19">
-        <f>ROUND( VLOOKUP($B46,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A46,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B46,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A46,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>4.09</v>
       </c>
       <c r="G46" s="19" t="str">
@@ -11458,7 +11504,7 @@
         <v>165.8</v>
       </c>
       <c r="F47" s="19">
-        <f>ROUND( VLOOKUP($B47,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A47,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B47,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A47,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.6</v>
       </c>
       <c r="G47" s="19" t="str">
@@ -11483,7 +11529,7 @@
         <v>250</v>
       </c>
       <c r="F48" s="19">
-        <f>ROUND( VLOOKUP($B48,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A48,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B48,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A48,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.0699999999999998</v>
       </c>
       <c r="G48" s="19" t="str">
@@ -11508,7 +11554,7 @@
         <v>658</v>
       </c>
       <c r="F49" s="19">
-        <f>ROUND( VLOOKUP($B49,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A49,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B49,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A49,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.63</v>
       </c>
       <c r="G49" s="19" t="str">
@@ -11533,7 +11579,7 @@
         <v>173</v>
       </c>
       <c r="F50" s="19">
-        <f>ROUND( VLOOKUP($B50,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A50,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B50,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A50,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.63</v>
       </c>
       <c r="G50" s="19" t="str">
@@ -11558,7 +11604,7 @@
         <v>24498</v>
       </c>
       <c r="F51" s="19">
-        <f>ROUND( VLOOKUP($B51,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A51,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B51,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A51,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.38</v>
       </c>
       <c r="G51" s="19" t="str">
@@ -11583,7 +11629,7 @@
         <v>4335.3</v>
       </c>
       <c r="F52" s="19">
-        <f>ROUND( VLOOKUP($B52,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A52,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B52,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A52,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.75</v>
       </c>
       <c r="G52" s="19" t="str">
@@ -11608,7 +11654,7 @@
         <v>765.1</v>
       </c>
       <c r="F53" s="19">
-        <f>ROUND( VLOOKUP($B53,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A53,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B53,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A53,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.75</v>
       </c>
       <c r="G53" s="19" t="str">
@@ -11633,7 +11679,7 @@
         <v>45</v>
       </c>
       <c r="F54" s="19">
-        <f>ROUND( VLOOKUP($B54,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A54,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B54,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A54,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G54" s="19" t="str">
@@ -11658,7 +11704,7 @@
         <v>640</v>
       </c>
       <c r="F55" s="19">
-        <f>ROUND( VLOOKUP($B55,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A55,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B55,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A55,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G55" s="19" t="str">
@@ -11683,7 +11729,7 @@
         <v>234</v>
       </c>
       <c r="F56" s="19">
-        <f>ROUND( VLOOKUP($B56,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A56,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B56,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A56,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G56" s="19" t="str">
@@ -11708,7 +11754,7 @@
         <v>87</v>
       </c>
       <c r="F57" s="19">
-        <f>ROUND( VLOOKUP($B57,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A57,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B57,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A57,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G57" s="19" t="str">
@@ -11733,7 +11779,7 @@
         <v>38</v>
       </c>
       <c r="F58" s="19">
-        <f>ROUND( VLOOKUP($B58,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A58,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B58,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A58,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.88</v>
       </c>
       <c r="G58" s="19" t="str">
@@ -11758,7 +11804,7 @@
         <v>1196</v>
       </c>
       <c r="F59" s="19">
-        <f>ROUND( VLOOKUP($B59,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A59,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B59,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A59,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.66</v>
       </c>
       <c r="G59" s="19" t="str">
@@ -11783,7 +11829,7 @@
         <v>3734.9</v>
       </c>
       <c r="F60" s="19">
-        <f>ROUND( VLOOKUP($B60,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A60,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B60,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A60,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.32</v>
       </c>
       <c r="G60" s="19" t="str">
@@ -11808,7 +11854,7 @@
         <v>659.1</v>
       </c>
       <c r="F61" s="19">
-        <f>ROUND( VLOOKUP($B61,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A61,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B61,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A61,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.32</v>
       </c>
       <c r="G61" s="19" t="str">
@@ -11833,7 +11879,7 @@
         <v>414</v>
       </c>
       <c r="F62" s="19">
-        <f>ROUND( VLOOKUP($B62,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A62,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B62,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A62,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.74</v>
       </c>
       <c r="G62" s="19" t="str">
@@ -11858,7 +11904,7 @@
         <v>792</v>
       </c>
       <c r="F63" s="19">
-        <f>ROUND( VLOOKUP($B63,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A63,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B63,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A63,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.74</v>
       </c>
       <c r="G63" s="19" t="str">
@@ -11883,7 +11929,7 @@
         <v>5347</v>
       </c>
       <c r="F64" s="19">
-        <f>ROUND( VLOOKUP($B64,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A64,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B64,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A64,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.74</v>
       </c>
       <c r="G64" s="19" t="str">
@@ -11908,7 +11954,7 @@
         <v>437</v>
       </c>
       <c r="F65" s="19">
-        <f>ROUND( VLOOKUP($B65,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A65,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B65,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A65,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.74</v>
       </c>
       <c r="G65" s="19" t="str">
@@ -11933,7 +11979,7 @@
         <v>199</v>
       </c>
       <c r="F66" s="19">
-        <f>ROUND( VLOOKUP($B66,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A66,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B66,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A66,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.74</v>
       </c>
       <c r="G66" s="19" t="str">
@@ -11958,7 +12004,7 @@
         <v>1255</v>
       </c>
       <c r="F67" s="19">
-        <f>ROUND( VLOOKUP($B67,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A67,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B67,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A67,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.21</v>
       </c>
       <c r="G67" s="19" t="str">
@@ -11983,7 +12029,7 @@
         <v>24704.400000000001</v>
       </c>
       <c r="F68" s="19">
-        <f>ROUND( VLOOKUP($B68,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A68,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B68,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A68,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.16</v>
       </c>
       <c r="G68" s="19" t="str">
@@ -12008,7 +12054,7 @@
         <v>37056.6</v>
       </c>
       <c r="F69" s="19">
-        <f>ROUND( VLOOKUP($B69,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A69,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B69,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A69,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.16</v>
       </c>
       <c r="G69" s="19" t="str">
@@ -12033,7 +12079,7 @@
         <v>510</v>
       </c>
       <c r="F70" s="19">
-        <f>ROUND( VLOOKUP($B70,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A70,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B70,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A70,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>1.99</v>
       </c>
       <c r="G70" s="19" t="str">
@@ -12058,7 +12104,7 @@
         <v>403</v>
       </c>
       <c r="F71" s="19">
-        <f>ROUND( VLOOKUP($B71,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A71,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B71,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A71,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>1.99</v>
       </c>
       <c r="G71" s="19" t="str">
@@ -12083,7 +12129,7 @@
         <v>110</v>
       </c>
       <c r="F72" s="19">
-        <f>ROUND( VLOOKUP($B72,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A72,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B72,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A72,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>1.61</v>
       </c>
       <c r="G72" s="19" t="str">
@@ -12108,7 +12154,7 @@
         <v>1004</v>
       </c>
       <c r="F73" s="19">
-        <f>ROUND( VLOOKUP($B73,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A73,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B73,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A73,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>1.82</v>
       </c>
       <c r="G73" s="19" t="str">
@@ -12133,7 +12179,7 @@
         <v>73</v>
       </c>
       <c r="F74" s="19">
-        <f>ROUND( VLOOKUP($B74,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A74,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B74,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A74,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>1.82</v>
       </c>
       <c r="G74" s="19" t="str">
@@ -12158,7 +12204,7 @@
         <v>2536.5</v>
       </c>
       <c r="F75" s="19">
-        <f>ROUND( VLOOKUP($B75,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A75,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B75,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A75,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.07</v>
       </c>
       <c r="G75" s="19" t="str">
@@ -12183,7 +12229,7 @@
         <v>7083</v>
       </c>
       <c r="F76" s="19">
-        <f>ROUND( VLOOKUP($B76,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A76,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B76,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A76,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.07</v>
       </c>
       <c r="G76" s="19" t="str">
@@ -12208,7 +12254,7 @@
         <v>314</v>
       </c>
       <c r="F77" s="19">
-        <f>ROUND( VLOOKUP($B77,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A77,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B77,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A77,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.07</v>
       </c>
       <c r="G77" s="19" t="str">
@@ -12233,7 +12279,7 @@
         <v>165</v>
       </c>
       <c r="F78" s="19">
-        <f>ROUND( VLOOKUP($B78,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A78,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B78,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A78,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.07</v>
       </c>
       <c r="G78" s="19" t="str">
@@ -12258,7 +12304,7 @@
         <v>413.1</v>
       </c>
       <c r="F79" s="19">
-        <f>ROUND( VLOOKUP($B79,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A79,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B79,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A79,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.54</v>
       </c>
       <c r="G79" s="19" t="str">
@@ -12283,7 +12329,7 @@
         <v>72.900000000000006</v>
       </c>
       <c r="F80" s="19">
-        <f>ROUND( VLOOKUP($B80,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A80,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B80,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A80,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.54</v>
       </c>
       <c r="G80" s="19" t="str">
@@ -12308,7 +12354,7 @@
         <v>9620.7000000000007</v>
       </c>
       <c r="F81" s="19">
-        <f>ROUND( VLOOKUP($B81,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A81,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B81,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A81,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>1.79</v>
       </c>
       <c r="G81" s="19" t="str">
@@ -12333,7 +12379,7 @@
         <v>1663</v>
       </c>
       <c r="F82" s="19">
-        <f>ROUND( VLOOKUP($B82,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A82,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B82,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A82,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.2799999999999998</v>
       </c>
       <c r="G82" s="19" t="str">
@@ -12358,7 +12404,7 @@
         <v>3305.5</v>
       </c>
       <c r="F83" s="19">
-        <f>ROUND( VLOOKUP($B83,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A83,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B83,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A83,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.2799999999999998</v>
       </c>
       <c r="G83" s="19" t="str">
@@ -12383,7 +12429,7 @@
         <v>5466.6</v>
       </c>
       <c r="F84" s="19">
-        <f>ROUND( VLOOKUP($B84,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A84,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B84,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A84,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.2799999999999998</v>
       </c>
       <c r="G84" s="19" t="str">
@@ -12408,7 +12454,7 @@
         <v>1872.1</v>
       </c>
       <c r="F85" s="19">
-        <f>ROUND( VLOOKUP($B85,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A85,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B85,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A85,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.2799999999999998</v>
       </c>
       <c r="G85" s="19" t="str">
@@ -12433,7 +12479,7 @@
         <v>4696</v>
       </c>
       <c r="F86" s="19">
-        <f>ROUND( VLOOKUP($B86,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A86,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B86,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A86,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.2799999999999998</v>
       </c>
       <c r="G86" s="19" t="str">
@@ -12458,7 +12504,7 @@
         <v>1824</v>
       </c>
       <c r="F87" s="19">
-        <f>ROUND( VLOOKUP($B87,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A87,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B87,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A87,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.2799999999999998</v>
       </c>
       <c r="G87" s="19" t="str">
@@ -12483,7 +12529,7 @@
         <v>97</v>
       </c>
       <c r="F88" s="19">
-        <f>ROUND( VLOOKUP($B88,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A88,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B88,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A88,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.07</v>
       </c>
       <c r="G88" s="19" t="str">
@@ -12508,7 +12554,7 @@
         <v>54</v>
       </c>
       <c r="F89" s="19">
-        <f>ROUND( VLOOKUP($B89,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A89,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B89,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A89,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.03</v>
       </c>
       <c r="G89" s="19" t="str">
@@ -12533,7 +12579,7 @@
         <v>5850.6</v>
       </c>
       <c r="F90" s="19">
-        <f>ROUND( VLOOKUP($B90,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A90,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B90,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A90,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.5</v>
       </c>
       <c r="G90" s="19" t="str">
@@ -12558,7 +12604,7 @@
         <v>1032.5</v>
       </c>
       <c r="F91" s="19">
-        <f>ROUND( VLOOKUP($B91,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A91,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B91,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A91,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.5</v>
       </c>
       <c r="G91" s="19" t="str">
@@ -12583,7 +12629,7 @@
         <v>4300</v>
       </c>
       <c r="F92" s="19">
-        <f>ROUND( VLOOKUP($B92,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A92,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B92,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A92,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.03</v>
       </c>
       <c r="G92" s="19" t="str">
@@ -12608,7 +12654,7 @@
         <v>539</v>
       </c>
       <c r="F93" s="19">
-        <f>ROUND( VLOOKUP($B93,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A93,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B93,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A93,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.03</v>
       </c>
       <c r="G93" s="19" t="str">
@@ -12633,7 +12679,7 @@
         <v>21988.5</v>
       </c>
       <c r="F94" s="19">
-        <f>ROUND( VLOOKUP($B94,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A94,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B94,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A94,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.03</v>
       </c>
       <c r="G94" s="19" t="str">
@@ -12658,7 +12704,7 @@
         <v>408</v>
       </c>
       <c r="F95" s="19">
-        <f>ROUND( VLOOKUP($B95,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A95,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B95,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A95,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.03</v>
       </c>
       <c r="G95" s="19" t="str">
@@ -12683,7 +12729,7 @@
         <v>2456.9</v>
       </c>
       <c r="F96" s="19">
-        <f>ROUND( VLOOKUP($B96,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A96,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B96,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A96,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.03</v>
       </c>
       <c r="G96" s="19" t="str">
@@ -12708,7 +12754,7 @@
         <v>2448.6999999999998</v>
       </c>
       <c r="F97" s="19">
-        <f>ROUND( VLOOKUP($B97,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A97,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B97,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A97,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.4500000000000002</v>
       </c>
       <c r="G97" s="19" t="str">
@@ -12733,7 +12779,7 @@
         <v>5062.1000000000004</v>
       </c>
       <c r="F98" s="19">
-        <f>ROUND( VLOOKUP($B98,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A98,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B98,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A98,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.4500000000000002</v>
       </c>
       <c r="G98" s="19" t="str">
@@ -12758,7 +12804,7 @@
         <v>204.7</v>
       </c>
       <c r="F99" s="19">
-        <f>ROUND( VLOOKUP($B99,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A99,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B99,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A99,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.84</v>
       </c>
       <c r="G99" s="19" t="str">
@@ -12783,7 +12829,7 @@
         <v>70.8</v>
       </c>
       <c r="F100" s="19">
-        <f>ROUND( VLOOKUP($B100,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A100,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B100,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A100,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.84</v>
       </c>
       <c r="G100" s="19" t="str">
@@ -12808,7 +12854,7 @@
         <v>389</v>
       </c>
       <c r="F101" s="19">
-        <f>ROUND( VLOOKUP($B101,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A101,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B101,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A101,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>2.4500000000000002</v>
       </c>
       <c r="G101" s="19" t="str">
@@ -12833,7 +12879,7 @@
         <v>18</v>
       </c>
       <c r="F102" s="19">
-        <f>ROUND( VLOOKUP($B102,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A102,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B102,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A102,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.84</v>
       </c>
       <c r="G102" s="19" t="str">
@@ -12858,7 +12904,7 @@
         <v>4683.5</v>
       </c>
       <c r="F103" s="19">
-        <f>ROUND( VLOOKUP($B103,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A103,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B103,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A103,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.5</v>
       </c>
       <c r="G103" s="19" t="str">
@@ -12883,7 +12929,7 @@
         <v>826.5</v>
       </c>
       <c r="F104" s="19">
-        <f>ROUND( VLOOKUP($B104,$L$2:$M$26, 2, FALSE) * (1+ VLOOKUP($A104,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
+        <f>ROUND( VLOOKUP($B104,$L$5:$M$29, 2, FALSE) * (1+ VLOOKUP($A104,'vomcost mult'!$N$10:$R$32,5, FALSE)), 2)</f>
         <v>3.5</v>
       </c>
       <c r="G104" s="19" t="str">
@@ -12945,10 +12991,85 @@
       <c r="G1" s="71" t="s">
         <v>167</v>
       </c>
+      <c r="I1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J1" t="s">
+        <v>323</v>
+      </c>
+      <c r="K1" t="s">
+        <v>323</v>
+      </c>
+      <c r="L1" t="s">
+        <v>323</v>
+      </c>
+      <c r="M1" t="s">
+        <v>323</v>
+      </c>
+      <c r="N1" t="s">
+        <v>323</v>
+      </c>
+      <c r="O1" t="s">
+        <v>323</v>
+      </c>
+      <c r="P1" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>323</v>
+      </c>
+      <c r="R1" t="s">
+        <v>323</v>
+      </c>
+      <c r="S1" t="s">
+        <v>323</v>
+      </c>
+      <c r="T1" t="s">
+        <v>323</v>
+      </c>
+      <c r="U1" t="s">
+        <v>323</v>
+      </c>
+      <c r="V1" t="s">
+        <v>323</v>
+      </c>
+      <c r="W1" t="s">
+        <v>323</v>
+      </c>
+      <c r="X1" t="s">
+        <v>323</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>323</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="2" spans="1:33">
       <c r="A2" s="17" t="s">
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
@@ -14829,7 +14950,7 @@
     </row>
     <row r="25" spans="1:33">
       <c r="A25" s="17" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
@@ -15672,7 +15793,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="17" t="s">
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="C48" s="19"/>
       <c r="D48" s="19"/>
@@ -16265,7 +16386,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:Q93"/>
+  <dimension ref="A1:Q94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="73" bestFit="1" customWidth="1"/>
@@ -16307,13 +16428,19 @@
         <v>167</v>
       </c>
       <c r="M1" t="s">
-        <v>278</v>
+        <v>323</v>
+      </c>
+      <c r="N1" t="s">
+        <v>323</v>
+      </c>
+      <c r="O1" t="s">
+        <v>323</v>
       </c>
       <c r="P1" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="Q1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -16336,24 +16463,21 @@
         <v>1200</v>
       </c>
       <c r="G2" s="19">
-        <f>M2</f>
+        <f>M3</f>
         <v>2.6399999999999997</v>
       </c>
       <c r="I2" s="19" t="str">
         <f>IF(Table6[[#This Row],[transferCap]]&lt;10, "remove", "")</f>
         <v/>
       </c>
-      <c r="M2">
-        <f>ROUND(P2*Q2, 2)+1</f>
-        <v>2.6399999999999997</v>
-      </c>
-      <c r="P2">
-        <f>(1+ VLOOKUP($B2,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1280000000000001</v>
-      </c>
-      <c r="Q2">
-        <f>(1+ VLOOKUP($C2,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.456</v>
+      <c r="M2" t="s">
+        <v>275</v>
+      </c>
+      <c r="P2" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -16376,7 +16500,7 @@
         <v>1200</v>
       </c>
       <c r="G3" s="19">
-        <f t="shared" ref="G3:G66" si="0">M3</f>
+        <f t="shared" ref="G3:G66" si="0">M4</f>
         <v>2.6399999999999997</v>
       </c>
       <c r="I3" s="19" t="str">
@@ -16384,16 +16508,16 @@
         <v/>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M66" si="1">ROUND(P3*Q3, 2)+1</f>
+        <f>ROUND(P3*Q3, 2)+1</f>
         <v>2.6399999999999997</v>
       </c>
       <c r="P3">
-        <f>(1+ VLOOKUP($B3,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B2,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1280000000000001</v>
+      </c>
+      <c r="Q3">
+        <f>(1+ VLOOKUP($C2,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.456</v>
-      </c>
-      <c r="Q3">
-        <f>(1+ VLOOKUP($C3,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1280000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -16424,16 +16548,16 @@
         <v/>
       </c>
       <c r="M4">
-        <f t="shared" si="1"/>
-        <v>2.25</v>
+        <f t="shared" ref="M4:M67" si="1">ROUND(P4*Q4, 2)+1</f>
+        <v>2.6399999999999997</v>
       </c>
       <c r="P4">
-        <f>(1+ VLOOKUP($B4,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B3,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.456</v>
+      </c>
+      <c r="Q4">
+        <f>(1+ VLOOKUP($C3,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1280000000000001</v>
-      </c>
-      <c r="Q4">
-        <f>(1+ VLOOKUP($C4,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -16468,12 +16592,12 @@
         <v>2.25</v>
       </c>
       <c r="P5">
-        <f>(1+ VLOOKUP($B5,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B4,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1280000000000001</v>
+      </c>
+      <c r="Q5">
+        <f>(1+ VLOOKUP($C4,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q5">
-        <f>(1+ VLOOKUP($C5,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1280000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -16505,15 +16629,15 @@
       </c>
       <c r="M6">
         <f t="shared" si="1"/>
-        <v>2.2400000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="P6">
-        <f>(1+ VLOOKUP($B6,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.121</v>
+        <f>(1+ VLOOKUP($B5,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
       </c>
       <c r="Q6">
-        <f>(1+ VLOOKUP($C6,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
+        <f>(1+ VLOOKUP($C5,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1280000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -16548,12 +16672,12 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="P7">
-        <f>(1+ VLOOKUP($B7,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B6,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.121</v>
+      </c>
+      <c r="Q7">
+        <f>(1+ VLOOKUP($C6,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q7">
-        <f>(1+ VLOOKUP($C7,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.121</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -16585,15 +16709,15 @@
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>2.1799999999999997</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="P8">
-        <f>(1+ VLOOKUP($B8,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B7,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q8">
+        <f>(1+ VLOOKUP($C7,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.121</v>
-      </c>
-      <c r="Q8">
-        <f>(1+ VLOOKUP($C8,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.054</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -16628,12 +16752,12 @@
         <v>2.1799999999999997</v>
       </c>
       <c r="P9">
-        <f>(1+ VLOOKUP($B9,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B8,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.121</v>
+      </c>
+      <c r="Q9">
+        <f>(1+ VLOOKUP($C8,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.054</v>
-      </c>
-      <c r="Q9">
-        <f>(1+ VLOOKUP($C9,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.121</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -16665,15 +16789,15 @@
       </c>
       <c r="M10">
         <f t="shared" si="1"/>
-        <v>2.3200000000000003</v>
+        <v>2.1799999999999997</v>
       </c>
       <c r="P10">
-        <f>(1+ VLOOKUP($B10,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B9,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.054</v>
+      </c>
+      <c r="Q10">
+        <f>(1+ VLOOKUP($C9,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.121</v>
-      </c>
-      <c r="Q10">
-        <f>(1+ VLOOKUP($C10,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.18</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -16708,12 +16832,12 @@
         <v>2.3200000000000003</v>
       </c>
       <c r="P11">
-        <f>(1+ VLOOKUP($B11,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B10,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.121</v>
+      </c>
+      <c r="Q11">
+        <f>(1+ VLOOKUP($C10,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.18</v>
-      </c>
-      <c r="Q11">
-        <f>(1+ VLOOKUP($C11,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.121</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -16745,15 +16869,15 @@
       </c>
       <c r="M12">
         <f t="shared" si="1"/>
-        <v>2.31</v>
+        <v>2.3200000000000003</v>
       </c>
       <c r="P12">
-        <f>(1+ VLOOKUP($B12,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B11,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.18</v>
+      </c>
+      <c r="Q12">
+        <f>(1+ VLOOKUP($C11,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.121</v>
-      </c>
-      <c r="Q12">
-        <f>(1+ VLOOKUP($C12,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.165</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -16788,12 +16912,12 @@
         <v>2.31</v>
       </c>
       <c r="P13">
-        <f>(1+ VLOOKUP($B13,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B12,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.121</v>
+      </c>
+      <c r="Q13">
+        <f>(1+ VLOOKUP($C12,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
-      </c>
-      <c r="Q13">
-        <f>(1+ VLOOKUP($C13,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.121</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -16825,15 +16949,15 @@
       </c>
       <c r="M14">
         <f t="shared" si="1"/>
-        <v>2.6100000000000003</v>
+        <v>2.31</v>
       </c>
       <c r="P14">
-        <f>(1+ VLOOKUP($B14,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.456</v>
+        <f>(1+ VLOOKUP($B13,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.165</v>
       </c>
       <c r="Q14">
-        <f>(1+ VLOOKUP($C14,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
+        <f>(1+ VLOOKUP($C13,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.121</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -16868,12 +16992,12 @@
         <v>2.6100000000000003</v>
       </c>
       <c r="P15">
-        <f>(1+ VLOOKUP($B15,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B14,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.456</v>
+      </c>
+      <c r="Q15">
+        <f>(1+ VLOOKUP($C14,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q15">
-        <f>(1+ VLOOKUP($C15,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.456</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -16905,15 +17029,15 @@
       </c>
       <c r="M16">
         <f t="shared" si="1"/>
-        <v>2.5300000000000002</v>
+        <v>2.6100000000000003</v>
       </c>
       <c r="P16">
-        <f>(1+ VLOOKUP($B16,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B15,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q16">
+        <f>(1+ VLOOKUP($C15,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.456</v>
-      </c>
-      <c r="Q16">
-        <f>(1+ VLOOKUP($C16,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.054</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -16948,12 +17072,12 @@
         <v>2.5300000000000002</v>
       </c>
       <c r="P17">
-        <f>(1+ VLOOKUP($B17,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B16,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.456</v>
+      </c>
+      <c r="Q17">
+        <f>(1+ VLOOKUP($C16,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.054</v>
-      </c>
-      <c r="Q17">
-        <f>(1+ VLOOKUP($C17,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.456</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -16985,15 +17109,15 @@
       </c>
       <c r="M18">
         <f t="shared" si="1"/>
-        <v>2.3899999999999997</v>
+        <v>2.5300000000000002</v>
       </c>
       <c r="P18">
-        <f>(1+ VLOOKUP($B18,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
+        <f>(1+ VLOOKUP($B17,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.054</v>
       </c>
       <c r="Q18">
-        <f>(1+ VLOOKUP($C18,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.25</v>
+        <f>(1+ VLOOKUP($C17,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.456</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -17028,12 +17152,12 @@
         <v>2.3899999999999997</v>
       </c>
       <c r="P19">
-        <f>(1+ VLOOKUP($B19,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B18,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q19">
+        <f>(1+ VLOOKUP($C18,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.25</v>
-      </c>
-      <c r="Q19">
-        <f>(1+ VLOOKUP($C19,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -17065,15 +17189,15 @@
       </c>
       <c r="M20">
         <f t="shared" si="1"/>
-        <v>2.37</v>
+        <v>2.3899999999999997</v>
       </c>
       <c r="P20">
-        <f>(1+ VLOOKUP($B20,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B19,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q20">
+        <f>(1+ VLOOKUP($C19,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q20">
-        <f>(1+ VLOOKUP($C20,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.238</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -17108,12 +17232,12 @@
         <v>2.37</v>
       </c>
       <c r="P21">
-        <f>(1+ VLOOKUP($B21,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B20,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q21">
+        <f>(1+ VLOOKUP($C20,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.238</v>
-      </c>
-      <c r="Q21">
-        <f>(1+ VLOOKUP($C21,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -17145,15 +17269,15 @@
       </c>
       <c r="M22">
         <f t="shared" si="1"/>
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="P22">
-        <f>(1+ VLOOKUP($B22,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B21,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.238</v>
+      </c>
+      <c r="Q22">
+        <f>(1+ VLOOKUP($C21,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q22">
-        <f>(1+ VLOOKUP($C22,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.054</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -17188,12 +17312,12 @@
         <v>2.17</v>
       </c>
       <c r="P23">
-        <f>(1+ VLOOKUP($B23,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B22,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q23">
+        <f>(1+ VLOOKUP($C22,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.054</v>
-      </c>
-      <c r="Q23">
-        <f>(1+ VLOOKUP($C23,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -17225,15 +17349,15 @@
       </c>
       <c r="M24">
         <f t="shared" si="1"/>
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="P24">
-        <f>(1+ VLOOKUP($B24,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B23,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.054</v>
+      </c>
+      <c r="Q24">
+        <f>(1+ VLOOKUP($C23,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q24">
-        <f>(1+ VLOOKUP($C24,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.18</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -17268,12 +17392,12 @@
         <v>2.31</v>
       </c>
       <c r="P25">
-        <f>(1+ VLOOKUP($B25,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B24,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q25">
+        <f>(1+ VLOOKUP($C24,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.18</v>
-      </c>
-      <c r="Q25">
-        <f>(1+ VLOOKUP($C25,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -17305,15 +17429,15 @@
       </c>
       <c r="M26">
         <f t="shared" si="1"/>
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="P26">
-        <f>(1+ VLOOKUP($B26,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B25,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.18</v>
+      </c>
+      <c r="Q26">
+        <f>(1+ VLOOKUP($C25,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q26">
-        <f>(1+ VLOOKUP($C26,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.296</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -17348,12 +17472,12 @@
         <v>2.44</v>
       </c>
       <c r="P27">
-        <f>(1+ VLOOKUP($B27,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B26,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q27">
+        <f>(1+ VLOOKUP($C26,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.296</v>
-      </c>
-      <c r="Q27">
-        <f>(1+ VLOOKUP($C27,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -17385,15 +17509,15 @@
       </c>
       <c r="M28">
         <f t="shared" si="1"/>
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="P28">
-        <f>(1+ VLOOKUP($B28,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B27,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.296</v>
+      </c>
+      <c r="Q28">
+        <f>(1+ VLOOKUP($C27,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q28">
-        <f>(1+ VLOOKUP($C28,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.69</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -17428,12 +17552,12 @@
         <v>1.76</v>
       </c>
       <c r="P29">
-        <f>(1+ VLOOKUP($B29,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B28,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q29">
+        <f>(1+ VLOOKUP($C28,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>0.69</v>
-      </c>
-      <c r="Q29">
-        <f>(1+ VLOOKUP($C29,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -17465,15 +17589,15 @@
       </c>
       <c r="M30">
         <f t="shared" si="1"/>
-        <v>2.2800000000000002</v>
+        <v>1.76</v>
       </c>
       <c r="P30">
-        <f>(1+ VLOOKUP($B30,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B29,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.69</v>
+      </c>
+      <c r="Q30">
+        <f>(1+ VLOOKUP($C29,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q30">
-        <f>(1+ VLOOKUP($C30,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.157</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -17508,12 +17632,12 @@
         <v>2.2800000000000002</v>
       </c>
       <c r="P31">
-        <f>(1+ VLOOKUP($B31,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B30,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q31">
+        <f>(1+ VLOOKUP($C30,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.157</v>
-      </c>
-      <c r="Q31">
-        <f>(1+ VLOOKUP($C31,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -17545,15 +17669,15 @@
       </c>
       <c r="M32">
         <f t="shared" si="1"/>
-        <v>2.29</v>
+        <v>2.2800000000000002</v>
       </c>
       <c r="P32">
-        <f>(1+ VLOOKUP($B32,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B31,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.157</v>
+      </c>
+      <c r="Q32">
+        <f>(1+ VLOOKUP($C31,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q32">
-        <f>(1+ VLOOKUP($C32,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.165</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -17588,12 +17712,12 @@
         <v>2.29</v>
       </c>
       <c r="P33">
-        <f>(1+ VLOOKUP($B33,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B32,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q33">
+        <f>(1+ VLOOKUP($C32,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
-      </c>
-      <c r="Q33">
-        <f>(1+ VLOOKUP($C33,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -17625,15 +17749,15 @@
       </c>
       <c r="M34">
         <f t="shared" si="1"/>
-        <v>2.5499999999999998</v>
+        <v>2.29</v>
       </c>
       <c r="P34">
-        <f>(1+ VLOOKUP($B34,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.25</v>
+        <f>(1+ VLOOKUP($B33,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.165</v>
       </c>
       <c r="Q34">
-        <f>(1+ VLOOKUP($C34,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.238</v>
+        <f>(1+ VLOOKUP($C33,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -17668,12 +17792,12 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="P35">
-        <f>(1+ VLOOKUP($B35,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B34,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q35">
+        <f>(1+ VLOOKUP($C34,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.238</v>
-      </c>
-      <c r="Q35">
-        <f>(1+ VLOOKUP($C35,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.25</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -17705,15 +17829,15 @@
       </c>
       <c r="M36">
         <f t="shared" si="1"/>
-        <v>1.8599999999999999</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="P36">
-        <f>(1+ VLOOKUP($B36,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B35,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.238</v>
+      </c>
+      <c r="Q36">
+        <f>(1+ VLOOKUP($C35,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.25</v>
-      </c>
-      <c r="Q36">
-        <f>(1+ VLOOKUP($C36,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.69</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -17748,12 +17872,12 @@
         <v>1.8599999999999999</v>
       </c>
       <c r="P37">
-        <f>(1+ VLOOKUP($B37,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B36,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q37">
+        <f>(1+ VLOOKUP($C36,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>0.69</v>
-      </c>
-      <c r="Q37">
-        <f>(1+ VLOOKUP($C37,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.25</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -17785,15 +17909,15 @@
       </c>
       <c r="M38">
         <f t="shared" si="1"/>
-        <v>2.4500000000000002</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="P38">
-        <f>(1+ VLOOKUP($B38,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B37,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.69</v>
+      </c>
+      <c r="Q38">
+        <f>(1+ VLOOKUP($C37,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.25</v>
-      </c>
-      <c r="Q38">
-        <f>(1+ VLOOKUP($C38,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.157</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -17828,12 +17952,12 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="P39">
-        <f>(1+ VLOOKUP($B39,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B38,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q39">
+        <f>(1+ VLOOKUP($C38,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.157</v>
-      </c>
-      <c r="Q39">
-        <f>(1+ VLOOKUP($C39,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.25</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -17865,15 +17989,15 @@
       </c>
       <c r="M40">
         <f t="shared" si="1"/>
-        <v>2.46</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="P40">
-        <f>(1+ VLOOKUP($B40,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.238</v>
+        <f>(1+ VLOOKUP($B39,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.157</v>
       </c>
       <c r="Q40">
-        <f>(1+ VLOOKUP($C40,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.18</v>
+        <f>(1+ VLOOKUP($C39,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -17908,12 +18032,12 @@
         <v>2.46</v>
       </c>
       <c r="P41">
-        <f>(1+ VLOOKUP($B41,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B40,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.238</v>
+      </c>
+      <c r="Q41">
+        <f>(1+ VLOOKUP($C40,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.18</v>
-      </c>
-      <c r="Q41">
-        <f>(1+ VLOOKUP($C41,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.238</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -17945,15 +18069,15 @@
       </c>
       <c r="M42">
         <f t="shared" si="1"/>
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="P42">
-        <f>(1+ VLOOKUP($B42,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B41,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.18</v>
+      </c>
+      <c r="Q42">
+        <f>(1+ VLOOKUP($C41,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.238</v>
-      </c>
-      <c r="Q42">
-        <f>(1+ VLOOKUP($C42,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.296</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -17988,12 +18112,12 @@
         <v>2.6</v>
       </c>
       <c r="P43">
-        <f>(1+ VLOOKUP($B43,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B42,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.238</v>
+      </c>
+      <c r="Q43">
+        <f>(1+ VLOOKUP($C42,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.296</v>
-      </c>
-      <c r="Q43">
-        <f>(1+ VLOOKUP($C43,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.238</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -18025,15 +18149,15 @@
       </c>
       <c r="M44">
         <f t="shared" si="1"/>
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="P44">
-        <f>(1+ VLOOKUP($B44,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B43,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.296</v>
+      </c>
+      <c r="Q44">
+        <f>(1+ VLOOKUP($C43,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.238</v>
-      </c>
-      <c r="Q44">
-        <f>(1+ VLOOKUP($C44,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.165</v>
       </c>
     </row>
     <row r="45" spans="1:17">
@@ -18068,12 +18192,12 @@
         <v>2.44</v>
       </c>
       <c r="P45">
-        <f>(1+ VLOOKUP($B45,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B44,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.238</v>
+      </c>
+      <c r="Q45">
+        <f>(1+ VLOOKUP($C44,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
-      </c>
-      <c r="Q45">
-        <f>(1+ VLOOKUP($C45,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.238</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -18108,12 +18232,12 @@
         <v>2.44</v>
       </c>
       <c r="P46">
-        <f>(1+ VLOOKUP($B46,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B45,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.165</v>
+      </c>
+      <c r="Q46">
+        <f>(1+ VLOOKUP($C45,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.238</v>
-      </c>
-      <c r="Q46">
-        <f>(1+ VLOOKUP($C46,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.165</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -18148,12 +18272,12 @@
         <v>2.44</v>
       </c>
       <c r="P47">
-        <f>(1+ VLOOKUP($B47,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B46,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.238</v>
+      </c>
+      <c r="Q47">
+        <f>(1+ VLOOKUP($C46,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
-      </c>
-      <c r="Q47">
-        <f>(1+ VLOOKUP($C47,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.238</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -18185,15 +18309,15 @@
       </c>
       <c r="M48">
         <f t="shared" si="1"/>
-        <v>1.88</v>
+        <v>2.44</v>
       </c>
       <c r="P48">
-        <f>(1+ VLOOKUP($B48,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.79600000000000004</v>
+        <f>(1+ VLOOKUP($B47,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.165</v>
       </c>
       <c r="Q48">
-        <f>(1+ VLOOKUP($C48,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
+        <f>(1+ VLOOKUP($C47,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.238</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -18228,12 +18352,12 @@
         <v>1.88</v>
       </c>
       <c r="P49">
-        <f>(1+ VLOOKUP($B49,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B48,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="Q49">
+        <f>(1+ VLOOKUP($C48,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q49">
-        <f>(1+ VLOOKUP($C49,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.79600000000000004</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -18265,15 +18389,15 @@
       </c>
       <c r="M50">
         <f t="shared" si="1"/>
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="P50">
-        <f>(1+ VLOOKUP($B50,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B49,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q50">
+        <f>(1+ VLOOKUP($C49,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>0.79600000000000004</v>
-      </c>
-      <c r="Q50">
-        <f>(1+ VLOOKUP($C50,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.70100000000000007</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -18308,12 +18432,12 @@
         <v>1.56</v>
       </c>
       <c r="P51">
-        <f>(1+ VLOOKUP($B51,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B50,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="Q51">
+        <f>(1+ VLOOKUP($C50,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>0.70100000000000007</v>
-      </c>
-      <c r="Q51">
-        <f>(1+ VLOOKUP($C51,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.79600000000000004</v>
       </c>
     </row>
     <row r="52" spans="1:17">
@@ -18345,15 +18469,15 @@
       </c>
       <c r="M52">
         <f t="shared" si="1"/>
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="P52">
-        <f>(1+ VLOOKUP($B52,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.91700000000000004</v>
+        <f>(1+ VLOOKUP($B51,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.70100000000000007</v>
       </c>
       <c r="Q52">
-        <f>(1+ VLOOKUP($C52,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.054</v>
+        <f>(1+ VLOOKUP($C51,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.79600000000000004</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -18388,12 +18512,12 @@
         <v>1.97</v>
       </c>
       <c r="P53">
-        <f>(1+ VLOOKUP($B53,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B52,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="Q53">
+        <f>(1+ VLOOKUP($C52,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.054</v>
-      </c>
-      <c r="Q53">
-        <f>(1+ VLOOKUP($C53,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.91700000000000004</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -18425,15 +18549,15 @@
       </c>
       <c r="M54">
         <f t="shared" si="1"/>
-        <v>2.4699999999999998</v>
+        <v>1.97</v>
       </c>
       <c r="P54">
-        <f>(1+ VLOOKUP($B54,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
+        <f>(1+ VLOOKUP($B53,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.054</v>
       </c>
       <c r="Q54">
-        <f>(1+ VLOOKUP($C54,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.325</v>
+        <f>(1+ VLOOKUP($C53,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.91700000000000004</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -18468,12 +18592,12 @@
         <v>2.4699999999999998</v>
       </c>
       <c r="P55">
-        <f>(1+ VLOOKUP($B55,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B54,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q55">
+        <f>(1+ VLOOKUP($C54,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.325</v>
-      </c>
-      <c r="Q55">
-        <f>(1+ VLOOKUP($C55,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:17">
@@ -18505,15 +18629,15 @@
       </c>
       <c r="M56">
         <f t="shared" si="1"/>
-        <v>2.31</v>
+        <v>2.4699999999999998</v>
       </c>
       <c r="P56">
-        <f>(1+ VLOOKUP($B56,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B55,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.325</v>
+      </c>
+      <c r="Q56">
+        <f>(1+ VLOOKUP($C55,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q56">
-        <f>(1+ VLOOKUP($C56,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.181</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -18548,12 +18672,12 @@
         <v>2.31</v>
       </c>
       <c r="P57">
-        <f>(1+ VLOOKUP($B57,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B56,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q57">
+        <f>(1+ VLOOKUP($C56,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.181</v>
-      </c>
-      <c r="Q57">
-        <f>(1+ VLOOKUP($C57,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -18585,15 +18709,15 @@
       </c>
       <c r="M58">
         <f t="shared" si="1"/>
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="P58">
-        <f>(1+ VLOOKUP($B58,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B57,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.181</v>
+      </c>
+      <c r="Q58">
+        <f>(1+ VLOOKUP($C57,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.1080000000000001</v>
-      </c>
-      <c r="Q58">
-        <f>(1+ VLOOKUP($C58,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.165</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -18628,12 +18752,12 @@
         <v>2.29</v>
       </c>
       <c r="P59">
-        <f>(1+ VLOOKUP($B59,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B58,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="Q59">
+        <f>(1+ VLOOKUP($C58,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
-      </c>
-      <c r="Q59">
-        <f>(1+ VLOOKUP($C59,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:17">
@@ -18665,15 +18789,15 @@
       </c>
       <c r="M60">
         <f t="shared" si="1"/>
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="P60">
-        <f>(1+ VLOOKUP($B60,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.054</v>
+        <f>(1+ VLOOKUP($B59,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.165</v>
       </c>
       <c r="Q60">
-        <f>(1+ VLOOKUP($C60,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.165</v>
+        <f>(1+ VLOOKUP($C59,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -18708,12 +18832,12 @@
         <v>2.23</v>
       </c>
       <c r="P61">
-        <f>(1+ VLOOKUP($B61,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B60,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.054</v>
+      </c>
+      <c r="Q61">
+        <f>(1+ VLOOKUP($C60,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
-      </c>
-      <c r="Q61">
-        <f>(1+ VLOOKUP($C61,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.054</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -18745,15 +18869,15 @@
       </c>
       <c r="M62">
         <f t="shared" si="1"/>
-        <v>1.54</v>
+        <v>2.23</v>
       </c>
       <c r="P62">
-        <f>(1+ VLOOKUP($B62,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.76700000000000002</v>
+        <f>(1+ VLOOKUP($B61,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.165</v>
       </c>
       <c r="Q62">
-        <f>(1+ VLOOKUP($C62,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.70100000000000007</v>
+        <f>(1+ VLOOKUP($C61,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.054</v>
       </c>
     </row>
     <row r="63" spans="1:17">
@@ -18788,12 +18912,12 @@
         <v>1.54</v>
       </c>
       <c r="P63">
-        <f>(1+ VLOOKUP($B63,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B62,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="Q63">
+        <f>(1+ VLOOKUP($C62,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>0.70100000000000007</v>
-      </c>
-      <c r="Q63">
-        <f>(1+ VLOOKUP($C63,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.76700000000000002</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -18825,15 +18949,15 @@
       </c>
       <c r="M64">
         <f t="shared" si="1"/>
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P64">
-        <f>(1+ VLOOKUP($B64,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B63,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.70100000000000007</v>
+      </c>
+      <c r="Q64">
+        <f>(1+ VLOOKUP($C63,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>0.76700000000000002</v>
-      </c>
-      <c r="Q64">
-        <f>(1+ VLOOKUP($C64,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.69</v>
       </c>
     </row>
     <row r="65" spans="1:17">
@@ -18868,12 +18992,12 @@
         <v>1.53</v>
       </c>
       <c r="P65">
-        <f>(1+ VLOOKUP($B65,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B64,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="Q65">
+        <f>(1+ VLOOKUP($C64,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>0.69</v>
-      </c>
-      <c r="Q65">
-        <f>(1+ VLOOKUP($C65,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.76700000000000002</v>
       </c>
     </row>
     <row r="66" spans="1:17">
@@ -18905,15 +19029,15 @@
       </c>
       <c r="M66">
         <f t="shared" si="1"/>
-        <v>1.8900000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="P66">
-        <f>(1+ VLOOKUP($B66,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B65,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.69</v>
+      </c>
+      <c r="Q66">
+        <f>(1+ VLOOKUP($C65,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>0.76700000000000002</v>
-      </c>
-      <c r="Q66">
-        <f>(1+ VLOOKUP($C66,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.157</v>
       </c>
     </row>
     <row r="67" spans="1:17">
@@ -18936,7 +19060,7 @@
         <v>700</v>
       </c>
       <c r="G67" s="19">
-        <f t="shared" ref="G67:G93" si="2">M67</f>
+        <f t="shared" ref="G67:G93" si="2">M68</f>
         <v>1.8900000000000001</v>
       </c>
       <c r="I67" s="19" t="str">
@@ -18944,16 +19068,16 @@
         <v/>
       </c>
       <c r="M67">
-        <f t="shared" ref="M67:M93" si="3">ROUND(P67*Q67, 2)+1</f>
+        <f t="shared" si="1"/>
         <v>1.8900000000000001</v>
       </c>
       <c r="P67">
-        <f>(1+ VLOOKUP($B67,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B66,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="Q67">
+        <f>(1+ VLOOKUP($C66,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.157</v>
-      </c>
-      <c r="Q67">
-        <f>(1+ VLOOKUP($C67,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.76700000000000002</v>
       </c>
     </row>
     <row r="68" spans="1:17">
@@ -18984,16 +19108,16 @@
         <v/>
       </c>
       <c r="M68">
-        <f t="shared" si="3"/>
-        <v>2.5300000000000002</v>
+        <f t="shared" ref="M68:M94" si="3">ROUND(P68*Q68, 2)+1</f>
+        <v>1.8900000000000001</v>
       </c>
       <c r="P68">
-        <f>(1+ VLOOKUP($B68,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.18</v>
+        <f>(1+ VLOOKUP($B67,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.157</v>
       </c>
       <c r="Q68">
-        <f>(1+ VLOOKUP($C68,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.296</v>
+        <f>(1+ VLOOKUP($C67,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.76700000000000002</v>
       </c>
     </row>
     <row r="69" spans="1:17">
@@ -19028,12 +19152,12 @@
         <v>2.5300000000000002</v>
       </c>
       <c r="P69">
-        <f>(1+ VLOOKUP($B69,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B68,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.18</v>
+      </c>
+      <c r="Q69">
+        <f>(1+ VLOOKUP($C68,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.296</v>
-      </c>
-      <c r="Q69">
-        <f>(1+ VLOOKUP($C69,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.18</v>
       </c>
     </row>
     <row r="70" spans="1:17">
@@ -19065,15 +19189,15 @@
       </c>
       <c r="M70">
         <f t="shared" si="3"/>
-        <v>2.37</v>
+        <v>2.5300000000000002</v>
       </c>
       <c r="P70">
-        <f>(1+ VLOOKUP($B70,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B69,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.296</v>
+      </c>
+      <c r="Q70">
+        <f>(1+ VLOOKUP($C69,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.18</v>
-      </c>
-      <c r="Q70">
-        <f>(1+ VLOOKUP($C70,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.165</v>
       </c>
     </row>
     <row r="71" spans="1:17">
@@ -19108,12 +19232,12 @@
         <v>2.37</v>
       </c>
       <c r="P71">
-        <f>(1+ VLOOKUP($B71,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B70,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.18</v>
+      </c>
+      <c r="Q71">
+        <f>(1+ VLOOKUP($C70,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
-      </c>
-      <c r="Q71">
-        <f>(1+ VLOOKUP($C71,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.18</v>
       </c>
     </row>
     <row r="72" spans="1:17">
@@ -19145,15 +19269,15 @@
       </c>
       <c r="M72">
         <f t="shared" si="3"/>
-        <v>2.74</v>
+        <v>2.37</v>
       </c>
       <c r="P72">
-        <f>(1+ VLOOKUP($B72,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.31</v>
+        <f>(1+ VLOOKUP($B71,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.165</v>
       </c>
       <c r="Q72">
-        <f>(1+ VLOOKUP($C72,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.325</v>
+        <f>(1+ VLOOKUP($C71,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.18</v>
       </c>
     </row>
     <row r="73" spans="1:17">
@@ -19188,12 +19312,12 @@
         <v>2.74</v>
       </c>
       <c r="P73">
-        <f>(1+ VLOOKUP($B73,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B72,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.31</v>
+      </c>
+      <c r="Q73">
+        <f>(1+ VLOOKUP($C72,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.325</v>
-      </c>
-      <c r="Q73">
-        <f>(1+ VLOOKUP($C73,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.31</v>
       </c>
     </row>
     <row r="74" spans="1:17">
@@ -19225,15 +19349,15 @@
       </c>
       <c r="M74">
         <f t="shared" si="3"/>
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="P74">
-        <f>(1+ VLOOKUP($B74,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B73,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.325</v>
+      </c>
+      <c r="Q74">
+        <f>(1+ VLOOKUP($C73,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.31</v>
-      </c>
-      <c r="Q74">
-        <f>(1+ VLOOKUP($C74,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.296</v>
       </c>
     </row>
     <row r="75" spans="1:17">
@@ -19268,12 +19392,12 @@
         <v>2.7</v>
       </c>
       <c r="P75">
-        <f>(1+ VLOOKUP($B75,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B74,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.31</v>
+      </c>
+      <c r="Q75">
+        <f>(1+ VLOOKUP($C74,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.296</v>
-      </c>
-      <c r="Q75">
-        <f>(1+ VLOOKUP($C75,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.31</v>
       </c>
     </row>
     <row r="76" spans="1:17">
@@ -19305,15 +19429,15 @@
       </c>
       <c r="M76">
         <f t="shared" si="3"/>
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="P76">
-        <f>(1+ VLOOKUP($B76,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B75,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.296</v>
+      </c>
+      <c r="Q76">
+        <f>(1+ VLOOKUP($C75,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.31</v>
-      </c>
-      <c r="Q76">
-        <f>(1+ VLOOKUP($C76,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.173</v>
       </c>
     </row>
     <row r="77" spans="1:17">
@@ -19348,12 +19472,12 @@
         <v>2.54</v>
       </c>
       <c r="P77">
-        <f>(1+ VLOOKUP($B77,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B76,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.31</v>
+      </c>
+      <c r="Q77">
+        <f>(1+ VLOOKUP($C76,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.173</v>
-      </c>
-      <c r="Q77">
-        <f>(1+ VLOOKUP($C77,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.31</v>
       </c>
     </row>
     <row r="78" spans="1:17">
@@ -19385,15 +19509,15 @@
       </c>
       <c r="M78">
         <f t="shared" si="3"/>
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="P78">
-        <f>(1+ VLOOKUP($B78,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.325</v>
+        <f>(1+ VLOOKUP($B77,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.173</v>
       </c>
       <c r="Q78">
-        <f>(1+ VLOOKUP($C78,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.181</v>
+        <f>(1+ VLOOKUP($C77,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.31</v>
       </c>
     </row>
     <row r="79" spans="1:17">
@@ -19428,12 +19552,12 @@
         <v>2.56</v>
       </c>
       <c r="P79">
-        <f>(1+ VLOOKUP($B79,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B78,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.325</v>
+      </c>
+      <c r="Q79">
+        <f>(1+ VLOOKUP($C78,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.181</v>
-      </c>
-      <c r="Q79">
-        <f>(1+ VLOOKUP($C79,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.325</v>
       </c>
     </row>
     <row r="80" spans="1:17">
@@ -19465,15 +19589,15 @@
       </c>
       <c r="M80">
         <f t="shared" si="3"/>
-        <v>2.5499999999999998</v>
+        <v>2.56</v>
       </c>
       <c r="P80">
-        <f>(1+ VLOOKUP($B80,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B79,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.181</v>
+      </c>
+      <c r="Q80">
+        <f>(1+ VLOOKUP($C79,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.325</v>
-      </c>
-      <c r="Q80">
-        <f>(1+ VLOOKUP($C80,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.173</v>
       </c>
     </row>
     <row r="81" spans="1:17">
@@ -19508,12 +19632,12 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="P81">
-        <f>(1+ VLOOKUP($B81,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B80,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.325</v>
+      </c>
+      <c r="Q81">
+        <f>(1+ VLOOKUP($C80,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.173</v>
-      </c>
-      <c r="Q81">
-        <f>(1+ VLOOKUP($C81,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.325</v>
       </c>
     </row>
     <row r="82" spans="1:17">
@@ -19545,15 +19669,15 @@
       </c>
       <c r="M82">
         <f t="shared" si="3"/>
-        <v>2.5099999999999998</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="P82">
-        <f>(1+ VLOOKUP($B82,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.296</v>
+        <f>(1+ VLOOKUP($B81,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.173</v>
       </c>
       <c r="Q82">
-        <f>(1+ VLOOKUP($C82,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.165</v>
+        <f>(1+ VLOOKUP($C81,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.325</v>
       </c>
     </row>
     <row r="83" spans="1:17">
@@ -19588,12 +19712,12 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="P83">
-        <f>(1+ VLOOKUP($B83,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B82,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.296</v>
+      </c>
+      <c r="Q83">
+        <f>(1+ VLOOKUP($C82,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
-      </c>
-      <c r="Q83">
-        <f>(1+ VLOOKUP($C83,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.296</v>
       </c>
     </row>
     <row r="84" spans="1:17">
@@ -19628,12 +19752,12 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="P84">
-        <f>(1+ VLOOKUP($B84,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B83,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.165</v>
+      </c>
+      <c r="Q84">
+        <f>(1+ VLOOKUP($C83,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.296</v>
-      </c>
-      <c r="Q84">
-        <f>(1+ VLOOKUP($C84,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.165</v>
       </c>
     </row>
     <row r="85" spans="1:17">
@@ -19668,12 +19792,12 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="P85">
-        <f>(1+ VLOOKUP($B85,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B84,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.296</v>
+      </c>
+      <c r="Q85">
+        <f>(1+ VLOOKUP($C84,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
-      </c>
-      <c r="Q85">
-        <f>(1+ VLOOKUP($C85,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.296</v>
       </c>
     </row>
     <row r="86" spans="1:17">
@@ -19705,15 +19829,15 @@
       </c>
       <c r="M86">
         <f t="shared" si="3"/>
-        <v>1.8</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="P86">
-        <f>(1+ VLOOKUP($B86,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.69</v>
+        <f>(1+ VLOOKUP($B85,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.165</v>
       </c>
       <c r="Q86">
-        <f>(1+ VLOOKUP($C86,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.157</v>
+        <f>(1+ VLOOKUP($C85,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.296</v>
       </c>
     </row>
     <row r="87" spans="1:17">
@@ -19748,12 +19872,12 @@
         <v>1.8</v>
       </c>
       <c r="P87">
-        <f>(1+ VLOOKUP($B87,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B86,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.69</v>
+      </c>
+      <c r="Q87">
+        <f>(1+ VLOOKUP($C86,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.157</v>
-      </c>
-      <c r="Q87">
-        <f>(1+ VLOOKUP($C87,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>0.69</v>
       </c>
     </row>
     <row r="88" spans="1:17">
@@ -19785,15 +19909,15 @@
       </c>
       <c r="M88">
         <f t="shared" si="3"/>
-        <v>2.3899999999999997</v>
+        <v>1.8</v>
       </c>
       <c r="P88">
-        <f>(1+ VLOOKUP($B88,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.181</v>
+        <f>(1+ VLOOKUP($B87,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.157</v>
       </c>
       <c r="Q88">
-        <f>(1+ VLOOKUP($C88,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.173</v>
+        <f>(1+ VLOOKUP($C87,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>0.69</v>
       </c>
     </row>
     <row r="89" spans="1:17">
@@ -19828,12 +19952,12 @@
         <v>2.3899999999999997</v>
       </c>
       <c r="P89">
-        <f>(1+ VLOOKUP($B89,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B88,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.181</v>
+      </c>
+      <c r="Q89">
+        <f>(1+ VLOOKUP($C88,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.173</v>
-      </c>
-      <c r="Q89">
-        <f>(1+ VLOOKUP($C89,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.181</v>
       </c>
     </row>
     <row r="90" spans="1:17">
@@ -19865,15 +19989,15 @@
       </c>
       <c r="M90">
         <f t="shared" si="3"/>
-        <v>2.37</v>
+        <v>2.3899999999999997</v>
       </c>
       <c r="P90">
-        <f>(1+ VLOOKUP($B90,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B89,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.173</v>
       </c>
       <c r="Q90">
-        <f>(1+ VLOOKUP($C90,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.165</v>
+        <f>(1+ VLOOKUP($C89,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.181</v>
       </c>
     </row>
     <row r="91" spans="1:17">
@@ -19908,12 +20032,12 @@
         <v>2.37</v>
       </c>
       <c r="P91">
-        <f>(1+ VLOOKUP($B91,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B90,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.173</v>
+      </c>
+      <c r="Q91">
+        <f>(1+ VLOOKUP($C90,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
-      </c>
-      <c r="Q91">
-        <f>(1+ VLOOKUP($C91,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.173</v>
       </c>
     </row>
     <row r="92" spans="1:17">
@@ -19945,15 +20069,15 @@
       </c>
       <c r="M92">
         <f t="shared" si="3"/>
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="P92">
-        <f>(1+ VLOOKUP($B92,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <f>(1+ VLOOKUP($B91,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
       </c>
       <c r="Q92">
-        <f>(1+ VLOOKUP($C92,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
-        <v>1.157</v>
+        <f>(1+ VLOOKUP($C91,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.173</v>
       </c>
     </row>
     <row r="93" spans="1:17">
@@ -19988,10 +20112,24 @@
         <v>2.35</v>
       </c>
       <c r="P93">
+        <f>(1+ VLOOKUP($B92,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.165</v>
+      </c>
+      <c r="Q93">
+        <f>(1+ VLOOKUP($C92,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
+        <v>1.157</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17">
+      <c r="M94">
+        <f t="shared" si="3"/>
+        <v>2.35</v>
+      </c>
+      <c r="P94">
         <f>(1+ VLOOKUP($B93,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.157</v>
       </c>
-      <c r="Q93">
+      <c r="Q94">
         <f>(1+ VLOOKUP($C93,'vomcost mult'!$N$10:$R$32,5, FALSE))</f>
         <v>1.165</v>
       </c>
@@ -20095,7 +20233,7 @@
         <v>223</v>
       </c>
       <c r="G1" s="56" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -21424,38 +21562,38 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
-      <c r="W3" s="80"/>
-      <c r="X3" s="80"/>
-      <c r="Y3" s="80"/>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
-      <c r="AB3" s="80"/>
-      <c r="AC3" s="80"/>
-      <c r="AD3" s="80"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="83"/>
+      <c r="U3" s="83"/>
+      <c r="V3" s="83"/>
+      <c r="W3" s="83"/>
+      <c r="X3" s="83"/>
+      <c r="Y3" s="83"/>
+      <c r="Z3" s="83"/>
+      <c r="AA3" s="83"/>
+      <c r="AB3" s="83"/>
+      <c r="AC3" s="83"/>
+      <c r="AD3" s="83"/>
     </row>
     <row r="4" spans="1:30" ht="16.5" thickBot="1">
       <c r="A4" s="2" t="s">
@@ -21548,38 +21686,38 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="16.5" thickBot="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="82"/>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="82"/>
-      <c r="S5" s="82"/>
-      <c r="T5" s="82"/>
-      <c r="U5" s="82"/>
-      <c r="V5" s="82"/>
-      <c r="W5" s="82"/>
-      <c r="X5" s="82"/>
-      <c r="Y5" s="82"/>
-      <c r="Z5" s="82"/>
-      <c r="AA5" s="82"/>
-      <c r="AB5" s="82"/>
-      <c r="AC5" s="82"/>
-      <c r="AD5" s="83"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="85"/>
+      <c r="W5" s="85"/>
+      <c r="X5" s="85"/>
+      <c r="Y5" s="85"/>
+      <c r="Z5" s="85"/>
+      <c r="AA5" s="85"/>
+      <c r="AB5" s="85"/>
+      <c r="AC5" s="85"/>
+      <c r="AD5" s="86"/>
     </row>
     <row r="6" spans="1:30" ht="16.5" thickBot="1">
       <c r="A6" s="4"/>
@@ -34331,31 +34469,31 @@
     </row>
     <row r="2" spans="2:24" ht="15.75" thickBot="1"/>
     <row r="3" spans="2:24" ht="16.5" thickBot="1">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="85"/>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="85"/>
-      <c r="T3" s="85"/>
-      <c r="U3" s="85"/>
-      <c r="V3" s="85"/>
-      <c r="W3" s="85"/>
-      <c r="X3" s="86"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="W3" s="88"/>
+      <c r="X3" s="89"/>
     </row>
     <row r="4" spans="2:24" ht="23.25" thickBot="1">
       <c r="B4" s="12" t="s">
@@ -36528,10 +36666,10 @@
       </c>
     </row>
     <row r="33" spans="1:24" ht="16.5" thickBot="1">
-      <c r="B33" s="87" t="s">
+      <c r="B33" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="88"/>
+      <c r="C33" s="91"/>
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
       <c r="F33" s="16"/>
@@ -40418,7 +40556,7 @@
         <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D25">
         <f t="shared" ref="D25:S40" ca="1" si="6">SUMIFS( INDIRECT(CONCATENATE($C25,"!", $A25, ":", $A25)),  INDIRECT(CONCATENATE($C25, "!$4:$4")), D$1)</f>
@@ -40538,7 +40676,7 @@
         <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="6"/>
@@ -40658,7 +40796,7 @@
         <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="6"/>
@@ -40778,7 +40916,7 @@
         <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="6"/>
@@ -40898,7 +41036,7 @@
         <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D29">
         <f t="shared" ca="1" si="6"/>
@@ -41018,7 +41156,7 @@
         <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="6"/>
@@ -41138,7 +41276,7 @@
         <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D31">
         <f t="shared" ca="1" si="6"/>
@@ -41258,7 +41396,7 @@
         <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D32">
         <f t="shared" ca="1" si="6"/>
@@ -41378,7 +41516,7 @@
         <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="6"/>
@@ -41498,7 +41636,7 @@
         <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D34">
         <f t="shared" ca="1" si="6"/>
@@ -41618,7 +41756,7 @@
         <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D35">
         <f t="shared" ca="1" si="6"/>
@@ -41738,7 +41876,7 @@
         <v>125</v>
       </c>
       <c r="C36" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="6"/>
@@ -41858,7 +41996,7 @@
         <v>126</v>
       </c>
       <c r="C37" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D37">
         <f t="shared" ca="1" si="6"/>
@@ -41978,7 +42116,7 @@
         <v>127</v>
       </c>
       <c r="C38" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D38">
         <f t="shared" ca="1" si="6"/>
@@ -42098,7 +42236,7 @@
         <v>128</v>
       </c>
       <c r="C39" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D39">
         <f t="shared" ca="1" si="6"/>
@@ -42218,7 +42356,7 @@
         <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D40">
         <f t="shared" ca="1" si="6"/>
@@ -42338,7 +42476,7 @@
         <v>130</v>
       </c>
       <c r="C41" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D41">
         <f t="shared" ref="D41:R46" ca="1" si="10">SUMIFS( INDIRECT(CONCATENATE($C41,"!", $A41, ":", $A41)),  INDIRECT(CONCATENATE($C41, "!$4:$4")), D$1)</f>
@@ -42458,7 +42596,7 @@
         <v>131</v>
       </c>
       <c r="C42" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D42">
         <f t="shared" ca="1" si="10"/>
@@ -42578,7 +42716,7 @@
         <v>132</v>
       </c>
       <c r="C43" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D43">
         <f t="shared" ca="1" si="10"/>
@@ -42698,7 +42836,7 @@
         <v>133</v>
       </c>
       <c r="C44" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D44">
         <f t="shared" ca="1" si="10"/>
@@ -42818,7 +42956,7 @@
         <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="10"/>
@@ -42938,7 +43076,7 @@
         <v>135</v>
       </c>
       <c r="C46" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D46">
         <f t="shared" ca="1" si="10"/>
@@ -45865,10 +46003,16 @@
         <v>167</v>
       </c>
       <c r="J1" s="76"/>
+      <c r="L1" t="s">
+        <v>323</v>
+      </c>
+      <c r="M1" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="76" t="s">
-        <v>311</v>
+      <c r="A2" s="81" t="s">
+        <v>321</v>
       </c>
       <c r="B2" s="76"/>
       <c r="C2" s="76"/>
@@ -48188,7 +48332,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="17" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
@@ -50484,7 +50628,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="17" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C180" s="19"/>
       <c r="D180" s="19"/>
@@ -52789,27 +52933,27 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:15" ht="24">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
     </row>
     <row r="4" spans="1:15">
       <c r="E4" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -52817,18 +52961,18 @@
         <v>165</v>
       </c>
       <c r="F6" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="G6" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="F7" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="G7" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -52982,7 +53126,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G21" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="5:7">
@@ -53120,23 +53264,23 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="24">
-      <c r="A36" s="89"/>
-      <c r="B36" s="90" t="s">
+      <c r="A36" s="79"/>
+      <c r="B36" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="89"/>
-      <c r="D36" s="89"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="89"/>
-      <c r="H36" s="89"/>
-      <c r="I36" s="89"/>
-      <c r="J36" s="89"/>
-      <c r="K36" s="89"/>
-      <c r="L36" s="89"/>
-      <c r="M36" s="89"/>
-      <c r="N36" s="89"/>
-      <c r="O36" s="89"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="79"/>
+      <c r="J36" s="79"/>
+      <c r="K36" s="79"/>
+      <c r="L36" s="79"/>
+      <c r="M36" s="79"/>
+      <c r="N36" s="79"/>
+      <c r="O36" s="79"/>
     </row>
     <row r="43" spans="1:15">
       <c r="B43">
